--- a/artfynd/A 32085-2025 artfynd.xlsx
+++ b/artfynd/A 32085-2025 artfynd.xlsx
@@ -812,46 +812,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127295076</v>
+        <v>127297595</v>
       </c>
       <c r="B3" t="n">
-        <v>98436</v>
+        <v>75130</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -859,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505375</v>
+        <v>505508</v>
       </c>
       <c r="R3" t="n">
-        <v>6666039</v>
+        <v>6666170</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +895,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,6 +907,26 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -932,37 +943,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127297595</v>
+        <v>127295076</v>
       </c>
       <c r="B4" t="n">
-        <v>75127</v>
+        <v>98442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -970,10 +990,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505508</v>
+        <v>505375</v>
       </c>
       <c r="R4" t="n">
-        <v>6666170</v>
+        <v>6666039</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,7 +1025,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1015,7 +1035,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,26 +1047,6 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1063,45 +1063,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127296095</v>
+        <v>127294425</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>97320</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1109,10 +1102,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505457</v>
+        <v>505296</v>
       </c>
       <c r="R5" t="n">
-        <v>6666067</v>
+        <v>6666023</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1137,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1154,7 +1147,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,26 +1159,6 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Dead branch  # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1202,38 +1175,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127294425</v>
+        <v>127296095</v>
       </c>
       <c r="B6" t="n">
-        <v>97314</v>
+        <v>79046</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1241,10 +1221,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505296</v>
+        <v>505457</v>
       </c>
       <c r="R6" t="n">
-        <v>6666023</v>
+        <v>6666067</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1276,7 +1256,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1286,7 +1266,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1298,6 +1278,26 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Dead branch  # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1314,44 +1314,36 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127295189</v>
+        <v>127296163</v>
       </c>
       <c r="B7" t="n">
-        <v>98436</v>
+        <v>96695</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1361,10 +1353,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505380</v>
+        <v>505465</v>
       </c>
       <c r="R7" t="n">
-        <v>6666036</v>
+        <v>6666072</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1396,7 +1388,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1406,7 +1398,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1418,6 +1410,26 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1434,10 +1446,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127294826</v>
+        <v>127295189</v>
       </c>
       <c r="B8" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1464,7 +1476,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1481,10 +1493,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505332</v>
+        <v>505380</v>
       </c>
       <c r="R8" t="n">
-        <v>6666037</v>
+        <v>6666036</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1516,7 +1528,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1526,7 +1538,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1554,36 +1566,44 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127296163</v>
+        <v>127294826</v>
       </c>
       <c r="B9" t="n">
-        <v>96689</v>
+        <v>98442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1593,10 +1613,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505465</v>
+        <v>505332</v>
       </c>
       <c r="R9" t="n">
-        <v>6666072</v>
+        <v>6666037</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1628,7 +1648,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1638,7 +1658,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1650,26 +1670,6 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1689,7 +1689,7 @@
         <v>127295345</v>
       </c>
       <c r="B10" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>127297697</v>
       </c>
       <c r="B11" t="n">
-        <v>96689</v>
+        <v>96695</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>127294550</v>
       </c>
       <c r="B12" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>127295061</v>
       </c>
       <c r="B13" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>127294748</v>
       </c>
       <c r="B14" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>127295213</v>
       </c>
       <c r="B15" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2418,46 +2418,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127295297</v>
+        <v>127297615</v>
       </c>
       <c r="B16" t="n">
-        <v>98436</v>
+        <v>75130</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2465,10 +2456,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505400</v>
+        <v>505511</v>
       </c>
       <c r="R16" t="n">
-        <v>6666034</v>
+        <v>6666168</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2500,7 +2491,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2510,7 +2501,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2522,6 +2513,26 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2538,44 +2549,36 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127296113</v>
+        <v>127297651</v>
       </c>
       <c r="B17" t="n">
-        <v>98436</v>
+        <v>96695</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2585,10 +2588,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505461</v>
+        <v>505512</v>
       </c>
       <c r="R17" t="n">
-        <v>6666073</v>
+        <v>6666168</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2620,7 +2623,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2630,7 +2633,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2642,6 +2645,26 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2658,37 +2681,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127297615</v>
+        <v>127295297</v>
       </c>
       <c r="B18" t="n">
-        <v>75127</v>
+        <v>98442</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2696,10 +2728,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505511</v>
+        <v>505400</v>
       </c>
       <c r="R18" t="n">
-        <v>6666168</v>
+        <v>6666034</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2731,7 +2763,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2741,7 +2773,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2753,26 +2785,6 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2789,36 +2801,44 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127297651</v>
+        <v>127296113</v>
       </c>
       <c r="B19" t="n">
-        <v>96689</v>
+        <v>98442</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2828,10 +2848,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>505512</v>
+        <v>505461</v>
       </c>
       <c r="R19" t="n">
-        <v>6666168</v>
+        <v>6666073</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2863,7 +2883,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2873,7 +2893,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2885,26 +2905,6 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2924,7 +2924,7 @@
         <v>127295662</v>
       </c>
       <c r="B20" t="n">
-        <v>75127</v>
+        <v>75130</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>127296043</v>
       </c>
       <c r="B21" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3172,36 +3172,44 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127297420</v>
+        <v>127295317</v>
       </c>
       <c r="B22" t="n">
-        <v>96689</v>
+        <v>98442</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -3211,10 +3219,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>505483</v>
+        <v>505401</v>
       </c>
       <c r="R22" t="n">
-        <v>6666164</v>
+        <v>6666036</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3246,7 +3254,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3256,7 +3264,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3268,26 +3276,6 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3304,44 +3292,36 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127295317</v>
+        <v>127297420</v>
       </c>
       <c r="B23" t="n">
-        <v>98436</v>
+        <v>96695</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -3351,10 +3331,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>505401</v>
+        <v>505483</v>
       </c>
       <c r="R23" t="n">
-        <v>6666036</v>
+        <v>6666164</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3386,7 +3366,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3396,7 +3376,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3408,6 +3388,26 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3427,7 +3427,7 @@
         <v>127297958</v>
       </c>
       <c r="B24" t="n">
-        <v>75127</v>
+        <v>75130</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3555,45 +3555,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127294423</v>
+        <v>127298417</v>
       </c>
       <c r="B25" t="n">
-        <v>98436</v>
+        <v>98359</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3602,10 +3606,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>505296</v>
+        <v>505547</v>
       </c>
       <c r="R25" t="n">
-        <v>6666023</v>
+        <v>6666020</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3637,7 +3641,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3647,7 +3651,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3675,10 +3679,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127295681</v>
+        <v>127294423</v>
       </c>
       <c r="B26" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3705,7 +3709,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3722,10 +3726,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>505425</v>
+        <v>505296</v>
       </c>
       <c r="R26" t="n">
-        <v>6666033</v>
+        <v>6666023</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3757,7 +3761,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3767,7 +3771,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3795,10 +3799,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295207</v>
+        <v>127295681</v>
       </c>
       <c r="B27" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3825,7 +3829,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3842,10 +3846,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>505383</v>
+        <v>505425</v>
       </c>
       <c r="R27" t="n">
-        <v>6666039</v>
+        <v>6666033</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3877,7 +3881,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3887,7 +3891,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3915,49 +3919,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127298417</v>
+        <v>127295207</v>
       </c>
       <c r="B28" t="n">
-        <v>98353</v>
+        <v>98442</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>505547</v>
+        <v>505383</v>
       </c>
       <c r="R28" t="n">
-        <v>6666020</v>
+        <v>6666039</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4039,10 +4039,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127296321</v>
+        <v>127298321</v>
       </c>
       <c r="B29" t="n">
-        <v>79043</v>
+        <v>79632</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4050,21 +4050,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4077,10 +4077,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>505487</v>
+        <v>505552</v>
       </c>
       <c r="R29" t="n">
-        <v>6666090</v>
+        <v>6666024</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4137,22 +4137,22 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stump # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4170,46 +4170,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127294722</v>
+        <v>127296321</v>
       </c>
       <c r="B30" t="n">
-        <v>98436</v>
+        <v>79046</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4217,10 +4208,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>505312</v>
+        <v>505487</v>
       </c>
       <c r="R30" t="n">
-        <v>6666032</v>
+        <v>6666090</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4252,7 +4243,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4262,7 +4253,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4274,6 +4265,26 @@
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4290,10 +4301,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127298321</v>
+        <v>127297555</v>
       </c>
       <c r="B31" t="n">
-        <v>79629</v>
+        <v>75130</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4301,21 +4312,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4328,10 +4339,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>505552</v>
+        <v>505501</v>
       </c>
       <c r="R31" t="n">
-        <v>6666024</v>
+        <v>6666172</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4363,7 +4374,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4373,7 +4384,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4398,12 +4409,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stump # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4421,37 +4432,46 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127297555</v>
+        <v>127294722</v>
       </c>
       <c r="B32" t="n">
-        <v>75127</v>
+        <v>98442</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4459,10 +4479,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>505501</v>
+        <v>505312</v>
       </c>
       <c r="R32" t="n">
-        <v>6666172</v>
+        <v>6666032</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4494,7 +4514,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4504,7 +4524,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4516,26 +4536,6 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4555,7 +4555,7 @@
         <v>127295731</v>
       </c>
       <c r="B33" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>127294455</v>
       </c>
       <c r="B34" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>127298053</v>
       </c>
       <c r="B35" t="n">
-        <v>78417</v>
+        <v>78420</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>127296758</v>
       </c>
       <c r="B36" t="n">
-        <v>78417</v>
+        <v>78420</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         <v>127294976</v>
       </c>
       <c r="B37" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>127295841</v>
       </c>
       <c r="B38" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5294,36 +5294,44 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127297810</v>
+        <v>127294730</v>
       </c>
       <c r="B39" t="n">
-        <v>96689</v>
+        <v>98442</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -5333,10 +5341,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>505515</v>
+        <v>505313</v>
       </c>
       <c r="R39" t="n">
-        <v>6666146</v>
+        <v>6666027</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5368,7 +5376,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5378,7 +5386,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5390,26 +5398,6 @@
       <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5426,44 +5414,36 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127294730</v>
+        <v>127297810</v>
       </c>
       <c r="B40" t="n">
-        <v>98436</v>
+        <v>96695</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
@@ -5473,10 +5453,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>505313</v>
+        <v>505515</v>
       </c>
       <c r="R40" t="n">
-        <v>6666027</v>
+        <v>6666146</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5508,7 +5488,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5518,7 +5498,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5530,6 +5510,26 @@
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5549,7 +5549,7 @@
         <v>127295873</v>
       </c>
       <c r="B41" t="n">
-        <v>96689</v>
+        <v>96695</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5815,44 +5815,36 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127295399</v>
+        <v>127301907</v>
       </c>
       <c r="B43" t="n">
-        <v>98436</v>
+        <v>96790</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1841</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
@@ -5862,10 +5854,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>505404</v>
+        <v>505491</v>
       </c>
       <c r="R43" t="n">
-        <v>6666039</v>
+        <v>6666106</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5895,19 +5887,9 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>15:03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5919,6 +5901,26 @@
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5935,36 +5937,44 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127301907</v>
+        <v>127295399</v>
       </c>
       <c r="B44" t="n">
-        <v>96784</v>
+        <v>98442</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1841</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
@@ -5974,10 +5984,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>505491</v>
+        <v>505404</v>
       </c>
       <c r="R44" t="n">
-        <v>6666106</v>
+        <v>6666039</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6007,9 +6017,19 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6021,26 +6041,6 @@
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6057,46 +6057,37 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127295179</v>
+        <v>127298146</v>
       </c>
       <c r="B45" t="n">
-        <v>98436</v>
+        <v>91345</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6104,10 +6095,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>505378</v>
+        <v>505544</v>
       </c>
       <c r="R45" t="n">
-        <v>6666040</v>
+        <v>6666053</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6139,7 +6130,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6149,7 +6140,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6161,6 +6152,21 @@
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6177,10 +6183,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127295238</v>
+        <v>127295179</v>
       </c>
       <c r="B46" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6207,7 +6213,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>149</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6224,10 +6230,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>505388</v>
+        <v>505378</v>
       </c>
       <c r="R46" t="n">
-        <v>6666037</v>
+        <v>6666040</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6259,7 +6265,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6269,7 +6275,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6297,37 +6303,46 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127298146</v>
+        <v>127295238</v>
       </c>
       <c r="B47" t="n">
-        <v>91339</v>
+        <v>98442</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6335,10 +6350,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>505544</v>
+        <v>505388</v>
       </c>
       <c r="R47" t="n">
-        <v>6666053</v>
+        <v>6666037</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6370,7 +6385,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6380,7 +6395,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6392,21 +6407,6 @@
       <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6426,7 +6426,7 @@
         <v>127297221</v>
       </c>
       <c r="B48" t="n">
-        <v>75118</v>
+        <v>75121</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6554,37 +6554,46 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127296862</v>
+        <v>127296142</v>
       </c>
       <c r="B49" t="n">
-        <v>79043</v>
+        <v>98442</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6592,10 +6601,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>505478</v>
+        <v>505465</v>
       </c>
       <c r="R49" t="n">
-        <v>6666105</v>
+        <v>6666072</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6627,7 +6636,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6637,7 +6646,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6649,26 +6658,6 @@
       <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6685,46 +6674,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127296142</v>
+        <v>127296862</v>
       </c>
       <c r="B50" t="n">
-        <v>98436</v>
+        <v>79046</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6732,10 +6712,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>505465</v>
+        <v>505478</v>
       </c>
       <c r="R50" t="n">
-        <v>6666072</v>
+        <v>6666105</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6767,7 +6747,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6777,7 +6757,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6789,6 +6769,26 @@
       <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 32085-2025 artfynd.xlsx
+++ b/artfynd/A 32085-2025 artfynd.xlsx
@@ -812,37 +812,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127297595</v>
+        <v>127295076</v>
       </c>
       <c r="B3" t="n">
-        <v>75130</v>
+        <v>98442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -850,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505508</v>
+        <v>505375</v>
       </c>
       <c r="R3" t="n">
-        <v>6666170</v>
+        <v>6666039</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,26 +916,6 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -943,46 +932,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127295076</v>
+        <v>127297595</v>
       </c>
       <c r="B4" t="n">
-        <v>98442</v>
+        <v>75130</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -990,10 +970,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505375</v>
+        <v>505508</v>
       </c>
       <c r="R4" t="n">
-        <v>6666039</v>
+        <v>6666170</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1025,7 +1005,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1035,7 +1015,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,6 +1027,26 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1063,38 +1063,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127294425</v>
+        <v>127296095</v>
       </c>
       <c r="B5" t="n">
-        <v>97320</v>
+        <v>79046</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1102,10 +1109,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505296</v>
+        <v>505457</v>
       </c>
       <c r="R5" t="n">
-        <v>6666023</v>
+        <v>6666067</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1137,7 +1144,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1147,7 +1154,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,6 +1166,26 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Dead branch  # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1175,45 +1202,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127296095</v>
+        <v>127294425</v>
       </c>
       <c r="B6" t="n">
-        <v>79046</v>
+        <v>97320</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1221,10 +1241,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505457</v>
+        <v>505296</v>
       </c>
       <c r="R6" t="n">
-        <v>6666067</v>
+        <v>6666023</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,7 +1276,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1266,7 +1286,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,26 +1298,6 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Dead branch  # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1314,36 +1314,44 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127296163</v>
+        <v>127295189</v>
       </c>
       <c r="B7" t="n">
-        <v>96695</v>
+        <v>98442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1353,10 +1361,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505465</v>
+        <v>505380</v>
       </c>
       <c r="R7" t="n">
-        <v>6666072</v>
+        <v>6666036</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1388,7 +1396,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1398,7 +1406,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1410,26 +1418,6 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1446,7 +1434,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127295189</v>
+        <v>127294826</v>
       </c>
       <c r="B8" t="n">
         <v>98442</v>
@@ -1476,7 +1464,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1493,10 +1481,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505380</v>
+        <v>505332</v>
       </c>
       <c r="R8" t="n">
-        <v>6666036</v>
+        <v>6666037</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1528,7 +1516,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1538,7 +1526,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1566,7 +1554,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127294826</v>
+        <v>127295345</v>
       </c>
       <c r="B9" t="n">
         <v>98442</v>
@@ -1596,7 +1584,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1613,10 +1601,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505332</v>
+        <v>505402</v>
       </c>
       <c r="R9" t="n">
-        <v>6666037</v>
+        <v>6666038</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1648,7 +1636,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1658,7 +1646,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1686,44 +1674,36 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127295345</v>
+        <v>127296163</v>
       </c>
       <c r="B10" t="n">
-        <v>98442</v>
+        <v>96695</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1733,10 +1713,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505402</v>
+        <v>505465</v>
       </c>
       <c r="R10" t="n">
-        <v>6666038</v>
+        <v>6666072</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1768,7 +1748,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1778,7 +1758,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1790,6 +1770,26 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -3052,44 +3052,36 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127296043</v>
+        <v>127297420</v>
       </c>
       <c r="B21" t="n">
-        <v>98442</v>
+        <v>96695</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -3099,10 +3091,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>505457</v>
+        <v>505483</v>
       </c>
       <c r="R21" t="n">
-        <v>6666067</v>
+        <v>6666164</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3134,7 +3126,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3144,7 +3136,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3156,6 +3148,26 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3172,46 +3184,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295317</v>
+        <v>127297958</v>
       </c>
       <c r="B22" t="n">
-        <v>98442</v>
+        <v>75130</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3219,10 +3222,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>505401</v>
+        <v>505525</v>
       </c>
       <c r="R22" t="n">
-        <v>6666036</v>
+        <v>6666131</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3254,7 +3257,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3264,7 +3267,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3276,6 +3279,26 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3292,36 +3315,44 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127297420</v>
+        <v>127296043</v>
       </c>
       <c r="B23" t="n">
-        <v>96695</v>
+        <v>98442</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -3331,10 +3362,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>505483</v>
+        <v>505457</v>
       </c>
       <c r="R23" t="n">
-        <v>6666164</v>
+        <v>6666067</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3366,7 +3397,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3376,7 +3407,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3388,26 +3419,6 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3424,37 +3435,46 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127297958</v>
+        <v>127295317</v>
       </c>
       <c r="B24" t="n">
-        <v>75130</v>
+        <v>98442</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3462,10 +3482,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505525</v>
+        <v>505401</v>
       </c>
       <c r="R24" t="n">
-        <v>6666131</v>
+        <v>6666036</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3497,7 +3517,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3507,7 +3527,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3519,26 +3539,6 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3555,49 +3555,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127298417</v>
+        <v>127294423</v>
       </c>
       <c r="B25" t="n">
-        <v>98359</v>
+        <v>98442</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3606,10 +3602,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>505547</v>
+        <v>505296</v>
       </c>
       <c r="R25" t="n">
-        <v>6666020</v>
+        <v>6666023</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3641,7 +3637,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3651,7 +3647,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3679,7 +3675,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127294423</v>
+        <v>127295681</v>
       </c>
       <c r="B26" t="n">
         <v>98442</v>
@@ -3709,7 +3705,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3726,10 +3722,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>505296</v>
+        <v>505425</v>
       </c>
       <c r="R26" t="n">
-        <v>6666023</v>
+        <v>6666033</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3761,7 +3757,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3771,7 +3767,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3799,7 +3795,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295681</v>
+        <v>127295207</v>
       </c>
       <c r="B27" t="n">
         <v>98442</v>
@@ -3829,7 +3825,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3846,10 +3842,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>505425</v>
+        <v>505383</v>
       </c>
       <c r="R27" t="n">
-        <v>6666033</v>
+        <v>6666039</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3881,7 +3877,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3891,7 +3887,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3919,45 +3915,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127295207</v>
+        <v>127298417</v>
       </c>
       <c r="B28" t="n">
-        <v>98442</v>
+        <v>98359</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>505383</v>
+        <v>505547</v>
       </c>
       <c r="R28" t="n">
-        <v>6666039</v>
+        <v>6666020</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4039,10 +4039,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127298321</v>
+        <v>127296321</v>
       </c>
       <c r="B29" t="n">
-        <v>79632</v>
+        <v>79046</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4050,21 +4050,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4077,10 +4077,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>505552</v>
+        <v>505487</v>
       </c>
       <c r="R29" t="n">
-        <v>6666024</v>
+        <v>6666090</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4137,22 +4137,22 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stump # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4170,10 +4170,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127296321</v>
+        <v>127297555</v>
       </c>
       <c r="B30" t="n">
-        <v>79046</v>
+        <v>75130</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4181,21 +4181,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>505487</v>
+        <v>505501</v>
       </c>
       <c r="R30" t="n">
-        <v>6666090</v>
+        <v>6666172</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4268,22 +4268,22 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4301,10 +4301,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127297555</v>
+        <v>127298321</v>
       </c>
       <c r="B31" t="n">
-        <v>75130</v>
+        <v>79632</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4312,21 +4312,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>308</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4339,10 +4339,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>505501</v>
+        <v>505552</v>
       </c>
       <c r="R31" t="n">
-        <v>6666172</v>
+        <v>6666024</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Stump # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -5174,44 +5174,36 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127295841</v>
+        <v>127297810</v>
       </c>
       <c r="B38" t="n">
-        <v>98442</v>
+        <v>96695</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -5221,10 +5213,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>505457</v>
+        <v>505515</v>
       </c>
       <c r="R38" t="n">
-        <v>6666062</v>
+        <v>6666146</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5256,7 +5248,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5266,7 +5258,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5278,6 +5270,26 @@
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5294,7 +5306,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127294730</v>
+        <v>127295841</v>
       </c>
       <c r="B39" t="n">
         <v>98442</v>
@@ -5324,7 +5336,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5341,10 +5353,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>505313</v>
+        <v>505457</v>
       </c>
       <c r="R39" t="n">
-        <v>6666027</v>
+        <v>6666062</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5376,7 +5388,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5386,7 +5398,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5414,36 +5426,44 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127297810</v>
+        <v>127294730</v>
       </c>
       <c r="B40" t="n">
-        <v>96695</v>
+        <v>98442</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
@@ -5453,10 +5473,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>505515</v>
+        <v>505313</v>
       </c>
       <c r="R40" t="n">
-        <v>6666146</v>
+        <v>6666027</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5488,7 +5508,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5498,7 +5518,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5510,26 +5530,6 @@
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -6423,32 +6423,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127297221</v>
+        <v>127296862</v>
       </c>
       <c r="B48" t="n">
-        <v>75121</v>
+        <v>79046</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6439</v>
+        <v>185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6464,7 +6464,7 @@
         <v>505478</v>
       </c>
       <c r="R48" t="n">
-        <v>6666109</v>
+        <v>6666105</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6521,22 +6521,22 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6554,46 +6554,37 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127296142</v>
+        <v>127297221</v>
       </c>
       <c r="B49" t="n">
-        <v>98442</v>
+        <v>75121</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6439</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6601,10 +6592,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>505465</v>
+        <v>505478</v>
       </c>
       <c r="R49" t="n">
-        <v>6666072</v>
+        <v>6666109</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6636,7 +6627,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6646,7 +6637,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6658,6 +6649,26 @@
       <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6674,37 +6685,46 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127296862</v>
+        <v>127296142</v>
       </c>
       <c r="B50" t="n">
-        <v>79046</v>
+        <v>98442</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6712,10 +6732,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>505478</v>
+        <v>505465</v>
       </c>
       <c r="R50" t="n">
-        <v>6666105</v>
+        <v>6666072</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6747,7 +6767,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6757,7 +6777,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6769,26 +6789,6 @@
       <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 32085-2025 artfynd.xlsx
+++ b/artfynd/A 32085-2025 artfynd.xlsx
@@ -812,46 +812,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127295076</v>
+        <v>127297595</v>
       </c>
       <c r="B3" t="n">
-        <v>98442</v>
+        <v>75130</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -859,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505375</v>
+        <v>505508</v>
       </c>
       <c r="R3" t="n">
-        <v>6666039</v>
+        <v>6666170</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +895,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,6 +907,26 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -932,37 +943,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127297595</v>
+        <v>127295076</v>
       </c>
       <c r="B4" t="n">
-        <v>75130</v>
+        <v>98443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -970,10 +990,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505508</v>
+        <v>505375</v>
       </c>
       <c r="R4" t="n">
-        <v>6666170</v>
+        <v>6666039</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,7 +1025,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1015,7 +1035,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,26 +1047,6 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1063,45 +1063,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127296095</v>
+        <v>127294425</v>
       </c>
       <c r="B5" t="n">
-        <v>79046</v>
+        <v>97321</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1109,10 +1102,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505457</v>
+        <v>505296</v>
       </c>
       <c r="R5" t="n">
-        <v>6666067</v>
+        <v>6666023</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1137,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1154,7 +1147,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,26 +1159,6 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Dead branch  # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1202,38 +1175,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127294425</v>
+        <v>127296095</v>
       </c>
       <c r="B6" t="n">
-        <v>97320</v>
+        <v>79046</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1241,10 +1221,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505296</v>
+        <v>505457</v>
       </c>
       <c r="R6" t="n">
-        <v>6666023</v>
+        <v>6666067</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1276,7 +1256,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1286,7 +1266,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1298,6 +1278,26 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Dead branch  # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1314,10 +1314,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127295189</v>
+        <v>127295345</v>
       </c>
       <c r="B7" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505380</v>
+        <v>505402</v>
       </c>
       <c r="R7" t="n">
-        <v>6666036</v>
+        <v>6666038</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1437,7 +1437,7 @@
         <v>127294826</v>
       </c>
       <c r="B8" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1554,10 +1554,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127295345</v>
+        <v>127295189</v>
       </c>
       <c r="B9" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505402</v>
+        <v>505380</v>
       </c>
       <c r="R9" t="n">
-        <v>6666038</v>
+        <v>6666036</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1677,7 +1677,7 @@
         <v>127296163</v>
       </c>
       <c r="B10" t="n">
-        <v>96695</v>
+        <v>96696</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>127297697</v>
       </c>
       <c r="B11" t="n">
-        <v>96695</v>
+        <v>96696</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>127294550</v>
       </c>
       <c r="B12" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2058,10 +2058,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127295061</v>
+        <v>127294748</v>
       </c>
       <c r="B13" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505372</v>
+        <v>505318</v>
       </c>
       <c r="R13" t="n">
-        <v>6666038</v>
+        <v>6666032</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2178,10 +2178,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127294748</v>
+        <v>127295061</v>
       </c>
       <c r="B14" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2225,10 +2225,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505318</v>
+        <v>505372</v>
       </c>
       <c r="R14" t="n">
-        <v>6666032</v>
+        <v>6666038</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2301,7 +2301,7 @@
         <v>127295213</v>
       </c>
       <c r="B15" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2418,37 +2418,46 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127297615</v>
+        <v>127295297</v>
       </c>
       <c r="B16" t="n">
-        <v>75130</v>
+        <v>98443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2456,10 +2465,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505511</v>
+        <v>505400</v>
       </c>
       <c r="R16" t="n">
-        <v>6666168</v>
+        <v>6666034</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2491,7 +2500,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2501,7 +2510,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2513,26 +2522,6 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2549,36 +2538,44 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127297651</v>
+        <v>127296113</v>
       </c>
       <c r="B17" t="n">
-        <v>96695</v>
+        <v>98443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2588,10 +2585,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505512</v>
+        <v>505461</v>
       </c>
       <c r="R17" t="n">
-        <v>6666168</v>
+        <v>6666073</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2623,7 +2620,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2633,7 +2630,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2645,26 +2642,6 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2681,46 +2658,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127295297</v>
+        <v>127297615</v>
       </c>
       <c r="B18" t="n">
-        <v>98442</v>
+        <v>75130</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2728,10 +2696,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505400</v>
+        <v>505511</v>
       </c>
       <c r="R18" t="n">
-        <v>6666034</v>
+        <v>6666168</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2763,7 +2731,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2773,7 +2741,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2785,6 +2753,26 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2801,44 +2789,36 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127296113</v>
+        <v>127297651</v>
       </c>
       <c r="B19" t="n">
-        <v>98442</v>
+        <v>96696</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2848,10 +2828,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>505461</v>
+        <v>505512</v>
       </c>
       <c r="R19" t="n">
-        <v>6666073</v>
+        <v>6666168</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2883,7 +2863,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2893,7 +2873,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2905,6 +2885,26 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3052,36 +3052,44 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127297420</v>
+        <v>127296043</v>
       </c>
       <c r="B21" t="n">
-        <v>96695</v>
+        <v>98443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -3091,10 +3099,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>505483</v>
+        <v>505457</v>
       </c>
       <c r="R21" t="n">
-        <v>6666164</v>
+        <v>6666067</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3126,7 +3134,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3136,7 +3144,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3148,26 +3156,6 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3184,37 +3172,46 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127297958</v>
+        <v>127295317</v>
       </c>
       <c r="B22" t="n">
-        <v>75130</v>
+        <v>98443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3222,10 +3219,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>505525</v>
+        <v>505401</v>
       </c>
       <c r="R22" t="n">
-        <v>6666131</v>
+        <v>6666036</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3257,7 +3254,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3267,7 +3264,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3279,26 +3276,6 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3315,44 +3292,36 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127296043</v>
+        <v>127297420</v>
       </c>
       <c r="B23" t="n">
-        <v>98442</v>
+        <v>96696</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -3362,10 +3331,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>505457</v>
+        <v>505483</v>
       </c>
       <c r="R23" t="n">
-        <v>6666067</v>
+        <v>6666164</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3397,7 +3366,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3407,7 +3376,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3419,6 +3388,26 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3435,46 +3424,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295317</v>
+        <v>127297958</v>
       </c>
       <c r="B24" t="n">
-        <v>98442</v>
+        <v>75130</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3482,10 +3462,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505401</v>
+        <v>505525</v>
       </c>
       <c r="R24" t="n">
-        <v>6666036</v>
+        <v>6666131</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3517,7 +3497,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3527,7 +3507,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3539,6 +3519,26 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3555,45 +3555,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127294423</v>
+        <v>127298417</v>
       </c>
       <c r="B25" t="n">
-        <v>98442</v>
+        <v>98360</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3602,10 +3606,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>505296</v>
+        <v>505547</v>
       </c>
       <c r="R25" t="n">
-        <v>6666023</v>
+        <v>6666020</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3637,7 +3641,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3647,7 +3651,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3675,10 +3679,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127295681</v>
+        <v>127295207</v>
       </c>
       <c r="B26" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3705,7 +3709,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3722,10 +3726,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>505425</v>
+        <v>505383</v>
       </c>
       <c r="R26" t="n">
-        <v>6666033</v>
+        <v>6666039</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3757,7 +3761,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3767,7 +3771,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3795,10 +3799,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295207</v>
+        <v>127294423</v>
       </c>
       <c r="B27" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3825,7 +3829,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3842,10 +3846,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>505383</v>
+        <v>505296</v>
       </c>
       <c r="R27" t="n">
-        <v>6666039</v>
+        <v>6666023</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3877,7 +3881,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3887,7 +3891,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3915,49 +3919,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127298417</v>
+        <v>127295681</v>
       </c>
       <c r="B28" t="n">
-        <v>98359</v>
+        <v>98443</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>505547</v>
+        <v>505425</v>
       </c>
       <c r="R28" t="n">
-        <v>6666020</v>
+        <v>6666033</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4039,10 +4039,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127296321</v>
+        <v>127298321</v>
       </c>
       <c r="B29" t="n">
-        <v>79046</v>
+        <v>79632</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4050,21 +4050,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4077,10 +4077,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>505487</v>
+        <v>505552</v>
       </c>
       <c r="R29" t="n">
-        <v>6666090</v>
+        <v>6666024</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4137,22 +4137,22 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stump # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4170,10 +4170,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127297555</v>
+        <v>127296321</v>
       </c>
       <c r="B30" t="n">
-        <v>75130</v>
+        <v>79046</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4181,21 +4181,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>308</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>505501</v>
+        <v>505487</v>
       </c>
       <c r="R30" t="n">
-        <v>6666172</v>
+        <v>6666090</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4268,22 +4268,22 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4301,10 +4301,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127298321</v>
+        <v>127297555</v>
       </c>
       <c r="B31" t="n">
-        <v>79632</v>
+        <v>75130</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4312,21 +4312,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4339,10 +4339,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>505552</v>
+        <v>505501</v>
       </c>
       <c r="R31" t="n">
-        <v>6666024</v>
+        <v>6666172</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stump # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4435,7 +4435,7 @@
         <v>127294722</v>
       </c>
       <c r="B32" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>127295731</v>
       </c>
       <c r="B33" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>127294455</v>
       </c>
       <c r="B34" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         <v>127294976</v>
       </c>
       <c r="B37" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5174,36 +5174,44 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127297810</v>
+        <v>127295841</v>
       </c>
       <c r="B38" t="n">
-        <v>96695</v>
+        <v>98443</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -5213,10 +5221,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>505515</v>
+        <v>505457</v>
       </c>
       <c r="R38" t="n">
-        <v>6666146</v>
+        <v>6666062</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5248,7 +5256,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5258,7 +5266,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5270,26 +5278,6 @@
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5306,10 +5294,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127295841</v>
+        <v>127294730</v>
       </c>
       <c r="B39" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5336,7 +5324,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5353,10 +5341,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>505457</v>
+        <v>505313</v>
       </c>
       <c r="R39" t="n">
-        <v>6666062</v>
+        <v>6666027</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5388,7 +5376,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5398,7 +5386,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5426,44 +5414,36 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127294730</v>
+        <v>127297810</v>
       </c>
       <c r="B40" t="n">
-        <v>98442</v>
+        <v>96696</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
@@ -5473,10 +5453,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>505313</v>
+        <v>505515</v>
       </c>
       <c r="R40" t="n">
-        <v>6666027</v>
+        <v>6666146</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5508,7 +5488,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5518,7 +5498,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5530,6 +5510,26 @@
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5549,7 +5549,7 @@
         <v>127295873</v>
       </c>
       <c r="B41" t="n">
-        <v>96695</v>
+        <v>96696</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>127301907</v>
       </c>
       <c r="B43" t="n">
-        <v>96790</v>
+        <v>96791</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>127295399</v>
       </c>
       <c r="B44" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6057,37 +6057,46 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127298146</v>
+        <v>127295238</v>
       </c>
       <c r="B45" t="n">
-        <v>91345</v>
+        <v>98443</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6095,10 +6104,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>505544</v>
+        <v>505388</v>
       </c>
       <c r="R45" t="n">
-        <v>6666053</v>
+        <v>6666037</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6130,7 +6139,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6140,7 +6149,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6152,21 +6161,6 @@
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6186,7 +6180,7 @@
         <v>127295179</v>
       </c>
       <c r="B46" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6303,46 +6297,37 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127295238</v>
+        <v>127298146</v>
       </c>
       <c r="B47" t="n">
-        <v>98442</v>
+        <v>91346</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6350,10 +6335,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>505388</v>
+        <v>505544</v>
       </c>
       <c r="R47" t="n">
-        <v>6666037</v>
+        <v>6666053</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6385,7 +6370,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6395,7 +6380,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6407,6 +6392,21 @@
       <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6688,7 +6688,7 @@
         <v>127296142</v>
       </c>
       <c r="B50" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 32085-2025 artfynd.xlsx
+++ b/artfynd/A 32085-2025 artfynd.xlsx
@@ -812,37 +812,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127297595</v>
+        <v>127295076</v>
       </c>
       <c r="B3" t="n">
-        <v>75130</v>
+        <v>98443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -850,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505508</v>
+        <v>505375</v>
       </c>
       <c r="R3" t="n">
-        <v>6666170</v>
+        <v>6666039</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,26 +916,6 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -943,46 +932,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127295076</v>
+        <v>127297595</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>75130</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -990,10 +970,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505375</v>
+        <v>505508</v>
       </c>
       <c r="R4" t="n">
-        <v>6666039</v>
+        <v>6666170</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1025,7 +1005,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1035,7 +1015,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,6 +1027,26 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1314,44 +1314,36 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127295345</v>
+        <v>127296163</v>
       </c>
       <c r="B7" t="n">
-        <v>98443</v>
+        <v>96696</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1361,10 +1353,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505402</v>
+        <v>505465</v>
       </c>
       <c r="R7" t="n">
-        <v>6666038</v>
+        <v>6666072</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1396,7 +1388,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1406,7 +1398,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1418,6 +1410,26 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1434,7 +1446,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127294826</v>
+        <v>127295345</v>
       </c>
       <c r="B8" t="n">
         <v>98443</v>
@@ -1464,7 +1476,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1481,10 +1493,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505332</v>
+        <v>505402</v>
       </c>
       <c r="R8" t="n">
-        <v>6666037</v>
+        <v>6666038</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1516,7 +1528,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1526,7 +1538,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1554,7 +1566,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127295189</v>
+        <v>127294826</v>
       </c>
       <c r="B9" t="n">
         <v>98443</v>
@@ -1584,7 +1596,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1601,10 +1613,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505380</v>
+        <v>505332</v>
       </c>
       <c r="R9" t="n">
-        <v>6666036</v>
+        <v>6666037</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1636,7 +1648,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1646,7 +1658,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1674,36 +1686,44 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127296163</v>
+        <v>127295189</v>
       </c>
       <c r="B10" t="n">
-        <v>96696</v>
+        <v>98443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1713,10 +1733,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505465</v>
+        <v>505380</v>
       </c>
       <c r="R10" t="n">
-        <v>6666072</v>
+        <v>6666036</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1748,7 +1768,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1758,7 +1778,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1770,26 +1790,6 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -3052,44 +3052,36 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127296043</v>
+        <v>127297420</v>
       </c>
       <c r="B21" t="n">
-        <v>98443</v>
+        <v>96696</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -3099,10 +3091,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>505457</v>
+        <v>505483</v>
       </c>
       <c r="R21" t="n">
-        <v>6666067</v>
+        <v>6666164</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3134,7 +3126,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3144,7 +3136,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3156,6 +3148,26 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3172,46 +3184,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295317</v>
+        <v>127297958</v>
       </c>
       <c r="B22" t="n">
-        <v>98443</v>
+        <v>75130</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3219,10 +3222,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>505401</v>
+        <v>505525</v>
       </c>
       <c r="R22" t="n">
-        <v>6666036</v>
+        <v>6666131</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3254,7 +3257,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3264,7 +3267,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3276,6 +3279,26 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3292,36 +3315,44 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127297420</v>
+        <v>127296043</v>
       </c>
       <c r="B23" t="n">
-        <v>96696</v>
+        <v>98443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -3331,10 +3362,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>505483</v>
+        <v>505457</v>
       </c>
       <c r="R23" t="n">
-        <v>6666164</v>
+        <v>6666067</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3366,7 +3397,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3376,7 +3407,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3388,26 +3419,6 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3424,37 +3435,46 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127297958</v>
+        <v>127295317</v>
       </c>
       <c r="B24" t="n">
-        <v>75130</v>
+        <v>98443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3462,10 +3482,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505525</v>
+        <v>505401</v>
       </c>
       <c r="R24" t="n">
-        <v>6666131</v>
+        <v>6666036</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3497,7 +3517,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3507,7 +3527,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3519,26 +3539,6 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3555,49 +3555,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127298417</v>
+        <v>127295207</v>
       </c>
       <c r="B25" t="n">
-        <v>98360</v>
+        <v>98443</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3606,10 +3602,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>505547</v>
+        <v>505383</v>
       </c>
       <c r="R25" t="n">
-        <v>6666020</v>
+        <v>6666039</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3641,7 +3637,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3651,7 +3647,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3679,7 +3675,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127295207</v>
+        <v>127294423</v>
       </c>
       <c r="B26" t="n">
         <v>98443</v>
@@ -3709,7 +3705,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3726,10 +3722,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>505383</v>
+        <v>505296</v>
       </c>
       <c r="R26" t="n">
-        <v>6666039</v>
+        <v>6666023</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3761,7 +3757,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3771,7 +3767,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3799,7 +3795,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127294423</v>
+        <v>127295681</v>
       </c>
       <c r="B27" t="n">
         <v>98443</v>
@@ -3829,7 +3825,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3846,10 +3842,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>505296</v>
+        <v>505425</v>
       </c>
       <c r="R27" t="n">
-        <v>6666023</v>
+        <v>6666033</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3881,7 +3877,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3891,7 +3887,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3919,45 +3915,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127295681</v>
+        <v>127298417</v>
       </c>
       <c r="B28" t="n">
-        <v>98443</v>
+        <v>98360</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>505425</v>
+        <v>505547</v>
       </c>
       <c r="R28" t="n">
-        <v>6666033</v>
+        <v>6666020</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4039,10 +4039,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127298321</v>
+        <v>127296321</v>
       </c>
       <c r="B29" t="n">
-        <v>79632</v>
+        <v>79046</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4050,21 +4050,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4077,10 +4077,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>505552</v>
+        <v>505487</v>
       </c>
       <c r="R29" t="n">
-        <v>6666024</v>
+        <v>6666090</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4137,22 +4137,22 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stump # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4170,10 +4170,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127296321</v>
+        <v>127297555</v>
       </c>
       <c r="B30" t="n">
-        <v>79046</v>
+        <v>75130</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4181,21 +4181,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>505487</v>
+        <v>505501</v>
       </c>
       <c r="R30" t="n">
-        <v>6666090</v>
+        <v>6666172</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4268,22 +4268,22 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4301,10 +4301,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127297555</v>
+        <v>127298321</v>
       </c>
       <c r="B31" t="n">
-        <v>75130</v>
+        <v>79632</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4312,21 +4312,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>308</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4339,10 +4339,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>505501</v>
+        <v>505552</v>
       </c>
       <c r="R31" t="n">
-        <v>6666172</v>
+        <v>6666024</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Stump # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4923,37 +4923,46 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127296758</v>
+        <v>127294976</v>
       </c>
       <c r="B36" t="n">
-        <v>78420</v>
+        <v>98443</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4961,10 +4970,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>505486</v>
+        <v>505373</v>
       </c>
       <c r="R36" t="n">
-        <v>6666108</v>
+        <v>6666042</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4996,7 +5005,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5006,7 +5015,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5018,26 +5027,6 @@
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5054,46 +5043,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127294976</v>
+        <v>127296758</v>
       </c>
       <c r="B37" t="n">
-        <v>98443</v>
+        <v>78420</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5101,10 +5081,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>505373</v>
+        <v>505486</v>
       </c>
       <c r="R37" t="n">
-        <v>6666042</v>
+        <v>6666108</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5136,7 +5116,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5146,7 +5126,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5158,6 +5138,26 @@
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">

--- a/artfynd/A 32085-2025 artfynd.xlsx
+++ b/artfynd/A 32085-2025 artfynd.xlsx
@@ -812,46 +812,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127295076</v>
+        <v>127297595</v>
       </c>
       <c r="B3" t="n">
-        <v>98443</v>
+        <v>75130</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -859,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505375</v>
+        <v>505508</v>
       </c>
       <c r="R3" t="n">
-        <v>6666039</v>
+        <v>6666170</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +895,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,6 +907,26 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -932,37 +943,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127297595</v>
+        <v>127295076</v>
       </c>
       <c r="B4" t="n">
-        <v>75130</v>
+        <v>98443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -970,10 +990,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505508</v>
+        <v>505375</v>
       </c>
       <c r="R4" t="n">
-        <v>6666170</v>
+        <v>6666039</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,7 +1025,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1015,7 +1035,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,26 +1047,6 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1446,7 +1446,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127295345</v>
+        <v>127295189</v>
       </c>
       <c r="B8" t="n">
         <v>98443</v>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505402</v>
+        <v>505380</v>
       </c>
       <c r="R8" t="n">
-        <v>6666038</v>
+        <v>6666036</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1686,7 +1686,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127295189</v>
+        <v>127295345</v>
       </c>
       <c r="B10" t="n">
         <v>98443</v>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505380</v>
+        <v>505402</v>
       </c>
       <c r="R10" t="n">
-        <v>6666036</v>
+        <v>6666038</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2058,7 +2058,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127294748</v>
+        <v>127295061</v>
       </c>
       <c r="B13" t="n">
         <v>98443</v>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505318</v>
+        <v>505372</v>
       </c>
       <c r="R13" t="n">
-        <v>6666032</v>
+        <v>6666038</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2178,7 +2178,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127295061</v>
+        <v>127294748</v>
       </c>
       <c r="B14" t="n">
         <v>98443</v>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2225,10 +2225,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505372</v>
+        <v>505318</v>
       </c>
       <c r="R14" t="n">
-        <v>6666038</v>
+        <v>6666032</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2418,46 +2418,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127295297</v>
+        <v>127297615</v>
       </c>
       <c r="B16" t="n">
-        <v>98443</v>
+        <v>75130</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2465,10 +2456,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505400</v>
+        <v>505511</v>
       </c>
       <c r="R16" t="n">
-        <v>6666034</v>
+        <v>6666168</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2500,7 +2491,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2510,7 +2501,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2522,6 +2513,26 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2538,44 +2549,36 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127296113</v>
+        <v>127297651</v>
       </c>
       <c r="B17" t="n">
-        <v>98443</v>
+        <v>96696</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2585,10 +2588,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505461</v>
+        <v>505512</v>
       </c>
       <c r="R17" t="n">
-        <v>6666073</v>
+        <v>6666168</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2620,7 +2623,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2630,7 +2633,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2642,6 +2645,26 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2658,37 +2681,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127297615</v>
+        <v>127295297</v>
       </c>
       <c r="B18" t="n">
-        <v>75130</v>
+        <v>98443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2696,10 +2728,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505511</v>
+        <v>505400</v>
       </c>
       <c r="R18" t="n">
-        <v>6666168</v>
+        <v>6666034</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2731,7 +2763,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2741,7 +2773,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2753,26 +2785,6 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2789,36 +2801,44 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127297651</v>
+        <v>127296113</v>
       </c>
       <c r="B19" t="n">
-        <v>96696</v>
+        <v>98443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2828,10 +2848,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>505512</v>
+        <v>505461</v>
       </c>
       <c r="R19" t="n">
-        <v>6666168</v>
+        <v>6666073</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2863,7 +2883,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2873,7 +2893,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2885,26 +2905,6 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3052,36 +3052,44 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127297420</v>
+        <v>127296043</v>
       </c>
       <c r="B21" t="n">
-        <v>96696</v>
+        <v>98443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -3091,10 +3099,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>505483</v>
+        <v>505457</v>
       </c>
       <c r="R21" t="n">
-        <v>6666164</v>
+        <v>6666067</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3126,7 +3134,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3136,7 +3144,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3148,26 +3156,6 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3184,37 +3172,46 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127297958</v>
+        <v>127295317</v>
       </c>
       <c r="B22" t="n">
-        <v>75130</v>
+        <v>98443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3222,10 +3219,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>505525</v>
+        <v>505401</v>
       </c>
       <c r="R22" t="n">
-        <v>6666131</v>
+        <v>6666036</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3257,7 +3254,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3267,7 +3264,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3279,26 +3276,6 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3315,44 +3292,36 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127296043</v>
+        <v>127297420</v>
       </c>
       <c r="B23" t="n">
-        <v>98443</v>
+        <v>96696</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -3362,10 +3331,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>505457</v>
+        <v>505483</v>
       </c>
       <c r="R23" t="n">
-        <v>6666067</v>
+        <v>6666164</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3397,7 +3366,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3407,7 +3376,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3419,6 +3388,26 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3435,46 +3424,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295317</v>
+        <v>127297958</v>
       </c>
       <c r="B24" t="n">
-        <v>98443</v>
+        <v>75130</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3482,10 +3462,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505401</v>
+        <v>505525</v>
       </c>
       <c r="R24" t="n">
-        <v>6666036</v>
+        <v>6666131</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3517,7 +3497,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3527,7 +3507,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3539,6 +3519,26 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3555,45 +3555,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295207</v>
+        <v>127298417</v>
       </c>
       <c r="B25" t="n">
-        <v>98443</v>
+        <v>98360</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3602,10 +3606,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>505383</v>
+        <v>505547</v>
       </c>
       <c r="R25" t="n">
-        <v>6666039</v>
+        <v>6666020</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3637,7 +3641,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3647,7 +3651,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3915,49 +3919,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127298417</v>
+        <v>127295207</v>
       </c>
       <c r="B28" t="n">
-        <v>98360</v>
+        <v>98443</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>505547</v>
+        <v>505383</v>
       </c>
       <c r="R28" t="n">
-        <v>6666020</v>
+        <v>6666039</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4923,46 +4923,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127294976</v>
+        <v>127296758</v>
       </c>
       <c r="B36" t="n">
-        <v>98443</v>
+        <v>78420</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4970,10 +4961,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>505373</v>
+        <v>505486</v>
       </c>
       <c r="R36" t="n">
-        <v>6666042</v>
+        <v>6666108</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5005,7 +4996,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5015,7 +5006,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5027,6 +5018,26 @@
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5043,37 +5054,46 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127296758</v>
+        <v>127294976</v>
       </c>
       <c r="B37" t="n">
-        <v>78420</v>
+        <v>98443</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5081,10 +5101,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>505486</v>
+        <v>505373</v>
       </c>
       <c r="R37" t="n">
-        <v>6666108</v>
+        <v>6666042</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5116,7 +5136,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5126,7 +5146,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5138,26 +5158,6 @@
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5174,44 +5174,36 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127295841</v>
+        <v>127297810</v>
       </c>
       <c r="B38" t="n">
-        <v>98443</v>
+        <v>96696</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -5221,10 +5213,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>505457</v>
+        <v>505515</v>
       </c>
       <c r="R38" t="n">
-        <v>6666062</v>
+        <v>6666146</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5256,7 +5248,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5266,7 +5258,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5278,6 +5270,26 @@
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5294,7 +5306,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127294730</v>
+        <v>127295841</v>
       </c>
       <c r="B39" t="n">
         <v>98443</v>
@@ -5324,7 +5336,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5341,10 +5353,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>505313</v>
+        <v>505457</v>
       </c>
       <c r="R39" t="n">
-        <v>6666027</v>
+        <v>6666062</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5376,7 +5388,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5386,7 +5398,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5414,36 +5426,44 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127297810</v>
+        <v>127294730</v>
       </c>
       <c r="B40" t="n">
-        <v>96696</v>
+        <v>98443</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
@@ -5453,10 +5473,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>505515</v>
+        <v>505313</v>
       </c>
       <c r="R40" t="n">
-        <v>6666146</v>
+        <v>6666027</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5488,7 +5508,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5498,7 +5518,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5510,26 +5530,6 @@
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5815,36 +5815,44 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127301907</v>
+        <v>127295399</v>
       </c>
       <c r="B43" t="n">
-        <v>96791</v>
+        <v>98443</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1841</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
@@ -5854,10 +5862,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>505491</v>
+        <v>505404</v>
       </c>
       <c r="R43" t="n">
-        <v>6666106</v>
+        <v>6666039</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5887,9 +5895,19 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5901,26 +5919,6 @@
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5937,44 +5935,36 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127295399</v>
+        <v>127301907</v>
       </c>
       <c r="B44" t="n">
-        <v>98443</v>
+        <v>96791</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1841</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
@@ -5984,10 +5974,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>505404</v>
+        <v>505491</v>
       </c>
       <c r="R44" t="n">
-        <v>6666039</v>
+        <v>6666106</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6017,19 +6007,9 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>15:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6041,6 +6021,26 @@
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6057,46 +6057,37 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127295238</v>
+        <v>127298146</v>
       </c>
       <c r="B45" t="n">
-        <v>98443</v>
+        <v>91346</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6104,10 +6095,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>505388</v>
+        <v>505544</v>
       </c>
       <c r="R45" t="n">
-        <v>6666037</v>
+        <v>6666053</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6139,7 +6130,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6149,7 +6140,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6161,6 +6152,21 @@
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6297,37 +6303,46 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127298146</v>
+        <v>127295238</v>
       </c>
       <c r="B47" t="n">
-        <v>91346</v>
+        <v>98443</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6335,10 +6350,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>505544</v>
+        <v>505388</v>
       </c>
       <c r="R47" t="n">
-        <v>6666053</v>
+        <v>6666037</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6370,7 +6385,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6380,7 +6395,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6392,21 +6407,6 @@
       <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6423,32 +6423,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127296862</v>
+        <v>127297221</v>
       </c>
       <c r="B48" t="n">
-        <v>79046</v>
+        <v>75121</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>6439</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6464,7 +6464,7 @@
         <v>505478</v>
       </c>
       <c r="R48" t="n">
-        <v>6666105</v>
+        <v>6666109</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6521,22 +6521,22 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6554,32 +6554,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127297221</v>
+        <v>127296862</v>
       </c>
       <c r="B49" t="n">
-        <v>75121</v>
+        <v>79046</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6439</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6595,7 +6595,7 @@
         <v>505478</v>
       </c>
       <c r="R49" t="n">
-        <v>6666109</v>
+        <v>6666105</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6652,22 +6652,22 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>

--- a/artfynd/A 32085-2025 artfynd.xlsx
+++ b/artfynd/A 32085-2025 artfynd.xlsx
@@ -1806,36 +1806,44 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127297697</v>
+        <v>127294550</v>
       </c>
       <c r="B11" t="n">
-        <v>96696</v>
+        <v>98443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1845,10 +1853,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505514</v>
+        <v>505307</v>
       </c>
       <c r="R11" t="n">
-        <v>6666167</v>
+        <v>6666031</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1880,7 +1888,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1890,7 +1898,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1902,26 +1910,6 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1938,7 +1926,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127294550</v>
+        <v>127295061</v>
       </c>
       <c r="B12" t="n">
         <v>98443</v>
@@ -1968,7 +1956,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1985,10 +1973,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505307</v>
+        <v>505372</v>
       </c>
       <c r="R12" t="n">
-        <v>6666031</v>
+        <v>6666038</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2020,7 +2008,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2030,7 +2018,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2058,7 +2046,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127295061</v>
+        <v>127294748</v>
       </c>
       <c r="B13" t="n">
         <v>98443</v>
@@ -2088,7 +2076,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2105,10 +2093,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505372</v>
+        <v>505318</v>
       </c>
       <c r="R13" t="n">
-        <v>6666038</v>
+        <v>6666032</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2140,7 +2128,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2150,7 +2138,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2178,44 +2166,36 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127294748</v>
+        <v>127297697</v>
       </c>
       <c r="B14" t="n">
-        <v>98443</v>
+        <v>96696</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2225,10 +2205,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505318</v>
+        <v>505514</v>
       </c>
       <c r="R14" t="n">
-        <v>6666032</v>
+        <v>6666167</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2260,7 +2240,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2270,7 +2250,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2282,6 +2262,26 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -3052,44 +3052,36 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127296043</v>
+        <v>127297420</v>
       </c>
       <c r="B21" t="n">
-        <v>98443</v>
+        <v>96696</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -3099,10 +3091,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>505457</v>
+        <v>505483</v>
       </c>
       <c r="R21" t="n">
-        <v>6666067</v>
+        <v>6666164</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3134,7 +3126,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3144,7 +3136,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3156,6 +3148,26 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3172,46 +3184,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295317</v>
+        <v>127297958</v>
       </c>
       <c r="B22" t="n">
-        <v>98443</v>
+        <v>75130</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3219,10 +3222,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>505401</v>
+        <v>505525</v>
       </c>
       <c r="R22" t="n">
-        <v>6666036</v>
+        <v>6666131</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3254,7 +3257,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3264,7 +3267,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3276,6 +3279,26 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3292,36 +3315,44 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127297420</v>
+        <v>127296043</v>
       </c>
       <c r="B23" t="n">
-        <v>96696</v>
+        <v>98443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -3331,10 +3362,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>505483</v>
+        <v>505457</v>
       </c>
       <c r="R23" t="n">
-        <v>6666164</v>
+        <v>6666067</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3366,7 +3397,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3376,7 +3407,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3388,26 +3419,6 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3424,37 +3435,46 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127297958</v>
+        <v>127295317</v>
       </c>
       <c r="B24" t="n">
-        <v>75130</v>
+        <v>98443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3462,10 +3482,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505525</v>
+        <v>505401</v>
       </c>
       <c r="R24" t="n">
-        <v>6666131</v>
+        <v>6666036</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3497,7 +3517,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3507,7 +3527,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3519,26 +3539,6 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -5174,36 +5174,44 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127297810</v>
+        <v>127295841</v>
       </c>
       <c r="B38" t="n">
-        <v>96696</v>
+        <v>98443</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -5213,10 +5221,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>505515</v>
+        <v>505457</v>
       </c>
       <c r="R38" t="n">
-        <v>6666146</v>
+        <v>6666062</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5248,7 +5256,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5258,7 +5266,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5270,26 +5278,6 @@
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5306,7 +5294,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127295841</v>
+        <v>127294730</v>
       </c>
       <c r="B39" t="n">
         <v>98443</v>
@@ -5336,7 +5324,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5353,10 +5341,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>505457</v>
+        <v>505313</v>
       </c>
       <c r="R39" t="n">
-        <v>6666062</v>
+        <v>6666027</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5388,7 +5376,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5398,7 +5386,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5426,44 +5414,36 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127294730</v>
+        <v>127297810</v>
       </c>
       <c r="B40" t="n">
-        <v>98443</v>
+        <v>96696</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
@@ -5473,10 +5453,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>505313</v>
+        <v>505515</v>
       </c>
       <c r="R40" t="n">
-        <v>6666027</v>
+        <v>6666146</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5508,7 +5488,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5518,7 +5498,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5530,6 +5510,26 @@
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">

--- a/artfynd/A 32085-2025 artfynd.xlsx
+++ b/artfynd/A 32085-2025 artfynd.xlsx
@@ -1314,36 +1314,44 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127296163</v>
+        <v>127295189</v>
       </c>
       <c r="B7" t="n">
-        <v>96696</v>
+        <v>98443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1353,10 +1361,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505465</v>
+        <v>505380</v>
       </c>
       <c r="R7" t="n">
-        <v>6666072</v>
+        <v>6666036</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1388,7 +1396,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1398,7 +1406,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1410,26 +1418,6 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1446,7 +1434,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127295189</v>
+        <v>127294826</v>
       </c>
       <c r="B8" t="n">
         <v>98443</v>
@@ -1476,7 +1464,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1493,10 +1481,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505380</v>
+        <v>505332</v>
       </c>
       <c r="R8" t="n">
-        <v>6666036</v>
+        <v>6666037</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1528,7 +1516,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1538,7 +1526,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1566,7 +1554,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127294826</v>
+        <v>127295345</v>
       </c>
       <c r="B9" t="n">
         <v>98443</v>
@@ -1596,7 +1584,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1613,10 +1601,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505332</v>
+        <v>505402</v>
       </c>
       <c r="R9" t="n">
-        <v>6666037</v>
+        <v>6666038</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1648,7 +1636,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1658,7 +1646,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1686,44 +1674,36 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127295345</v>
+        <v>127296163</v>
       </c>
       <c r="B10" t="n">
-        <v>98443</v>
+        <v>96696</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1733,10 +1713,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505402</v>
+        <v>505465</v>
       </c>
       <c r="R10" t="n">
-        <v>6666038</v>
+        <v>6666072</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1768,7 +1748,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1778,7 +1758,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1790,6 +1770,26 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -2418,37 +2418,46 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127297615</v>
+        <v>127295297</v>
       </c>
       <c r="B16" t="n">
-        <v>75130</v>
+        <v>98443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2456,10 +2465,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505511</v>
+        <v>505400</v>
       </c>
       <c r="R16" t="n">
-        <v>6666168</v>
+        <v>6666034</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2491,7 +2500,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2501,7 +2510,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2513,26 +2522,6 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2549,36 +2538,44 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127297651</v>
+        <v>127296113</v>
       </c>
       <c r="B17" t="n">
-        <v>96696</v>
+        <v>98443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2588,10 +2585,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505512</v>
+        <v>505461</v>
       </c>
       <c r="R17" t="n">
-        <v>6666168</v>
+        <v>6666073</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2623,7 +2620,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2633,7 +2630,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2645,26 +2642,6 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2681,46 +2658,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127295297</v>
+        <v>127297615</v>
       </c>
       <c r="B18" t="n">
-        <v>98443</v>
+        <v>75130</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2728,10 +2696,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505400</v>
+        <v>505511</v>
       </c>
       <c r="R18" t="n">
-        <v>6666034</v>
+        <v>6666168</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2763,7 +2731,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2773,7 +2741,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2785,6 +2753,26 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2801,44 +2789,36 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127296113</v>
+        <v>127297651</v>
       </c>
       <c r="B19" t="n">
-        <v>98443</v>
+        <v>96696</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2848,10 +2828,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>505461</v>
+        <v>505512</v>
       </c>
       <c r="R19" t="n">
-        <v>6666073</v>
+        <v>6666168</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2883,7 +2863,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2893,7 +2873,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2905,6 +2885,26 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -4039,37 +4039,46 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127296321</v>
+        <v>127294722</v>
       </c>
       <c r="B29" t="n">
-        <v>79046</v>
+        <v>98443</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4077,10 +4086,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>505487</v>
+        <v>505312</v>
       </c>
       <c r="R29" t="n">
-        <v>6666090</v>
+        <v>6666032</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4112,7 +4121,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4122,7 +4131,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4134,26 +4143,6 @@
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4170,10 +4159,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127297555</v>
+        <v>127296321</v>
       </c>
       <c r="B30" t="n">
-        <v>75130</v>
+        <v>79046</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4181,21 +4170,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>308</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4208,10 +4197,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>505501</v>
+        <v>505487</v>
       </c>
       <c r="R30" t="n">
-        <v>6666172</v>
+        <v>6666090</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4243,7 +4232,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4253,7 +4242,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4268,22 +4257,22 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4301,10 +4290,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127298321</v>
+        <v>127297555</v>
       </c>
       <c r="B31" t="n">
-        <v>79632</v>
+        <v>75130</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4312,21 +4301,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4339,10 +4328,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>505552</v>
+        <v>505501</v>
       </c>
       <c r="R31" t="n">
-        <v>6666024</v>
+        <v>6666172</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4374,7 +4363,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4384,7 +4373,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4409,12 +4398,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stump # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4432,46 +4421,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127294722</v>
+        <v>127298321</v>
       </c>
       <c r="B32" t="n">
-        <v>98443</v>
+        <v>79632</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4479,10 +4459,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>505312</v>
+        <v>505552</v>
       </c>
       <c r="R32" t="n">
-        <v>6666032</v>
+        <v>6666024</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4514,7 +4494,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4524,7 +4504,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4536,6 +4516,26 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stump # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -6554,37 +6554,46 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127296862</v>
+        <v>127296142</v>
       </c>
       <c r="B49" t="n">
-        <v>79046</v>
+        <v>98443</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6592,10 +6601,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>505478</v>
+        <v>505465</v>
       </c>
       <c r="R49" t="n">
-        <v>6666105</v>
+        <v>6666072</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6627,7 +6636,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6637,7 +6646,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6649,26 +6658,6 @@
       <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6685,46 +6674,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127296142</v>
+        <v>127296862</v>
       </c>
       <c r="B50" t="n">
-        <v>98443</v>
+        <v>79046</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6732,10 +6712,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>505465</v>
+        <v>505478</v>
       </c>
       <c r="R50" t="n">
-        <v>6666072</v>
+        <v>6666105</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6767,7 +6747,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6777,7 +6757,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6789,6 +6769,26 @@
       <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 32085-2025 artfynd.xlsx
+++ b/artfynd/A 32085-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127298150</v>
       </c>
       <c r="B2" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -812,37 +812,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127297595</v>
+        <v>127295076</v>
       </c>
       <c r="B3" t="n">
-        <v>75130</v>
+        <v>98447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -850,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505508</v>
+        <v>505375</v>
       </c>
       <c r="R3" t="n">
-        <v>6666170</v>
+        <v>6666039</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,26 +916,6 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -943,46 +932,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127295076</v>
+        <v>127297595</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>75134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -990,10 +970,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505375</v>
+        <v>505508</v>
       </c>
       <c r="R4" t="n">
-        <v>6666039</v>
+        <v>6666170</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1025,7 +1005,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1035,7 +1015,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,6 +1027,26 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1063,38 +1063,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127294425</v>
+        <v>127296095</v>
       </c>
       <c r="B5" t="n">
-        <v>97321</v>
+        <v>79050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1102,10 +1109,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505296</v>
+        <v>505457</v>
       </c>
       <c r="R5" t="n">
-        <v>6666023</v>
+        <v>6666067</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1137,7 +1144,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1147,7 +1154,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,6 +1166,26 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Dead branch  # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1175,45 +1202,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127296095</v>
+        <v>127294425</v>
       </c>
       <c r="B6" t="n">
-        <v>79046</v>
+        <v>97325</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1221,10 +1241,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505457</v>
+        <v>505296</v>
       </c>
       <c r="R6" t="n">
-        <v>6666067</v>
+        <v>6666023</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,7 +1276,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1266,7 +1286,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,26 +1298,6 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Dead branch  # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1314,44 +1314,36 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127295189</v>
+        <v>127296163</v>
       </c>
       <c r="B7" t="n">
-        <v>98443</v>
+        <v>96700</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1361,10 +1353,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505380</v>
+        <v>505465</v>
       </c>
       <c r="R7" t="n">
-        <v>6666036</v>
+        <v>6666072</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1396,7 +1388,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1406,7 +1398,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1418,6 +1410,26 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1434,10 +1446,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127294826</v>
+        <v>127295189</v>
       </c>
       <c r="B8" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1464,7 +1476,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1481,10 +1493,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505332</v>
+        <v>505380</v>
       </c>
       <c r="R8" t="n">
-        <v>6666037</v>
+        <v>6666036</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1516,7 +1528,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1526,7 +1538,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1554,10 +1566,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127295345</v>
+        <v>127294826</v>
       </c>
       <c r="B9" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1596,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1601,10 +1613,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505402</v>
+        <v>505332</v>
       </c>
       <c r="R9" t="n">
-        <v>6666038</v>
+        <v>6666037</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1636,7 +1648,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1646,7 +1658,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1674,36 +1686,44 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127296163</v>
+        <v>127295345</v>
       </c>
       <c r="B10" t="n">
-        <v>96696</v>
+        <v>98447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1713,10 +1733,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505465</v>
+        <v>505402</v>
       </c>
       <c r="R10" t="n">
-        <v>6666072</v>
+        <v>6666038</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1748,7 +1768,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1758,7 +1778,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1770,26 +1790,6 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1806,44 +1806,36 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127294550</v>
+        <v>127297697</v>
       </c>
       <c r="B11" t="n">
-        <v>98443</v>
+        <v>96700</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1853,10 +1845,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505307</v>
+        <v>505514</v>
       </c>
       <c r="R11" t="n">
-        <v>6666031</v>
+        <v>6666167</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1888,7 +1880,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1898,7 +1890,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1910,6 +1902,26 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1926,10 +1938,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127295061</v>
+        <v>127294550</v>
       </c>
       <c r="B12" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1956,7 +1968,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1973,10 +1985,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505372</v>
+        <v>505307</v>
       </c>
       <c r="R12" t="n">
-        <v>6666038</v>
+        <v>6666031</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2008,7 +2020,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2018,7 +2030,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2046,10 +2058,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127294748</v>
+        <v>127295061</v>
       </c>
       <c r="B13" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2076,7 +2088,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2093,10 +2105,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505318</v>
+        <v>505372</v>
       </c>
       <c r="R13" t="n">
-        <v>6666032</v>
+        <v>6666038</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2128,7 +2140,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2138,7 +2150,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2166,36 +2178,44 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127297697</v>
+        <v>127294748</v>
       </c>
       <c r="B14" t="n">
-        <v>96696</v>
+        <v>98447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2205,10 +2225,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505514</v>
+        <v>505318</v>
       </c>
       <c r="R14" t="n">
-        <v>6666167</v>
+        <v>6666032</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2240,7 +2260,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2250,7 +2270,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2262,26 +2282,6 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2301,7 +2301,7 @@
         <v>127295213</v>
       </c>
       <c r="B15" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2418,46 +2418,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127295297</v>
+        <v>127297615</v>
       </c>
       <c r="B16" t="n">
-        <v>98443</v>
+        <v>75134</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2465,10 +2456,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505400</v>
+        <v>505511</v>
       </c>
       <c r="R16" t="n">
-        <v>6666034</v>
+        <v>6666168</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2500,7 +2491,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2510,7 +2501,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2522,6 +2513,26 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2538,44 +2549,36 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127296113</v>
+        <v>127297651</v>
       </c>
       <c r="B17" t="n">
-        <v>98443</v>
+        <v>96700</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2585,10 +2588,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505461</v>
+        <v>505512</v>
       </c>
       <c r="R17" t="n">
-        <v>6666073</v>
+        <v>6666168</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2620,7 +2623,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2630,7 +2633,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2642,6 +2645,26 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2658,37 +2681,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127297615</v>
+        <v>127295297</v>
       </c>
       <c r="B18" t="n">
-        <v>75130</v>
+        <v>98447</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2696,10 +2728,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505511</v>
+        <v>505400</v>
       </c>
       <c r="R18" t="n">
-        <v>6666168</v>
+        <v>6666034</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2731,7 +2763,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2741,7 +2773,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2753,26 +2785,6 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2789,36 +2801,44 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127297651</v>
+        <v>127296113</v>
       </c>
       <c r="B19" t="n">
-        <v>96696</v>
+        <v>98447</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2828,10 +2848,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>505512</v>
+        <v>505461</v>
       </c>
       <c r="R19" t="n">
-        <v>6666168</v>
+        <v>6666073</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2863,7 +2883,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2873,7 +2893,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2885,26 +2905,6 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2924,7 +2924,7 @@
         <v>127295662</v>
       </c>
       <c r="B20" t="n">
-        <v>75130</v>
+        <v>75134</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3052,36 +3052,44 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127297420</v>
+        <v>127296043</v>
       </c>
       <c r="B21" t="n">
-        <v>96696</v>
+        <v>98447</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -3091,10 +3099,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>505483</v>
+        <v>505457</v>
       </c>
       <c r="R21" t="n">
-        <v>6666164</v>
+        <v>6666067</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3126,7 +3134,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3136,7 +3144,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3148,26 +3156,6 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3184,37 +3172,46 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127297958</v>
+        <v>127295317</v>
       </c>
       <c r="B22" t="n">
-        <v>75130</v>
+        <v>98447</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3222,10 +3219,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>505525</v>
+        <v>505401</v>
       </c>
       <c r="R22" t="n">
-        <v>6666131</v>
+        <v>6666036</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3257,7 +3254,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3267,7 +3264,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3279,26 +3276,6 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3315,44 +3292,36 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127296043</v>
+        <v>127297420</v>
       </c>
       <c r="B23" t="n">
-        <v>98443</v>
+        <v>96700</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -3362,10 +3331,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>505457</v>
+        <v>505483</v>
       </c>
       <c r="R23" t="n">
-        <v>6666067</v>
+        <v>6666164</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3397,7 +3366,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3407,7 +3376,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3419,6 +3388,26 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3435,46 +3424,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295317</v>
+        <v>127297958</v>
       </c>
       <c r="B24" t="n">
-        <v>98443</v>
+        <v>75134</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3482,10 +3462,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505401</v>
+        <v>505525</v>
       </c>
       <c r="R24" t="n">
-        <v>6666036</v>
+        <v>6666131</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3517,7 +3497,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3527,7 +3507,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3539,6 +3519,26 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3558,7 +3558,7 @@
         <v>127298417</v>
       </c>
       <c r="B25" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>127294423</v>
       </c>
       <c r="B26" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>127295681</v>
       </c>
       <c r="B27" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>127295207</v>
       </c>
       <c r="B28" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4039,46 +4039,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127294722</v>
+        <v>127296321</v>
       </c>
       <c r="B29" t="n">
-        <v>98443</v>
+        <v>79050</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4086,10 +4077,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>505312</v>
+        <v>505487</v>
       </c>
       <c r="R29" t="n">
-        <v>6666032</v>
+        <v>6666090</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4121,7 +4112,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4131,7 +4122,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4143,6 +4134,26 @@
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4159,10 +4170,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127296321</v>
+        <v>127297555</v>
       </c>
       <c r="B30" t="n">
-        <v>79046</v>
+        <v>75134</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4170,21 +4181,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4197,10 +4208,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>505487</v>
+        <v>505501</v>
       </c>
       <c r="R30" t="n">
-        <v>6666090</v>
+        <v>6666172</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4232,7 +4243,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4242,7 +4253,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4257,22 +4268,22 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4290,10 +4301,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127297555</v>
+        <v>127298321</v>
       </c>
       <c r="B31" t="n">
-        <v>75130</v>
+        <v>79636</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4301,21 +4312,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>308</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4328,10 +4339,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>505501</v>
+        <v>505552</v>
       </c>
       <c r="R31" t="n">
-        <v>6666172</v>
+        <v>6666024</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4363,7 +4374,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4373,7 +4384,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4398,12 +4409,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Stump # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4421,37 +4432,46 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127298321</v>
+        <v>127294722</v>
       </c>
       <c r="B32" t="n">
-        <v>79632</v>
+        <v>98447</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4459,10 +4479,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>505552</v>
+        <v>505312</v>
       </c>
       <c r="R32" t="n">
-        <v>6666024</v>
+        <v>6666032</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4494,7 +4514,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4504,7 +4524,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4516,26 +4536,6 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Stump # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4555,7 +4555,7 @@
         <v>127295731</v>
       </c>
       <c r="B33" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>127294455</v>
       </c>
       <c r="B34" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>127298053</v>
       </c>
       <c r="B35" t="n">
-        <v>78420</v>
+        <v>78424</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>127296758</v>
       </c>
       <c r="B36" t="n">
-        <v>78420</v>
+        <v>78424</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         <v>127294976</v>
       </c>
       <c r="B37" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5174,44 +5174,36 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127295841</v>
+        <v>127297810</v>
       </c>
       <c r="B38" t="n">
-        <v>98443</v>
+        <v>96700</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -5221,10 +5213,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>505457</v>
+        <v>505515</v>
       </c>
       <c r="R38" t="n">
-        <v>6666062</v>
+        <v>6666146</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5256,7 +5248,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5266,7 +5258,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5278,6 +5270,26 @@
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5294,10 +5306,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127294730</v>
+        <v>127295841</v>
       </c>
       <c r="B39" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5324,7 +5336,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5341,10 +5353,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>505313</v>
+        <v>505457</v>
       </c>
       <c r="R39" t="n">
-        <v>6666027</v>
+        <v>6666062</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5376,7 +5388,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5386,7 +5398,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5414,36 +5426,44 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127297810</v>
+        <v>127294730</v>
       </c>
       <c r="B40" t="n">
-        <v>96696</v>
+        <v>98447</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
@@ -5453,10 +5473,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>505515</v>
+        <v>505313</v>
       </c>
       <c r="R40" t="n">
-        <v>6666146</v>
+        <v>6666027</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5488,7 +5508,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5498,7 +5518,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5510,26 +5530,6 @@
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5549,7 +5549,7 @@
         <v>127295873</v>
       </c>
       <c r="B41" t="n">
-        <v>96696</v>
+        <v>96700</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         <v>127294173</v>
       </c>
       <c r="B42" t="n">
-        <v>4772</v>
+        <v>4773</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>127295399</v>
       </c>
       <c r="B43" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
         <v>127301907</v>
       </c>
       <c r="B44" t="n">
-        <v>96791</v>
+        <v>96795</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6057,37 +6057,46 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127298146</v>
+        <v>127295179</v>
       </c>
       <c r="B45" t="n">
-        <v>91346</v>
+        <v>98447</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6095,10 +6104,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>505544</v>
+        <v>505378</v>
       </c>
       <c r="R45" t="n">
-        <v>6666053</v>
+        <v>6666040</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6130,7 +6139,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6140,7 +6149,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6152,21 +6161,6 @@
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6183,10 +6177,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127295179</v>
+        <v>127295238</v>
       </c>
       <c r="B46" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6213,7 +6207,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6230,10 +6224,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>505378</v>
+        <v>505388</v>
       </c>
       <c r="R46" t="n">
-        <v>6666040</v>
+        <v>6666037</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6265,7 +6259,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6275,7 +6269,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6303,46 +6297,37 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127295238</v>
+        <v>127298146</v>
       </c>
       <c r="B47" t="n">
-        <v>98443</v>
+        <v>91350</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6350,10 +6335,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>505388</v>
+        <v>505544</v>
       </c>
       <c r="R47" t="n">
-        <v>6666037</v>
+        <v>6666053</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6385,7 +6370,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6395,7 +6380,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6407,6 +6392,21 @@
       <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6423,37 +6423,46 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127297221</v>
+        <v>127296142</v>
       </c>
       <c r="B48" t="n">
-        <v>75121</v>
+        <v>98447</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6439</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6461,10 +6470,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>505478</v>
+        <v>505465</v>
       </c>
       <c r="R48" t="n">
-        <v>6666109</v>
+        <v>6666072</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6496,7 +6505,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6506,7 +6515,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6518,26 +6527,6 @@
       <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6554,46 +6543,37 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127296142</v>
+        <v>127296862</v>
       </c>
       <c r="B49" t="n">
-        <v>98443</v>
+        <v>79050</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6601,10 +6581,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>505465</v>
+        <v>505478</v>
       </c>
       <c r="R49" t="n">
-        <v>6666072</v>
+        <v>6666105</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6636,7 +6616,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6646,7 +6626,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6658,6 +6638,26 @@
       <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6674,32 +6674,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127296862</v>
+        <v>127297221</v>
       </c>
       <c r="B50" t="n">
-        <v>79046</v>
+        <v>75125</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>6439</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6715,7 +6715,7 @@
         <v>505478</v>
       </c>
       <c r="R50" t="n">
-        <v>6666105</v>
+        <v>6666109</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6747,7 +6747,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6772,22 +6772,22 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>

--- a/artfynd/A 32085-2025 artfynd.xlsx
+++ b/artfynd/A 32085-2025 artfynd.xlsx
@@ -812,46 +812,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127295076</v>
+        <v>127297595</v>
       </c>
       <c r="B3" t="n">
-        <v>98447</v>
+        <v>75134</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -859,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505375</v>
+        <v>505508</v>
       </c>
       <c r="R3" t="n">
-        <v>6666039</v>
+        <v>6666170</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +895,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,6 +907,26 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -932,37 +943,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127297595</v>
+        <v>127295076</v>
       </c>
       <c r="B4" t="n">
-        <v>75134</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -970,10 +990,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505508</v>
+        <v>505375</v>
       </c>
       <c r="R4" t="n">
-        <v>6666170</v>
+        <v>6666039</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,7 +1025,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1015,7 +1035,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,26 +1047,6 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -3052,44 +3052,36 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127296043</v>
+        <v>127297420</v>
       </c>
       <c r="B21" t="n">
-        <v>98447</v>
+        <v>96700</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -3099,10 +3091,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>505457</v>
+        <v>505483</v>
       </c>
       <c r="R21" t="n">
-        <v>6666067</v>
+        <v>6666164</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3134,7 +3126,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3144,7 +3136,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3156,6 +3148,26 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3172,46 +3184,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295317</v>
+        <v>127297958</v>
       </c>
       <c r="B22" t="n">
-        <v>98447</v>
+        <v>75134</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3219,10 +3222,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>505401</v>
+        <v>505525</v>
       </c>
       <c r="R22" t="n">
-        <v>6666036</v>
+        <v>6666131</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3254,7 +3257,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3264,7 +3267,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3276,6 +3279,26 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3292,36 +3315,44 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127297420</v>
+        <v>127296043</v>
       </c>
       <c r="B23" t="n">
-        <v>96700</v>
+        <v>98447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -3331,10 +3362,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>505483</v>
+        <v>505457</v>
       </c>
       <c r="R23" t="n">
-        <v>6666164</v>
+        <v>6666067</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3366,7 +3397,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3376,7 +3407,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3388,26 +3419,6 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3424,37 +3435,46 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127297958</v>
+        <v>127295317</v>
       </c>
       <c r="B24" t="n">
-        <v>75134</v>
+        <v>98447</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3462,10 +3482,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505525</v>
+        <v>505401</v>
       </c>
       <c r="R24" t="n">
-        <v>6666131</v>
+        <v>6666036</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3497,7 +3517,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3507,7 +3527,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3519,26 +3539,6 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -4301,37 +4301,46 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127298321</v>
+        <v>127294722</v>
       </c>
       <c r="B31" t="n">
-        <v>79636</v>
+        <v>98447</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4339,10 +4348,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>505552</v>
+        <v>505312</v>
       </c>
       <c r="R31" t="n">
-        <v>6666024</v>
+        <v>6666032</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4374,7 +4383,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4384,7 +4393,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4396,26 +4405,6 @@
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Stump # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4432,46 +4421,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127294722</v>
+        <v>127298321</v>
       </c>
       <c r="B32" t="n">
-        <v>98447</v>
+        <v>79636</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4479,10 +4459,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>505312</v>
+        <v>505552</v>
       </c>
       <c r="R32" t="n">
-        <v>6666032</v>
+        <v>6666024</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4514,7 +4494,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4524,7 +4504,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4536,6 +4516,26 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stump # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4923,37 +4923,46 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127296758</v>
+        <v>127294976</v>
       </c>
       <c r="B36" t="n">
-        <v>78424</v>
+        <v>98447</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4961,10 +4970,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>505486</v>
+        <v>505373</v>
       </c>
       <c r="R36" t="n">
-        <v>6666108</v>
+        <v>6666042</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4996,7 +5005,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5006,7 +5015,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5018,26 +5027,6 @@
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5054,46 +5043,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127294976</v>
+        <v>127296758</v>
       </c>
       <c r="B37" t="n">
-        <v>98447</v>
+        <v>78424</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5101,10 +5081,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>505373</v>
+        <v>505486</v>
       </c>
       <c r="R37" t="n">
-        <v>6666042</v>
+        <v>6666108</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5136,7 +5116,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5146,7 +5126,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5158,6 +5138,26 @@
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -6057,46 +6057,37 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127295179</v>
+        <v>127298146</v>
       </c>
       <c r="B45" t="n">
-        <v>98447</v>
+        <v>91350</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6104,10 +6095,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>505378</v>
+        <v>505544</v>
       </c>
       <c r="R45" t="n">
-        <v>6666040</v>
+        <v>6666053</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6139,7 +6130,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6149,7 +6140,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6161,6 +6152,21 @@
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6177,7 +6183,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127295238</v>
+        <v>127295179</v>
       </c>
       <c r="B46" t="n">
         <v>98447</v>
@@ -6207,7 +6213,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>149</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6224,10 +6230,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>505388</v>
+        <v>505378</v>
       </c>
       <c r="R46" t="n">
-        <v>6666037</v>
+        <v>6666040</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6259,7 +6265,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6269,7 +6275,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6297,37 +6303,46 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127298146</v>
+        <v>127295238</v>
       </c>
       <c r="B47" t="n">
-        <v>91350</v>
+        <v>98447</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6335,10 +6350,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>505544</v>
+        <v>505388</v>
       </c>
       <c r="R47" t="n">
-        <v>6666053</v>
+        <v>6666037</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6370,7 +6385,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6380,7 +6395,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6392,21 +6407,6 @@
       <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6423,46 +6423,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127296142</v>
+        <v>127296862</v>
       </c>
       <c r="B48" t="n">
-        <v>98447</v>
+        <v>79050</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6470,10 +6461,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>505465</v>
+        <v>505478</v>
       </c>
       <c r="R48" t="n">
-        <v>6666072</v>
+        <v>6666105</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6505,7 +6496,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6515,7 +6506,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6527,6 +6518,26 @@
       <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6543,32 +6554,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127296862</v>
+        <v>127297221</v>
       </c>
       <c r="B49" t="n">
-        <v>79050</v>
+        <v>75125</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>6439</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6584,7 +6595,7 @@
         <v>505478</v>
       </c>
       <c r="R49" t="n">
-        <v>6666105</v>
+        <v>6666109</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6616,7 +6627,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6626,7 +6637,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6641,22 +6652,22 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6674,37 +6685,46 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127297221</v>
+        <v>127296142</v>
       </c>
       <c r="B50" t="n">
-        <v>75125</v>
+        <v>98447</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6439</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6712,10 +6732,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>505478</v>
+        <v>505465</v>
       </c>
       <c r="R50" t="n">
-        <v>6666109</v>
+        <v>6666072</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6747,7 +6767,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6757,7 +6777,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6769,26 +6789,6 @@
       <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 32085-2025 artfynd.xlsx
+++ b/artfynd/A 32085-2025 artfynd.xlsx
@@ -6423,32 +6423,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127296862</v>
+        <v>127297221</v>
       </c>
       <c r="B48" t="n">
-        <v>79050</v>
+        <v>75125</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>6439</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6464,7 +6464,7 @@
         <v>505478</v>
       </c>
       <c r="R48" t="n">
-        <v>6666105</v>
+        <v>6666109</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6521,22 +6521,22 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6554,32 +6554,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127297221</v>
+        <v>127296862</v>
       </c>
       <c r="B49" t="n">
-        <v>75125</v>
+        <v>79050</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6439</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6595,7 +6595,7 @@
         <v>505478</v>
       </c>
       <c r="R49" t="n">
-        <v>6666109</v>
+        <v>6666105</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6652,22 +6652,22 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>

--- a/artfynd/A 32085-2025 artfynd.xlsx
+++ b/artfynd/A 32085-2025 artfynd.xlsx
@@ -3052,36 +3052,44 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127297420</v>
+        <v>127296043</v>
       </c>
       <c r="B21" t="n">
-        <v>96700</v>
+        <v>98447</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -3091,10 +3099,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>505483</v>
+        <v>505457</v>
       </c>
       <c r="R21" t="n">
-        <v>6666164</v>
+        <v>6666067</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3126,7 +3134,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3136,7 +3144,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3148,26 +3156,6 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3184,37 +3172,46 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127297958</v>
+        <v>127295317</v>
       </c>
       <c r="B22" t="n">
-        <v>75134</v>
+        <v>98447</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3222,10 +3219,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>505525</v>
+        <v>505401</v>
       </c>
       <c r="R22" t="n">
-        <v>6666131</v>
+        <v>6666036</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3257,7 +3254,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3267,7 +3264,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3279,26 +3276,6 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3315,44 +3292,36 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127296043</v>
+        <v>127297420</v>
       </c>
       <c r="B23" t="n">
-        <v>98447</v>
+        <v>96700</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -3362,10 +3331,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>505457</v>
+        <v>505483</v>
       </c>
       <c r="R23" t="n">
-        <v>6666067</v>
+        <v>6666164</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3397,7 +3366,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3407,7 +3376,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3419,6 +3388,26 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3435,46 +3424,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295317</v>
+        <v>127297958</v>
       </c>
       <c r="B24" t="n">
-        <v>98447</v>
+        <v>75134</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3482,10 +3462,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505401</v>
+        <v>505525</v>
       </c>
       <c r="R24" t="n">
-        <v>6666036</v>
+        <v>6666131</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3517,7 +3497,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3527,7 +3507,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3539,6 +3519,26 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">

--- a/artfynd/A 32085-2025 artfynd.xlsx
+++ b/artfynd/A 32085-2025 artfynd.xlsx
@@ -946,7 +946,7 @@
         <v>127295076</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1446,10 +1446,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127295189</v>
+        <v>127295345</v>
       </c>
       <c r="B8" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505380</v>
+        <v>505402</v>
       </c>
       <c r="R8" t="n">
-        <v>6666036</v>
+        <v>6666038</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1569,7 +1569,7 @@
         <v>127294826</v>
       </c>
       <c r="B9" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1686,10 +1686,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127295345</v>
+        <v>127295189</v>
       </c>
       <c r="B10" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505402</v>
+        <v>505380</v>
       </c>
       <c r="R10" t="n">
-        <v>6666038</v>
+        <v>6666036</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1941,7 +1941,7 @@
         <v>127294550</v>
       </c>
       <c r="B12" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2058,10 +2058,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127295061</v>
+        <v>127294748</v>
       </c>
       <c r="B13" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505372</v>
+        <v>505318</v>
       </c>
       <c r="R13" t="n">
-        <v>6666038</v>
+        <v>6666032</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2178,10 +2178,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127294748</v>
+        <v>127295061</v>
       </c>
       <c r="B14" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2225,10 +2225,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505318</v>
+        <v>505372</v>
       </c>
       <c r="R14" t="n">
-        <v>6666032</v>
+        <v>6666038</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2301,7 +2301,7 @@
         <v>127295213</v>
       </c>
       <c r="B15" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2418,10 +2418,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127297615</v>
+        <v>127297651</v>
       </c>
       <c r="B16" t="n">
-        <v>75134</v>
+        <v>96700</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2429,26 +2429,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>308</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2456,7 +2457,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505511</v>
+        <v>505512</v>
       </c>
       <c r="R16" t="n">
         <v>6666168</v>
@@ -2491,7 +2492,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2501,7 +2502,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2526,12 +2527,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2549,10 +2550,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127297651</v>
+        <v>127297615</v>
       </c>
       <c r="B17" t="n">
-        <v>96700</v>
+        <v>75134</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2560,27 +2561,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505512</v>
+        <v>505511</v>
       </c>
       <c r="R17" t="n">
         <v>6666168</v>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2658,12 +2658,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2684,7 +2684,7 @@
         <v>127295297</v>
       </c>
       <c r="B18" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>127296113</v>
       </c>
       <c r="B19" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3052,44 +3052,36 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127296043</v>
+        <v>127297420</v>
       </c>
       <c r="B21" t="n">
-        <v>98447</v>
+        <v>96700</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -3099,10 +3091,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>505457</v>
+        <v>505483</v>
       </c>
       <c r="R21" t="n">
-        <v>6666067</v>
+        <v>6666164</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3134,7 +3126,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3144,7 +3136,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3156,6 +3148,26 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3172,46 +3184,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295317</v>
+        <v>127297958</v>
       </c>
       <c r="B22" t="n">
-        <v>98447</v>
+        <v>75134</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3219,10 +3222,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>505401</v>
+        <v>505525</v>
       </c>
       <c r="R22" t="n">
-        <v>6666036</v>
+        <v>6666131</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3254,7 +3257,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3264,7 +3267,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3276,6 +3279,26 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3292,36 +3315,44 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127297420</v>
+        <v>127296043</v>
       </c>
       <c r="B23" t="n">
-        <v>96700</v>
+        <v>98448</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -3331,10 +3362,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>505483</v>
+        <v>505457</v>
       </c>
       <c r="R23" t="n">
-        <v>6666164</v>
+        <v>6666067</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3366,7 +3397,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3376,7 +3407,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3388,26 +3419,6 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3424,37 +3435,46 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127297958</v>
+        <v>127295317</v>
       </c>
       <c r="B24" t="n">
-        <v>75134</v>
+        <v>98448</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3462,10 +3482,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505525</v>
+        <v>505401</v>
       </c>
       <c r="R24" t="n">
-        <v>6666131</v>
+        <v>6666036</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3497,7 +3517,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3507,7 +3527,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3519,26 +3539,6 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3555,49 +3555,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127298417</v>
+        <v>127295207</v>
       </c>
       <c r="B25" t="n">
-        <v>98364</v>
+        <v>98448</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3606,10 +3602,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>505547</v>
+        <v>505383</v>
       </c>
       <c r="R25" t="n">
-        <v>6666020</v>
+        <v>6666039</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3641,7 +3637,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3651,7 +3647,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3682,7 +3678,7 @@
         <v>127294423</v>
       </c>
       <c r="B26" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3802,7 +3798,7 @@
         <v>127295681</v>
       </c>
       <c r="B27" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3919,45 +3915,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127295207</v>
+        <v>127298417</v>
       </c>
       <c r="B28" t="n">
-        <v>98447</v>
+        <v>98365</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>505383</v>
+        <v>505547</v>
       </c>
       <c r="R28" t="n">
-        <v>6666039</v>
+        <v>6666020</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4039,37 +4039,46 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127296321</v>
+        <v>127294722</v>
       </c>
       <c r="B29" t="n">
-        <v>79050</v>
+        <v>98448</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4077,10 +4086,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>505487</v>
+        <v>505312</v>
       </c>
       <c r="R29" t="n">
-        <v>6666090</v>
+        <v>6666032</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4112,7 +4121,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4122,7 +4131,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4134,26 +4143,6 @@
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4170,10 +4159,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127297555</v>
+        <v>127298321</v>
       </c>
       <c r="B30" t="n">
-        <v>75134</v>
+        <v>79636</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4181,21 +4170,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>308</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4208,10 +4197,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>505501</v>
+        <v>505552</v>
       </c>
       <c r="R30" t="n">
-        <v>6666172</v>
+        <v>6666024</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4243,7 +4232,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4253,7 +4242,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4278,12 +4267,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Stump # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4301,46 +4290,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127294722</v>
+        <v>127296321</v>
       </c>
       <c r="B31" t="n">
-        <v>98447</v>
+        <v>79050</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4348,10 +4328,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>505312</v>
+        <v>505487</v>
       </c>
       <c r="R31" t="n">
-        <v>6666032</v>
+        <v>6666090</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4383,7 +4363,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4393,7 +4373,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4405,6 +4385,26 @@
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4421,10 +4421,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127298321</v>
+        <v>127297555</v>
       </c>
       <c r="B32" t="n">
-        <v>79636</v>
+        <v>75134</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4432,21 +4432,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>505552</v>
+        <v>505501</v>
       </c>
       <c r="R32" t="n">
-        <v>6666024</v>
+        <v>6666172</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Stump # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4555,7 +4555,7 @@
         <v>127295731</v>
       </c>
       <c r="B33" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>127294455</v>
       </c>
       <c r="B34" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>127294976</v>
       </c>
       <c r="B36" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>127295841</v>
       </c>
       <c r="B39" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>127294730</v>
       </c>
       <c r="B40" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>127295399</v>
       </c>
       <c r="B43" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6183,10 +6183,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127295179</v>
+        <v>127295238</v>
       </c>
       <c r="B46" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>505378</v>
+        <v>505388</v>
       </c>
       <c r="R46" t="n">
-        <v>6666040</v>
+        <v>6666037</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6265,7 +6265,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6303,10 +6303,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127295238</v>
+        <v>127295179</v>
       </c>
       <c r="B47" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>149</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6350,10 +6350,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>505388</v>
+        <v>505378</v>
       </c>
       <c r="R47" t="n">
-        <v>6666037</v>
+        <v>6666040</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6688,7 +6688,7 @@
         <v>127296142</v>
       </c>
       <c r="B50" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 32085-2025 artfynd.xlsx
+++ b/artfynd/A 32085-2025 artfynd.xlsx
@@ -2418,36 +2418,44 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127297651</v>
+        <v>127295297</v>
       </c>
       <c r="B16" t="n">
-        <v>96700</v>
+        <v>98448</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2457,10 +2465,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505512</v>
+        <v>505400</v>
       </c>
       <c r="R16" t="n">
-        <v>6666168</v>
+        <v>6666034</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2492,7 +2500,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2502,7 +2510,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2514,26 +2522,6 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2550,37 +2538,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127297615</v>
+        <v>127296113</v>
       </c>
       <c r="B17" t="n">
-        <v>75134</v>
+        <v>98448</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2588,10 +2585,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505511</v>
+        <v>505461</v>
       </c>
       <c r="R17" t="n">
-        <v>6666168</v>
+        <v>6666073</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2623,7 +2620,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2633,7 +2630,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2645,26 +2642,6 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2681,44 +2658,36 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127295297</v>
+        <v>127297651</v>
       </c>
       <c r="B18" t="n">
-        <v>98448</v>
+        <v>96700</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2728,10 +2697,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505400</v>
+        <v>505512</v>
       </c>
       <c r="R18" t="n">
-        <v>6666034</v>
+        <v>6666168</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2763,7 +2732,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2773,7 +2742,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2785,6 +2754,26 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2801,46 +2790,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127296113</v>
+        <v>127297615</v>
       </c>
       <c r="B19" t="n">
-        <v>98448</v>
+        <v>75134</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2848,10 +2828,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>505461</v>
+        <v>505511</v>
       </c>
       <c r="R19" t="n">
-        <v>6666073</v>
+        <v>6666168</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2883,7 +2863,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2893,7 +2873,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2905,6 +2885,26 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -4923,46 +4923,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127294976</v>
+        <v>127296758</v>
       </c>
       <c r="B36" t="n">
-        <v>98448</v>
+        <v>78424</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4970,10 +4961,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>505373</v>
+        <v>505486</v>
       </c>
       <c r="R36" t="n">
-        <v>6666042</v>
+        <v>6666108</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5005,7 +4996,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5015,7 +5006,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5027,6 +5018,26 @@
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5043,37 +5054,46 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127296758</v>
+        <v>127294976</v>
       </c>
       <c r="B37" t="n">
-        <v>78424</v>
+        <v>98448</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5081,10 +5101,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>505486</v>
+        <v>505373</v>
       </c>
       <c r="R37" t="n">
-        <v>6666108</v>
+        <v>6666042</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5116,7 +5136,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5126,7 +5146,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5138,26 +5158,6 @@
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">

--- a/artfynd/A 32085-2025 artfynd.xlsx
+++ b/artfynd/A 32085-2025 artfynd.xlsx
@@ -812,37 +812,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127297595</v>
+        <v>127295076</v>
       </c>
       <c r="B3" t="n">
-        <v>75134</v>
+        <v>98450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -850,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505508</v>
+        <v>505375</v>
       </c>
       <c r="R3" t="n">
-        <v>6666170</v>
+        <v>6666039</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,26 +916,6 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -943,46 +932,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127295076</v>
+        <v>127297595</v>
       </c>
       <c r="B4" t="n">
-        <v>98448</v>
+        <v>75136</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -990,10 +970,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505375</v>
+        <v>505508</v>
       </c>
       <c r="R4" t="n">
-        <v>6666039</v>
+        <v>6666170</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1025,7 +1005,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1035,7 +1015,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,6 +1027,26 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1066,7 +1066,7 @@
         <v>127296095</v>
       </c>
       <c r="B5" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>127294425</v>
       </c>
       <c r="B6" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1314,36 +1314,44 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127296163</v>
+        <v>127294826</v>
       </c>
       <c r="B7" t="n">
-        <v>96700</v>
+        <v>98450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1353,10 +1361,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505465</v>
+        <v>505332</v>
       </c>
       <c r="R7" t="n">
-        <v>6666072</v>
+        <v>6666037</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1388,7 +1396,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1398,7 +1406,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1410,26 +1418,6 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1449,7 +1437,7 @@
         <v>127295345</v>
       </c>
       <c r="B8" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1566,44 +1554,36 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127294826</v>
+        <v>127296163</v>
       </c>
       <c r="B9" t="n">
-        <v>98448</v>
+        <v>96702</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1613,10 +1593,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505332</v>
+        <v>505465</v>
       </c>
       <c r="R9" t="n">
-        <v>6666037</v>
+        <v>6666072</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1648,7 +1628,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1658,7 +1638,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1670,6 +1650,26 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1689,7 +1689,7 @@
         <v>127295189</v>
       </c>
       <c r="B10" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>127297697</v>
       </c>
       <c r="B11" t="n">
-        <v>96700</v>
+        <v>96702</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>127294550</v>
       </c>
       <c r="B12" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2058,10 +2058,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127294748</v>
+        <v>127295061</v>
       </c>
       <c r="B13" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505318</v>
+        <v>505372</v>
       </c>
       <c r="R13" t="n">
-        <v>6666032</v>
+        <v>6666038</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2178,10 +2178,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127295061</v>
+        <v>127294748</v>
       </c>
       <c r="B14" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2225,10 +2225,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505372</v>
+        <v>505318</v>
       </c>
       <c r="R14" t="n">
-        <v>6666038</v>
+        <v>6666032</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2301,7 +2301,7 @@
         <v>127295213</v>
       </c>
       <c r="B15" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2418,46 +2418,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127295297</v>
+        <v>127297615</v>
       </c>
       <c r="B16" t="n">
-        <v>98448</v>
+        <v>75136</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2465,10 +2456,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505400</v>
+        <v>505511</v>
       </c>
       <c r="R16" t="n">
-        <v>6666034</v>
+        <v>6666168</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2500,7 +2491,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2510,7 +2501,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2522,6 +2513,26 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2538,44 +2549,36 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127296113</v>
+        <v>127297651</v>
       </c>
       <c r="B17" t="n">
-        <v>98448</v>
+        <v>96702</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2585,10 +2588,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505461</v>
+        <v>505512</v>
       </c>
       <c r="R17" t="n">
-        <v>6666073</v>
+        <v>6666168</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2620,7 +2623,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2630,7 +2633,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2642,6 +2645,26 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2658,36 +2681,44 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127297651</v>
+        <v>127295297</v>
       </c>
       <c r="B18" t="n">
-        <v>96700</v>
+        <v>98450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2697,10 +2728,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505512</v>
+        <v>505400</v>
       </c>
       <c r="R18" t="n">
-        <v>6666168</v>
+        <v>6666034</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2732,7 +2763,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2742,7 +2773,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2754,26 +2785,6 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2790,37 +2801,46 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127297615</v>
+        <v>127296113</v>
       </c>
       <c r="B19" t="n">
-        <v>75134</v>
+        <v>98450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2828,10 +2848,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>505511</v>
+        <v>505461</v>
       </c>
       <c r="R19" t="n">
-        <v>6666168</v>
+        <v>6666073</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2863,7 +2883,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2873,7 +2893,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2885,26 +2905,6 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2924,7 +2924,7 @@
         <v>127295662</v>
       </c>
       <c r="B20" t="n">
-        <v>75134</v>
+        <v>75136</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3052,36 +3052,44 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127297420</v>
+        <v>127296043</v>
       </c>
       <c r="B21" t="n">
-        <v>96700</v>
+        <v>98450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -3091,10 +3099,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>505483</v>
+        <v>505457</v>
       </c>
       <c r="R21" t="n">
-        <v>6666164</v>
+        <v>6666067</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3126,7 +3134,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3136,7 +3144,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3148,26 +3156,6 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3184,37 +3172,46 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127297958</v>
+        <v>127295317</v>
       </c>
       <c r="B22" t="n">
-        <v>75134</v>
+        <v>98450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3222,10 +3219,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>505525</v>
+        <v>505401</v>
       </c>
       <c r="R22" t="n">
-        <v>6666131</v>
+        <v>6666036</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3257,7 +3254,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3267,7 +3264,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3279,26 +3276,6 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3315,44 +3292,36 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127296043</v>
+        <v>127297420</v>
       </c>
       <c r="B23" t="n">
-        <v>98448</v>
+        <v>96702</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -3362,10 +3331,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>505457</v>
+        <v>505483</v>
       </c>
       <c r="R23" t="n">
-        <v>6666067</v>
+        <v>6666164</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3397,7 +3366,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3407,7 +3376,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3419,6 +3388,26 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3435,46 +3424,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295317</v>
+        <v>127297958</v>
       </c>
       <c r="B24" t="n">
-        <v>98448</v>
+        <v>75136</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3482,10 +3462,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505401</v>
+        <v>505525</v>
       </c>
       <c r="R24" t="n">
-        <v>6666036</v>
+        <v>6666131</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3517,7 +3497,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3527,7 +3507,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3539,6 +3519,26 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3555,45 +3555,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295207</v>
+        <v>127298417</v>
       </c>
       <c r="B25" t="n">
-        <v>98448</v>
+        <v>98367</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3602,10 +3606,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>505383</v>
+        <v>505547</v>
       </c>
       <c r="R25" t="n">
-        <v>6666039</v>
+        <v>6666020</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3637,7 +3641,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3647,7 +3651,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3678,7 +3682,7 @@
         <v>127294423</v>
       </c>
       <c r="B26" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3798,7 +3802,7 @@
         <v>127295681</v>
       </c>
       <c r="B27" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3915,49 +3919,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127298417</v>
+        <v>127295207</v>
       </c>
       <c r="B28" t="n">
-        <v>98365</v>
+        <v>98450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>505547</v>
+        <v>505383</v>
       </c>
       <c r="R28" t="n">
-        <v>6666020</v>
+        <v>6666039</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4039,46 +4039,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127294722</v>
+        <v>127298321</v>
       </c>
       <c r="B29" t="n">
-        <v>98448</v>
+        <v>79638</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4086,10 +4077,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>505312</v>
+        <v>505552</v>
       </c>
       <c r="R29" t="n">
-        <v>6666032</v>
+        <v>6666024</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4121,7 +4112,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4131,7 +4122,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4143,6 +4134,26 @@
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Stump # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4159,37 +4170,46 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127298321</v>
+        <v>127294722</v>
       </c>
       <c r="B30" t="n">
-        <v>79636</v>
+        <v>98450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4197,10 +4217,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>505552</v>
+        <v>505312</v>
       </c>
       <c r="R30" t="n">
-        <v>6666024</v>
+        <v>6666032</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4232,7 +4252,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4242,7 +4262,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4254,26 +4274,6 @@
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Stump # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4293,7 +4293,7 @@
         <v>127296321</v>
       </c>
       <c r="B31" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>127297555</v>
       </c>
       <c r="B32" t="n">
-        <v>75134</v>
+        <v>75136</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>127295731</v>
       </c>
       <c r="B33" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>127294455</v>
       </c>
       <c r="B34" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>127298053</v>
       </c>
       <c r="B35" t="n">
-        <v>78424</v>
+        <v>78426</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4923,37 +4923,46 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127296758</v>
+        <v>127294976</v>
       </c>
       <c r="B36" t="n">
-        <v>78424</v>
+        <v>98450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4961,10 +4970,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>505486</v>
+        <v>505373</v>
       </c>
       <c r="R36" t="n">
-        <v>6666108</v>
+        <v>6666042</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4996,7 +5005,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5006,7 +5015,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5018,26 +5027,6 @@
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5054,46 +5043,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127294976</v>
+        <v>127296758</v>
       </c>
       <c r="B37" t="n">
-        <v>98448</v>
+        <v>78426</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5101,10 +5081,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>505373</v>
+        <v>505486</v>
       </c>
       <c r="R37" t="n">
-        <v>6666042</v>
+        <v>6666108</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5136,7 +5116,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5146,7 +5126,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5158,6 +5138,26 @@
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5177,7 +5177,7 @@
         <v>127297810</v>
       </c>
       <c r="B38" t="n">
-        <v>96700</v>
+        <v>96702</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>127295841</v>
       </c>
       <c r="B39" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>127294730</v>
       </c>
       <c r="B40" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         <v>127295873</v>
       </c>
       <c r="B41" t="n">
-        <v>96700</v>
+        <v>96702</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>127295399</v>
       </c>
       <c r="B43" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
         <v>127301907</v>
       </c>
       <c r="B44" t="n">
-        <v>96795</v>
+        <v>96797</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
         <v>127298146</v>
       </c>
       <c r="B45" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6183,10 +6183,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127295238</v>
+        <v>127295179</v>
       </c>
       <c r="B46" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>149</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>505388</v>
+        <v>505378</v>
       </c>
       <c r="R46" t="n">
-        <v>6666037</v>
+        <v>6666040</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6265,7 +6265,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6303,10 +6303,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127295179</v>
+        <v>127295238</v>
       </c>
       <c r="B47" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6350,10 +6350,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>505378</v>
+        <v>505388</v>
       </c>
       <c r="R47" t="n">
-        <v>6666040</v>
+        <v>6666037</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6423,37 +6423,46 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127297221</v>
+        <v>127296142</v>
       </c>
       <c r="B48" t="n">
-        <v>75125</v>
+        <v>98450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6439</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6461,10 +6470,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>505478</v>
+        <v>505465</v>
       </c>
       <c r="R48" t="n">
-        <v>6666109</v>
+        <v>6666072</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6496,7 +6505,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6506,7 +6515,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6518,26 +6527,6 @@
       <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6557,7 +6546,7 @@
         <v>127296862</v>
       </c>
       <c r="B49" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6685,46 +6674,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127296142</v>
+        <v>127297221</v>
       </c>
       <c r="B50" t="n">
-        <v>98448</v>
+        <v>75127</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6439</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6732,10 +6712,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>505465</v>
+        <v>505478</v>
       </c>
       <c r="R50" t="n">
-        <v>6666072</v>
+        <v>6666109</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6767,7 +6747,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6777,7 +6757,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6789,6 +6769,26 @@
       <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 32085-2025 artfynd.xlsx
+++ b/artfynd/A 32085-2025 artfynd.xlsx
@@ -812,46 +812,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127295076</v>
+        <v>127297595</v>
       </c>
       <c r="B3" t="n">
-        <v>98450</v>
+        <v>75136</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -859,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505375</v>
+        <v>505508</v>
       </c>
       <c r="R3" t="n">
-        <v>6666039</v>
+        <v>6666170</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +895,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,6 +907,26 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -932,37 +943,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127297595</v>
+        <v>127295076</v>
       </c>
       <c r="B4" t="n">
-        <v>75136</v>
+        <v>98450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -970,10 +990,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505508</v>
+        <v>505375</v>
       </c>
       <c r="R4" t="n">
-        <v>6666170</v>
+        <v>6666039</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,7 +1025,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1015,7 +1035,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,26 +1047,6 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1063,45 +1063,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127296095</v>
+        <v>127294425</v>
       </c>
       <c r="B5" t="n">
-        <v>79052</v>
+        <v>97327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1109,10 +1102,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505457</v>
+        <v>505296</v>
       </c>
       <c r="R5" t="n">
-        <v>6666067</v>
+        <v>6666023</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1137,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1154,7 +1147,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,26 +1159,6 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Dead branch  # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1202,38 +1175,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127294425</v>
+        <v>127296095</v>
       </c>
       <c r="B6" t="n">
-        <v>97327</v>
+        <v>79052</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1241,10 +1221,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505296</v>
+        <v>505457</v>
       </c>
       <c r="R6" t="n">
-        <v>6666023</v>
+        <v>6666067</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1276,7 +1256,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1286,7 +1266,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1298,6 +1278,26 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Dead branch  # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1434,7 +1434,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127295345</v>
+        <v>127295189</v>
       </c>
       <c r="B8" t="n">
         <v>98450</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505402</v>
+        <v>505380</v>
       </c>
       <c r="R8" t="n">
-        <v>6666038</v>
+        <v>6666036</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1554,36 +1554,44 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127296163</v>
+        <v>127295345</v>
       </c>
       <c r="B9" t="n">
-        <v>96702</v>
+        <v>98450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1593,10 +1601,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505465</v>
+        <v>505402</v>
       </c>
       <c r="R9" t="n">
-        <v>6666072</v>
+        <v>6666038</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1628,7 +1636,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1638,7 +1646,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1650,26 +1658,6 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1686,44 +1674,36 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127295189</v>
+        <v>127296163</v>
       </c>
       <c r="B10" t="n">
-        <v>98450</v>
+        <v>96702</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1733,10 +1713,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505380</v>
+        <v>505465</v>
       </c>
       <c r="R10" t="n">
-        <v>6666036</v>
+        <v>6666072</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1768,7 +1748,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1778,7 +1758,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1790,6 +1770,26 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -2418,10 +2418,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127297615</v>
+        <v>127297651</v>
       </c>
       <c r="B16" t="n">
-        <v>75136</v>
+        <v>96702</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2429,26 +2429,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>308</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2456,7 +2457,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505511</v>
+        <v>505512</v>
       </c>
       <c r="R16" t="n">
         <v>6666168</v>
@@ -2491,7 +2492,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2501,7 +2502,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2526,12 +2527,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2549,10 +2550,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127297651</v>
+        <v>127297615</v>
       </c>
       <c r="B17" t="n">
-        <v>96702</v>
+        <v>75136</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2560,27 +2561,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505512</v>
+        <v>505511</v>
       </c>
       <c r="R17" t="n">
         <v>6666168</v>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2658,12 +2658,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -4039,37 +4039,46 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127298321</v>
+        <v>127294722</v>
       </c>
       <c r="B29" t="n">
-        <v>79638</v>
+        <v>98450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4077,10 +4086,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>505552</v>
+        <v>505312</v>
       </c>
       <c r="R29" t="n">
-        <v>6666024</v>
+        <v>6666032</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4112,7 +4121,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4122,7 +4131,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4134,26 +4143,6 @@
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Stump # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4170,46 +4159,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127294722</v>
+        <v>127296321</v>
       </c>
       <c r="B30" t="n">
-        <v>98450</v>
+        <v>79052</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4217,10 +4197,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>505312</v>
+        <v>505487</v>
       </c>
       <c r="R30" t="n">
-        <v>6666032</v>
+        <v>6666090</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4252,7 +4232,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4262,7 +4242,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4274,6 +4254,26 @@
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4290,10 +4290,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127296321</v>
+        <v>127297555</v>
       </c>
       <c r="B31" t="n">
-        <v>79052</v>
+        <v>75136</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4301,21 +4301,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>505487</v>
+        <v>505501</v>
       </c>
       <c r="R31" t="n">
-        <v>6666090</v>
+        <v>6666172</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4388,22 +4388,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4421,10 +4421,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127297555</v>
+        <v>127298321</v>
       </c>
       <c r="B32" t="n">
-        <v>75136</v>
+        <v>79638</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4432,21 +4432,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>308</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>505501</v>
+        <v>505552</v>
       </c>
       <c r="R32" t="n">
-        <v>6666172</v>
+        <v>6666024</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Stump # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -6423,46 +6423,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127296142</v>
+        <v>127296862</v>
       </c>
       <c r="B48" t="n">
-        <v>98450</v>
+        <v>79052</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6470,10 +6461,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>505465</v>
+        <v>505478</v>
       </c>
       <c r="R48" t="n">
-        <v>6666072</v>
+        <v>6666105</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6505,7 +6496,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6515,7 +6506,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6527,6 +6518,26 @@
       <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6543,32 +6554,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127296862</v>
+        <v>127297221</v>
       </c>
       <c r="B49" t="n">
-        <v>79052</v>
+        <v>75127</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>6439</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6584,7 +6595,7 @@
         <v>505478</v>
       </c>
       <c r="R49" t="n">
-        <v>6666105</v>
+        <v>6666109</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6616,7 +6627,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6626,7 +6637,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6641,22 +6652,22 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6674,37 +6685,46 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127297221</v>
+        <v>127296142</v>
       </c>
       <c r="B50" t="n">
-        <v>75127</v>
+        <v>98450</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6439</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6712,10 +6732,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>505478</v>
+        <v>505465</v>
       </c>
       <c r="R50" t="n">
-        <v>6666109</v>
+        <v>6666072</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6747,7 +6767,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6757,7 +6777,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6769,26 +6789,6 @@
       <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 32085-2025 artfynd.xlsx
+++ b/artfynd/A 32085-2025 artfynd.xlsx
@@ -812,37 +812,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127297595</v>
+        <v>127295076</v>
       </c>
       <c r="B3" t="n">
-        <v>75136</v>
+        <v>98450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -850,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505508</v>
+        <v>505375</v>
       </c>
       <c r="R3" t="n">
-        <v>6666170</v>
+        <v>6666039</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,26 +916,6 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -943,46 +932,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127295076</v>
+        <v>127297595</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>75136</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -990,10 +970,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505375</v>
+        <v>505508</v>
       </c>
       <c r="R4" t="n">
-        <v>6666039</v>
+        <v>6666170</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1025,7 +1005,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1035,7 +1015,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,6 +1027,26 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1314,44 +1314,36 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127294826</v>
+        <v>127296163</v>
       </c>
       <c r="B7" t="n">
-        <v>98450</v>
+        <v>96702</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1361,10 +1353,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505332</v>
+        <v>505465</v>
       </c>
       <c r="R7" t="n">
-        <v>6666037</v>
+        <v>6666072</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1396,7 +1388,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1406,7 +1398,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1418,6 +1410,26 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1434,7 +1446,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127295189</v>
+        <v>127294826</v>
       </c>
       <c r="B8" t="n">
         <v>98450</v>
@@ -1464,7 +1476,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1481,10 +1493,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505380</v>
+        <v>505332</v>
       </c>
       <c r="R8" t="n">
-        <v>6666036</v>
+        <v>6666037</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1516,7 +1528,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1526,7 +1538,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1554,7 +1566,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127295345</v>
+        <v>127295189</v>
       </c>
       <c r="B9" t="n">
         <v>98450</v>
@@ -1584,7 +1596,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1601,10 +1613,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505402</v>
+        <v>505380</v>
       </c>
       <c r="R9" t="n">
-        <v>6666038</v>
+        <v>6666036</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1636,7 +1648,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1646,7 +1658,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1674,36 +1686,44 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127296163</v>
+        <v>127295345</v>
       </c>
       <c r="B10" t="n">
-        <v>96702</v>
+        <v>98450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1713,10 +1733,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505465</v>
+        <v>505402</v>
       </c>
       <c r="R10" t="n">
-        <v>6666072</v>
+        <v>6666038</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1748,7 +1768,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1758,7 +1778,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1770,26 +1790,6 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -2418,10 +2418,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127297651</v>
+        <v>127297615</v>
       </c>
       <c r="B16" t="n">
-        <v>96702</v>
+        <v>75136</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2429,27 +2429,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2457,7 +2456,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505512</v>
+        <v>505511</v>
       </c>
       <c r="R16" t="n">
         <v>6666168</v>
@@ -2492,7 +2491,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2502,7 +2501,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2527,12 +2526,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2550,10 +2549,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127297615</v>
+        <v>127297651</v>
       </c>
       <c r="B17" t="n">
-        <v>75136</v>
+        <v>96702</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2561,26 +2560,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>308</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505511</v>
+        <v>505512</v>
       </c>
       <c r="R17" t="n">
         <v>6666168</v>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2658,12 +2658,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -3555,49 +3555,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127298417</v>
+        <v>127294423</v>
       </c>
       <c r="B25" t="n">
-        <v>98367</v>
+        <v>98450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3606,10 +3602,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>505547</v>
+        <v>505296</v>
       </c>
       <c r="R25" t="n">
-        <v>6666020</v>
+        <v>6666023</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3641,7 +3637,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3651,7 +3647,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3679,7 +3675,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127294423</v>
+        <v>127295681</v>
       </c>
       <c r="B26" t="n">
         <v>98450</v>
@@ -3709,7 +3705,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3726,10 +3722,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>505296</v>
+        <v>505425</v>
       </c>
       <c r="R26" t="n">
-        <v>6666023</v>
+        <v>6666033</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3761,7 +3757,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3771,7 +3767,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3799,7 +3795,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295681</v>
+        <v>127295207</v>
       </c>
       <c r="B27" t="n">
         <v>98450</v>
@@ -3829,7 +3825,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3846,10 +3842,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>505425</v>
+        <v>505383</v>
       </c>
       <c r="R27" t="n">
-        <v>6666033</v>
+        <v>6666039</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3881,7 +3877,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3891,7 +3887,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3919,45 +3915,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127295207</v>
+        <v>127298417</v>
       </c>
       <c r="B28" t="n">
-        <v>98450</v>
+        <v>98367</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>505383</v>
+        <v>505547</v>
       </c>
       <c r="R28" t="n">
-        <v>6666039</v>
+        <v>6666020</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 32085-2025 artfynd.xlsx
+++ b/artfynd/A 32085-2025 artfynd.xlsx
@@ -812,46 +812,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127295076</v>
+        <v>127297595</v>
       </c>
       <c r="B3" t="n">
-        <v>98450</v>
+        <v>75136</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -859,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505375</v>
+        <v>505508</v>
       </c>
       <c r="R3" t="n">
-        <v>6666039</v>
+        <v>6666170</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +895,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,6 +907,26 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -932,37 +943,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127297595</v>
+        <v>127295076</v>
       </c>
       <c r="B4" t="n">
-        <v>75136</v>
+        <v>98450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -970,10 +990,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505508</v>
+        <v>505375</v>
       </c>
       <c r="R4" t="n">
-        <v>6666170</v>
+        <v>6666039</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,7 +1025,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1015,7 +1035,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,26 +1047,6 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1063,38 +1063,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127294425</v>
+        <v>127296095</v>
       </c>
       <c r="B5" t="n">
-        <v>97327</v>
+        <v>79052</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1102,10 +1109,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505296</v>
+        <v>505457</v>
       </c>
       <c r="R5" t="n">
-        <v>6666023</v>
+        <v>6666067</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1137,7 +1144,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1147,7 +1154,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,6 +1166,26 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Dead branch  # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1175,45 +1202,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127296095</v>
+        <v>127294425</v>
       </c>
       <c r="B6" t="n">
-        <v>79052</v>
+        <v>97327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1221,10 +1241,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505457</v>
+        <v>505296</v>
       </c>
       <c r="R6" t="n">
-        <v>6666067</v>
+        <v>6666023</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,7 +1276,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1266,7 +1286,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,26 +1298,6 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Dead branch  # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1446,7 +1446,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127294826</v>
+        <v>127295345</v>
       </c>
       <c r="B8" t="n">
         <v>98450</v>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505332</v>
+        <v>505402</v>
       </c>
       <c r="R8" t="n">
-        <v>6666037</v>
+        <v>6666038</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1566,7 +1566,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127295189</v>
+        <v>127294826</v>
       </c>
       <c r="B9" t="n">
         <v>98450</v>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505380</v>
+        <v>505332</v>
       </c>
       <c r="R9" t="n">
-        <v>6666036</v>
+        <v>6666037</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1686,7 +1686,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127295345</v>
+        <v>127295189</v>
       </c>
       <c r="B10" t="n">
         <v>98450</v>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505402</v>
+        <v>505380</v>
       </c>
       <c r="R10" t="n">
-        <v>6666038</v>
+        <v>6666036</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2058,7 +2058,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127295061</v>
+        <v>127294748</v>
       </c>
       <c r="B13" t="n">
         <v>98450</v>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505372</v>
+        <v>505318</v>
       </c>
       <c r="R13" t="n">
-        <v>6666038</v>
+        <v>6666032</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2178,7 +2178,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127294748</v>
+        <v>127295061</v>
       </c>
       <c r="B14" t="n">
         <v>98450</v>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2225,10 +2225,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505318</v>
+        <v>505372</v>
       </c>
       <c r="R14" t="n">
-        <v>6666032</v>
+        <v>6666038</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -3555,7 +3555,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127294423</v>
+        <v>127295207</v>
       </c>
       <c r="B25" t="n">
         <v>98450</v>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3602,10 +3602,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>505296</v>
+        <v>505383</v>
       </c>
       <c r="R25" t="n">
-        <v>6666023</v>
+        <v>6666039</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3647,7 +3647,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3675,7 +3675,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127295681</v>
+        <v>127294423</v>
       </c>
       <c r="B26" t="n">
         <v>98450</v>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>505425</v>
+        <v>505296</v>
       </c>
       <c r="R26" t="n">
-        <v>6666033</v>
+        <v>6666023</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3795,7 +3795,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295207</v>
+        <v>127295681</v>
       </c>
       <c r="B27" t="n">
         <v>98450</v>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3842,10 +3842,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>505383</v>
+        <v>505425</v>
       </c>
       <c r="R27" t="n">
-        <v>6666039</v>
+        <v>6666033</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4039,46 +4039,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127294722</v>
+        <v>127296321</v>
       </c>
       <c r="B29" t="n">
-        <v>98450</v>
+        <v>79052</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4086,10 +4077,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>505312</v>
+        <v>505487</v>
       </c>
       <c r="R29" t="n">
-        <v>6666032</v>
+        <v>6666090</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4121,7 +4112,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4131,7 +4122,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4143,6 +4134,26 @@
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4159,10 +4170,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127296321</v>
+        <v>127297555</v>
       </c>
       <c r="B30" t="n">
-        <v>79052</v>
+        <v>75136</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4170,21 +4181,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4197,10 +4208,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>505487</v>
+        <v>505501</v>
       </c>
       <c r="R30" t="n">
-        <v>6666090</v>
+        <v>6666172</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4232,7 +4243,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4242,7 +4253,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4257,22 +4268,22 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4290,10 +4301,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127297555</v>
+        <v>127298321</v>
       </c>
       <c r="B31" t="n">
-        <v>75136</v>
+        <v>79638</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4301,21 +4312,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>308</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4328,10 +4339,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>505501</v>
+        <v>505552</v>
       </c>
       <c r="R31" t="n">
-        <v>6666172</v>
+        <v>6666024</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4363,7 +4374,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4373,7 +4384,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4398,12 +4409,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Stump # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4421,37 +4432,46 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127298321</v>
+        <v>127294722</v>
       </c>
       <c r="B32" t="n">
-        <v>79638</v>
+        <v>98450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4459,10 +4479,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>505552</v>
+        <v>505312</v>
       </c>
       <c r="R32" t="n">
-        <v>6666024</v>
+        <v>6666032</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4494,7 +4514,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4504,7 +4524,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4516,26 +4536,6 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Stump # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4923,46 +4923,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127294976</v>
+        <v>127296758</v>
       </c>
       <c r="B36" t="n">
-        <v>98450</v>
+        <v>78426</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4970,10 +4961,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>505373</v>
+        <v>505486</v>
       </c>
       <c r="R36" t="n">
-        <v>6666042</v>
+        <v>6666108</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5005,7 +4996,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5015,7 +5006,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5027,6 +5018,26 @@
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5043,37 +5054,46 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127296758</v>
+        <v>127294976</v>
       </c>
       <c r="B37" t="n">
-        <v>78426</v>
+        <v>98450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5081,10 +5101,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>505486</v>
+        <v>505373</v>
       </c>
       <c r="R37" t="n">
-        <v>6666108</v>
+        <v>6666042</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5116,7 +5136,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5126,7 +5146,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5138,26 +5158,6 @@
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5815,44 +5815,36 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127295399</v>
+        <v>127301907</v>
       </c>
       <c r="B43" t="n">
-        <v>98450</v>
+        <v>96797</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1841</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
@@ -5862,10 +5854,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>505404</v>
+        <v>505491</v>
       </c>
       <c r="R43" t="n">
-        <v>6666039</v>
+        <v>6666106</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5895,19 +5887,9 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>15:03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5919,6 +5901,26 @@
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5935,36 +5937,44 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127301907</v>
+        <v>127295399</v>
       </c>
       <c r="B44" t="n">
-        <v>96797</v>
+        <v>98450</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1841</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
@@ -5974,10 +5984,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>505491</v>
+        <v>505404</v>
       </c>
       <c r="R44" t="n">
-        <v>6666106</v>
+        <v>6666039</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6007,9 +6017,19 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6021,26 +6041,6 @@
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6057,37 +6057,46 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127298146</v>
+        <v>127295238</v>
       </c>
       <c r="B45" t="n">
-        <v>91352</v>
+        <v>98450</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6095,10 +6104,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>505544</v>
+        <v>505388</v>
       </c>
       <c r="R45" t="n">
-        <v>6666053</v>
+        <v>6666037</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6130,7 +6139,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6140,7 +6149,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6152,21 +6161,6 @@
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6303,46 +6297,37 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127295238</v>
+        <v>127298146</v>
       </c>
       <c r="B47" t="n">
-        <v>98450</v>
+        <v>91352</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6350,10 +6335,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>505388</v>
+        <v>505544</v>
       </c>
       <c r="R47" t="n">
-        <v>6666037</v>
+        <v>6666053</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6385,7 +6370,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6395,7 +6380,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6407,6 +6392,21 @@
       <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6423,32 +6423,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127296862</v>
+        <v>127297221</v>
       </c>
       <c r="B48" t="n">
-        <v>79052</v>
+        <v>75127</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>6439</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6464,7 +6464,7 @@
         <v>505478</v>
       </c>
       <c r="R48" t="n">
-        <v>6666105</v>
+        <v>6666109</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6521,22 +6521,22 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6554,32 +6554,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127297221</v>
+        <v>127296862</v>
       </c>
       <c r="B49" t="n">
-        <v>75127</v>
+        <v>79052</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6439</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6595,7 +6595,7 @@
         <v>505478</v>
       </c>
       <c r="R49" t="n">
-        <v>6666109</v>
+        <v>6666105</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6652,22 +6652,22 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>

--- a/artfynd/A 32085-2025 artfynd.xlsx
+++ b/artfynd/A 32085-2025 artfynd.xlsx
@@ -946,7 +946,7 @@
         <v>127295076</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>127294425</v>
       </c>
       <c r="B6" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>127296163</v>
       </c>
       <c r="B7" t="n">
-        <v>96702</v>
+        <v>96708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1446,10 +1446,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127295345</v>
+        <v>127295189</v>
       </c>
       <c r="B8" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505402</v>
+        <v>505380</v>
       </c>
       <c r="R8" t="n">
-        <v>6666038</v>
+        <v>6666036</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1569,7 +1569,7 @@
         <v>127294826</v>
       </c>
       <c r="B9" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1686,10 +1686,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127295189</v>
+        <v>127295345</v>
       </c>
       <c r="B10" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505380</v>
+        <v>505402</v>
       </c>
       <c r="R10" t="n">
-        <v>6666036</v>
+        <v>6666038</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1806,36 +1806,44 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127297697</v>
+        <v>127294550</v>
       </c>
       <c r="B11" t="n">
-        <v>96702</v>
+        <v>98456</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1845,10 +1853,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505514</v>
+        <v>505307</v>
       </c>
       <c r="R11" t="n">
-        <v>6666167</v>
+        <v>6666031</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1880,7 +1888,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1890,7 +1898,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1902,26 +1910,6 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1938,10 +1926,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127294550</v>
+        <v>127295061</v>
       </c>
       <c r="B12" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1968,7 +1956,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1985,10 +1973,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505307</v>
+        <v>505372</v>
       </c>
       <c r="R12" t="n">
-        <v>6666031</v>
+        <v>6666038</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2020,7 +2008,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2030,7 +2018,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2061,7 +2049,7 @@
         <v>127294748</v>
       </c>
       <c r="B13" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2178,44 +2166,36 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127295061</v>
+        <v>127297697</v>
       </c>
       <c r="B14" t="n">
-        <v>98450</v>
+        <v>96708</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2225,10 +2205,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505372</v>
+        <v>505514</v>
       </c>
       <c r="R14" t="n">
-        <v>6666038</v>
+        <v>6666167</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2260,7 +2240,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2270,7 +2250,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2282,6 +2262,26 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2301,7 +2301,7 @@
         <v>127295213</v>
       </c>
       <c r="B15" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2418,10 +2418,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127297615</v>
+        <v>127297651</v>
       </c>
       <c r="B16" t="n">
-        <v>75136</v>
+        <v>96708</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2429,26 +2429,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>308</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2456,7 +2457,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505511</v>
+        <v>505512</v>
       </c>
       <c r="R16" t="n">
         <v>6666168</v>
@@ -2491,7 +2492,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2501,7 +2502,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2526,12 +2527,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2549,10 +2550,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127297651</v>
+        <v>127297615</v>
       </c>
       <c r="B17" t="n">
-        <v>96702</v>
+        <v>75136</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2560,27 +2561,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505512</v>
+        <v>505511</v>
       </c>
       <c r="R17" t="n">
         <v>6666168</v>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2658,12 +2658,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2681,10 +2681,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127295297</v>
+        <v>127296113</v>
       </c>
       <c r="B18" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505400</v>
+        <v>505461</v>
       </c>
       <c r="R18" t="n">
-        <v>6666034</v>
+        <v>6666073</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2801,10 +2801,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127296113</v>
+        <v>127295297</v>
       </c>
       <c r="B19" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>505461</v>
+        <v>505400</v>
       </c>
       <c r="R19" t="n">
-        <v>6666073</v>
+        <v>6666034</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3052,44 +3052,36 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127296043</v>
+        <v>127297420</v>
       </c>
       <c r="B21" t="n">
-        <v>98450</v>
+        <v>96708</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -3099,10 +3091,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>505457</v>
+        <v>505483</v>
       </c>
       <c r="R21" t="n">
-        <v>6666067</v>
+        <v>6666164</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3134,7 +3126,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3144,7 +3136,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3156,6 +3148,26 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3172,46 +3184,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295317</v>
+        <v>127297958</v>
       </c>
       <c r="B22" t="n">
-        <v>98450</v>
+        <v>75136</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3219,10 +3222,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>505401</v>
+        <v>505525</v>
       </c>
       <c r="R22" t="n">
-        <v>6666036</v>
+        <v>6666131</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3254,7 +3257,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3264,7 +3267,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3276,6 +3279,26 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3292,36 +3315,44 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127297420</v>
+        <v>127296043</v>
       </c>
       <c r="B23" t="n">
-        <v>96702</v>
+        <v>98456</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -3331,10 +3362,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>505483</v>
+        <v>505457</v>
       </c>
       <c r="R23" t="n">
-        <v>6666164</v>
+        <v>6666067</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3366,7 +3397,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3376,7 +3407,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3388,26 +3419,6 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3424,37 +3435,46 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127297958</v>
+        <v>127295317</v>
       </c>
       <c r="B24" t="n">
-        <v>75136</v>
+        <v>98456</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3462,10 +3482,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505525</v>
+        <v>505401</v>
       </c>
       <c r="R24" t="n">
-        <v>6666131</v>
+        <v>6666036</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3497,7 +3517,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3507,7 +3527,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3519,26 +3539,6 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3555,45 +3555,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295207</v>
+        <v>127298417</v>
       </c>
       <c r="B25" t="n">
-        <v>98450</v>
+        <v>98373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3602,10 +3606,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>505383</v>
+        <v>505547</v>
       </c>
       <c r="R25" t="n">
-        <v>6666039</v>
+        <v>6666020</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3637,7 +3641,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3647,7 +3651,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3678,7 +3682,7 @@
         <v>127294423</v>
       </c>
       <c r="B26" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3798,7 +3802,7 @@
         <v>127295681</v>
       </c>
       <c r="B27" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3915,49 +3919,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127298417</v>
+        <v>127295207</v>
       </c>
       <c r="B28" t="n">
-        <v>98367</v>
+        <v>98456</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>505547</v>
+        <v>505383</v>
       </c>
       <c r="R28" t="n">
-        <v>6666020</v>
+        <v>6666039</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4435,7 +4435,7 @@
         <v>127294722</v>
       </c>
       <c r="B32" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>127295731</v>
       </c>
       <c r="B33" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>127294455</v>
       </c>
       <c r="B34" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         <v>127294976</v>
       </c>
       <c r="B37" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5174,36 +5174,44 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127297810</v>
+        <v>127295841</v>
       </c>
       <c r="B38" t="n">
-        <v>96702</v>
+        <v>98456</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -5213,10 +5221,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>505515</v>
+        <v>505457</v>
       </c>
       <c r="R38" t="n">
-        <v>6666146</v>
+        <v>6666062</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5248,7 +5256,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5258,7 +5266,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5270,26 +5278,6 @@
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5306,10 +5294,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127295841</v>
+        <v>127294730</v>
       </c>
       <c r="B39" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5336,7 +5324,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5353,10 +5341,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>505457</v>
+        <v>505313</v>
       </c>
       <c r="R39" t="n">
-        <v>6666062</v>
+        <v>6666027</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5388,7 +5376,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5398,7 +5386,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5426,44 +5414,36 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127294730</v>
+        <v>127297810</v>
       </c>
       <c r="B40" t="n">
-        <v>98450</v>
+        <v>96708</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
@@ -5473,10 +5453,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>505313</v>
+        <v>505515</v>
       </c>
       <c r="R40" t="n">
-        <v>6666027</v>
+        <v>6666146</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5508,7 +5488,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5518,7 +5498,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5530,6 +5510,26 @@
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5549,7 +5549,7 @@
         <v>127295873</v>
       </c>
       <c r="B41" t="n">
-        <v>96702</v>
+        <v>96708</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5815,36 +5815,44 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127301907</v>
+        <v>127295399</v>
       </c>
       <c r="B43" t="n">
-        <v>96797</v>
+        <v>98456</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1841</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
@@ -5854,10 +5862,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>505491</v>
+        <v>505404</v>
       </c>
       <c r="R43" t="n">
-        <v>6666106</v>
+        <v>6666039</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5887,9 +5895,19 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5901,26 +5919,6 @@
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5937,44 +5935,36 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127295399</v>
+        <v>127301907</v>
       </c>
       <c r="B44" t="n">
-        <v>98450</v>
+        <v>96803</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1841</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
@@ -5984,10 +5974,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>505404</v>
+        <v>505491</v>
       </c>
       <c r="R44" t="n">
-        <v>6666039</v>
+        <v>6666106</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6017,19 +6007,9 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>15:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6041,6 +6021,26 @@
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6057,46 +6057,37 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127295238</v>
+        <v>127298146</v>
       </c>
       <c r="B45" t="n">
-        <v>98450</v>
+        <v>91358</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6104,10 +6095,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>505388</v>
+        <v>505544</v>
       </c>
       <c r="R45" t="n">
-        <v>6666037</v>
+        <v>6666053</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6139,7 +6130,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6149,7 +6140,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6161,6 +6152,21 @@
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6180,7 +6186,7 @@
         <v>127295179</v>
       </c>
       <c r="B46" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6297,37 +6303,46 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127298146</v>
+        <v>127295238</v>
       </c>
       <c r="B47" t="n">
-        <v>91352</v>
+        <v>98456</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6335,10 +6350,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>505544</v>
+        <v>505388</v>
       </c>
       <c r="R47" t="n">
-        <v>6666053</v>
+        <v>6666037</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6370,7 +6385,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6380,7 +6395,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6392,21 +6407,6 @@
       <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6423,37 +6423,46 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127297221</v>
+        <v>127296142</v>
       </c>
       <c r="B48" t="n">
-        <v>75127</v>
+        <v>98456</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6439</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6461,10 +6470,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>505478</v>
+        <v>505465</v>
       </c>
       <c r="R48" t="n">
-        <v>6666109</v>
+        <v>6666072</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6496,7 +6505,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6506,7 +6515,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6518,26 +6527,6 @@
       <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6685,46 +6674,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127296142</v>
+        <v>127297221</v>
       </c>
       <c r="B50" t="n">
-        <v>98450</v>
+        <v>75127</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6439</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6732,10 +6712,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>505465</v>
+        <v>505478</v>
       </c>
       <c r="R50" t="n">
-        <v>6666072</v>
+        <v>6666109</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6767,7 +6747,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6777,7 +6757,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6789,6 +6769,26 @@
       <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 32085-2025 artfynd.xlsx
+++ b/artfynd/A 32085-2025 artfynd.xlsx
@@ -812,37 +812,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127297595</v>
+        <v>127295076</v>
       </c>
       <c r="B3" t="n">
-        <v>75136</v>
+        <v>98459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -850,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505508</v>
+        <v>505375</v>
       </c>
       <c r="R3" t="n">
-        <v>6666170</v>
+        <v>6666039</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,26 +916,6 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -943,46 +932,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127295076</v>
+        <v>127297595</v>
       </c>
       <c r="B4" t="n">
-        <v>98456</v>
+        <v>75139</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -990,10 +970,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505375</v>
+        <v>505508</v>
       </c>
       <c r="R4" t="n">
-        <v>6666039</v>
+        <v>6666170</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1025,7 +1005,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1035,7 +1015,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,6 +1027,26 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1066,7 +1066,7 @@
         <v>127296095</v>
       </c>
       <c r="B5" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>127294425</v>
       </c>
       <c r="B6" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1314,36 +1314,44 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127296163</v>
+        <v>127295189</v>
       </c>
       <c r="B7" t="n">
-        <v>96708</v>
+        <v>98459</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1353,10 +1361,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505465</v>
+        <v>505380</v>
       </c>
       <c r="R7" t="n">
-        <v>6666072</v>
+        <v>6666036</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1388,7 +1396,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1398,7 +1406,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1410,26 +1418,6 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1446,10 +1434,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127295189</v>
+        <v>127294826</v>
       </c>
       <c r="B8" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1464,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1493,10 +1481,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505380</v>
+        <v>505332</v>
       </c>
       <c r="R8" t="n">
-        <v>6666036</v>
+        <v>6666037</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1528,7 +1516,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1538,7 +1526,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1566,10 +1554,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127294826</v>
+        <v>127295345</v>
       </c>
       <c r="B9" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1584,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1613,10 +1601,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505332</v>
+        <v>505402</v>
       </c>
       <c r="R9" t="n">
-        <v>6666037</v>
+        <v>6666038</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1648,7 +1636,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1658,7 +1646,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1686,44 +1674,36 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127295345</v>
+        <v>127296163</v>
       </c>
       <c r="B10" t="n">
-        <v>98456</v>
+        <v>96711</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1733,10 +1713,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505402</v>
+        <v>505465</v>
       </c>
       <c r="R10" t="n">
-        <v>6666038</v>
+        <v>6666072</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1768,7 +1748,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1778,7 +1758,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1790,6 +1770,26 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1809,7 +1809,7 @@
         <v>127294550</v>
       </c>
       <c r="B11" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>127295061</v>
       </c>
       <c r="B12" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>127294748</v>
       </c>
       <c r="B13" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>127297697</v>
       </c>
       <c r="B14" t="n">
-        <v>96708</v>
+        <v>96711</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>127295213</v>
       </c>
       <c r="B15" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>127297651</v>
       </c>
       <c r="B16" t="n">
-        <v>96708</v>
+        <v>96711</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>127297615</v>
       </c>
       <c r="B17" t="n">
-        <v>75136</v>
+        <v>75139</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2681,10 +2681,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127296113</v>
+        <v>127295297</v>
       </c>
       <c r="B18" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505461</v>
+        <v>505400</v>
       </c>
       <c r="R18" t="n">
-        <v>6666073</v>
+        <v>6666034</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2801,10 +2801,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127295297</v>
+        <v>127296113</v>
       </c>
       <c r="B19" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>505400</v>
+        <v>505461</v>
       </c>
       <c r="R19" t="n">
-        <v>6666034</v>
+        <v>6666073</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2924,7 +2924,7 @@
         <v>127295662</v>
       </c>
       <c r="B20" t="n">
-        <v>75136</v>
+        <v>75139</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>127297420</v>
       </c>
       <c r="B21" t="n">
-        <v>96708</v>
+        <v>96711</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>127297958</v>
       </c>
       <c r="B22" t="n">
-        <v>75136</v>
+        <v>75139</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>127296043</v>
       </c>
       <c r="B23" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>127295317</v>
       </c>
       <c r="B24" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>127298417</v>
       </c>
       <c r="B25" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>127294423</v>
       </c>
       <c r="B26" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>127295681</v>
       </c>
       <c r="B27" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>127295207</v>
       </c>
       <c r="B28" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4039,10 +4039,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127296321</v>
+        <v>127298321</v>
       </c>
       <c r="B29" t="n">
-        <v>79052</v>
+        <v>79641</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4050,21 +4050,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4077,10 +4077,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>505487</v>
+        <v>505552</v>
       </c>
       <c r="R29" t="n">
-        <v>6666090</v>
+        <v>6666024</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4137,22 +4137,22 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stump # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4170,37 +4170,46 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127297555</v>
+        <v>127294722</v>
       </c>
       <c r="B30" t="n">
-        <v>75136</v>
+        <v>98459</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4208,10 +4217,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>505501</v>
+        <v>505312</v>
       </c>
       <c r="R30" t="n">
-        <v>6666172</v>
+        <v>6666032</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4243,7 +4252,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4253,7 +4262,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4265,26 +4274,6 @@
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4301,10 +4290,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127298321</v>
+        <v>127296321</v>
       </c>
       <c r="B31" t="n">
-        <v>79638</v>
+        <v>79055</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4312,21 +4301,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4339,10 +4328,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>505552</v>
+        <v>505487</v>
       </c>
       <c r="R31" t="n">
-        <v>6666024</v>
+        <v>6666090</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4374,7 +4363,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4384,7 +4373,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4399,22 +4388,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stump # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4432,46 +4421,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127294722</v>
+        <v>127297555</v>
       </c>
       <c r="B32" t="n">
-        <v>98456</v>
+        <v>75139</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4479,10 +4459,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>505312</v>
+        <v>505501</v>
       </c>
       <c r="R32" t="n">
-        <v>6666032</v>
+        <v>6666172</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4514,7 +4494,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4524,7 +4504,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4536,6 +4516,26 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4555,7 +4555,7 @@
         <v>127295731</v>
       </c>
       <c r="B33" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>127294455</v>
       </c>
       <c r="B34" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>127298053</v>
       </c>
       <c r="B35" t="n">
-        <v>78426</v>
+        <v>78429</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4923,37 +4923,46 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127296758</v>
+        <v>127294976</v>
       </c>
       <c r="B36" t="n">
-        <v>78426</v>
+        <v>98459</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4961,10 +4970,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>505486</v>
+        <v>505373</v>
       </c>
       <c r="R36" t="n">
-        <v>6666108</v>
+        <v>6666042</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4996,7 +5005,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5006,7 +5015,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5018,26 +5027,6 @@
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5054,46 +5043,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127294976</v>
+        <v>127296758</v>
       </c>
       <c r="B37" t="n">
-        <v>98456</v>
+        <v>78429</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5101,10 +5081,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>505373</v>
+        <v>505486</v>
       </c>
       <c r="R37" t="n">
-        <v>6666042</v>
+        <v>6666108</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5136,7 +5116,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5146,7 +5126,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5158,6 +5138,26 @@
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5174,44 +5174,36 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127295841</v>
+        <v>127297810</v>
       </c>
       <c r="B38" t="n">
-        <v>98456</v>
+        <v>96711</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -5221,10 +5213,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>505457</v>
+        <v>505515</v>
       </c>
       <c r="R38" t="n">
-        <v>6666062</v>
+        <v>6666146</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5256,7 +5248,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5266,7 +5258,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5278,6 +5270,26 @@
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5294,10 +5306,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127294730</v>
+        <v>127295841</v>
       </c>
       <c r="B39" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5324,7 +5336,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5341,10 +5353,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>505313</v>
+        <v>505457</v>
       </c>
       <c r="R39" t="n">
-        <v>6666027</v>
+        <v>6666062</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5376,7 +5388,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5386,7 +5398,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5414,36 +5426,44 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127297810</v>
+        <v>127294730</v>
       </c>
       <c r="B40" t="n">
-        <v>96708</v>
+        <v>98459</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
@@ -5453,10 +5473,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>505515</v>
+        <v>505313</v>
       </c>
       <c r="R40" t="n">
-        <v>6666146</v>
+        <v>6666027</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5488,7 +5508,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5498,7 +5518,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5510,26 +5530,6 @@
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5549,7 +5549,7 @@
         <v>127295873</v>
       </c>
       <c r="B41" t="n">
-        <v>96708</v>
+        <v>96711</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>127295399</v>
       </c>
       <c r="B43" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
         <v>127301907</v>
       </c>
       <c r="B44" t="n">
-        <v>96803</v>
+        <v>96806</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
         <v>127298146</v>
       </c>
       <c r="B45" t="n">
-        <v>91358</v>
+        <v>91361</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>127295179</v>
       </c>
       <c r="B46" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         <v>127295238</v>
       </c>
       <c r="B47" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6423,46 +6423,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127296142</v>
+        <v>127296862</v>
       </c>
       <c r="B48" t="n">
-        <v>98456</v>
+        <v>79055</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6470,10 +6461,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>505465</v>
+        <v>505478</v>
       </c>
       <c r="R48" t="n">
-        <v>6666072</v>
+        <v>6666105</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6505,7 +6496,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6515,7 +6506,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6527,6 +6518,26 @@
       <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6543,32 +6554,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127296862</v>
+        <v>127297221</v>
       </c>
       <c r="B49" t="n">
-        <v>79052</v>
+        <v>75130</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>6439</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6584,7 +6595,7 @@
         <v>505478</v>
       </c>
       <c r="R49" t="n">
-        <v>6666105</v>
+        <v>6666109</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6616,7 +6627,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6626,7 +6637,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6641,22 +6652,22 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6674,37 +6685,46 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127297221</v>
+        <v>127296142</v>
       </c>
       <c r="B50" t="n">
-        <v>75127</v>
+        <v>98459</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6439</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6712,10 +6732,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>505478</v>
+        <v>505465</v>
       </c>
       <c r="R50" t="n">
-        <v>6666109</v>
+        <v>6666072</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6747,7 +6767,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6757,7 +6777,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6769,26 +6789,6 @@
       <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 32085-2025 artfynd.xlsx
+++ b/artfynd/A 32085-2025 artfynd.xlsx
@@ -812,46 +812,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127295076</v>
+        <v>127297595</v>
       </c>
       <c r="B3" t="n">
-        <v>98459</v>
+        <v>75145</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -859,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505375</v>
+        <v>505508</v>
       </c>
       <c r="R3" t="n">
-        <v>6666039</v>
+        <v>6666170</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +895,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,6 +907,26 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -932,37 +943,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127297595</v>
+        <v>127295076</v>
       </c>
       <c r="B4" t="n">
-        <v>75139</v>
+        <v>98467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -970,10 +990,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505508</v>
+        <v>505375</v>
       </c>
       <c r="R4" t="n">
-        <v>6666170</v>
+        <v>6666039</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,7 +1025,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1015,7 +1035,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,26 +1047,6 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1066,7 +1066,7 @@
         <v>127296095</v>
       </c>
       <c r="B5" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>127294425</v>
       </c>
       <c r="B6" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1314,44 +1314,36 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127295189</v>
+        <v>127296163</v>
       </c>
       <c r="B7" t="n">
-        <v>98459</v>
+        <v>96719</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1361,10 +1353,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505380</v>
+        <v>505465</v>
       </c>
       <c r="R7" t="n">
-        <v>6666036</v>
+        <v>6666072</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1396,7 +1388,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1406,7 +1398,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1418,6 +1410,26 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1434,10 +1446,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127294826</v>
+        <v>127295189</v>
       </c>
       <c r="B8" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1464,7 +1476,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1481,10 +1493,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505332</v>
+        <v>505380</v>
       </c>
       <c r="R8" t="n">
-        <v>6666037</v>
+        <v>6666036</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1516,7 +1528,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1526,7 +1538,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1554,10 +1566,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127295345</v>
+        <v>127294826</v>
       </c>
       <c r="B9" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1596,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1601,10 +1613,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505402</v>
+        <v>505332</v>
       </c>
       <c r="R9" t="n">
-        <v>6666038</v>
+        <v>6666037</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1636,7 +1648,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1646,7 +1658,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1674,36 +1686,44 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127296163</v>
+        <v>127295345</v>
       </c>
       <c r="B10" t="n">
-        <v>96711</v>
+        <v>98467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1713,10 +1733,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505465</v>
+        <v>505402</v>
       </c>
       <c r="R10" t="n">
-        <v>6666072</v>
+        <v>6666038</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1748,7 +1768,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1758,7 +1778,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1770,26 +1790,6 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1806,44 +1806,36 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127294550</v>
+        <v>127297697</v>
       </c>
       <c r="B11" t="n">
-        <v>98459</v>
+        <v>96719</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1853,10 +1845,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505307</v>
+        <v>505514</v>
       </c>
       <c r="R11" t="n">
-        <v>6666031</v>
+        <v>6666167</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1888,7 +1880,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1898,7 +1890,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1910,6 +1902,26 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1926,10 +1938,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127295061</v>
+        <v>127294550</v>
       </c>
       <c r="B12" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1956,7 +1968,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1973,10 +1985,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505372</v>
+        <v>505307</v>
       </c>
       <c r="R12" t="n">
-        <v>6666038</v>
+        <v>6666031</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2008,7 +2020,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2018,7 +2030,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2046,10 +2058,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127294748</v>
+        <v>127295061</v>
       </c>
       <c r="B13" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2076,7 +2088,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2093,10 +2105,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505318</v>
+        <v>505372</v>
       </c>
       <c r="R13" t="n">
-        <v>6666032</v>
+        <v>6666038</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2128,7 +2140,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2138,7 +2150,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2166,36 +2178,44 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127297697</v>
+        <v>127294748</v>
       </c>
       <c r="B14" t="n">
-        <v>96711</v>
+        <v>98467</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2205,10 +2225,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505514</v>
+        <v>505318</v>
       </c>
       <c r="R14" t="n">
-        <v>6666167</v>
+        <v>6666032</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2240,7 +2260,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2250,7 +2270,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2262,26 +2282,6 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2301,7 +2301,7 @@
         <v>127295213</v>
       </c>
       <c r="B15" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2418,10 +2418,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127297651</v>
+        <v>127297615</v>
       </c>
       <c r="B16" t="n">
-        <v>96711</v>
+        <v>75145</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2429,27 +2429,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2457,7 +2456,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505512</v>
+        <v>505511</v>
       </c>
       <c r="R16" t="n">
         <v>6666168</v>
@@ -2492,7 +2491,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2502,7 +2501,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2527,12 +2526,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2550,10 +2549,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127297615</v>
+        <v>127297651</v>
       </c>
       <c r="B17" t="n">
-        <v>75139</v>
+        <v>96719</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2561,26 +2560,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>308</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505511</v>
+        <v>505512</v>
       </c>
       <c r="R17" t="n">
         <v>6666168</v>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2658,12 +2658,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2684,7 +2684,7 @@
         <v>127295297</v>
       </c>
       <c r="B18" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>127296113</v>
       </c>
       <c r="B19" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>127295662</v>
       </c>
       <c r="B20" t="n">
-        <v>75139</v>
+        <v>75145</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>127297420</v>
       </c>
       <c r="B21" t="n">
-        <v>96711</v>
+        <v>96719</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>127297958</v>
       </c>
       <c r="B22" t="n">
-        <v>75139</v>
+        <v>75145</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>127296043</v>
       </c>
       <c r="B23" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>127295317</v>
       </c>
       <c r="B24" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3555,49 +3555,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127298417</v>
+        <v>127294423</v>
       </c>
       <c r="B25" t="n">
-        <v>98376</v>
+        <v>98467</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3606,10 +3602,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>505547</v>
+        <v>505296</v>
       </c>
       <c r="R25" t="n">
-        <v>6666020</v>
+        <v>6666023</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3641,7 +3637,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3651,7 +3647,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3679,10 +3675,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127294423</v>
+        <v>127295681</v>
       </c>
       <c r="B26" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3709,7 +3705,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3726,10 +3722,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>505296</v>
+        <v>505425</v>
       </c>
       <c r="R26" t="n">
-        <v>6666023</v>
+        <v>6666033</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3761,7 +3757,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3771,7 +3767,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3799,10 +3795,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295681</v>
+        <v>127295207</v>
       </c>
       <c r="B27" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3829,7 +3825,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3846,10 +3842,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>505425</v>
+        <v>505383</v>
       </c>
       <c r="R27" t="n">
-        <v>6666033</v>
+        <v>6666039</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3881,7 +3877,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3891,7 +3887,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3919,45 +3915,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127295207</v>
+        <v>127298417</v>
       </c>
       <c r="B28" t="n">
-        <v>98459</v>
+        <v>98384</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>505383</v>
+        <v>505547</v>
       </c>
       <c r="R28" t="n">
-        <v>6666039</v>
+        <v>6666020</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4042,7 +4042,7 @@
         <v>127298321</v>
       </c>
       <c r="B29" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4170,46 +4170,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127294722</v>
+        <v>127296321</v>
       </c>
       <c r="B30" t="n">
-        <v>98459</v>
+        <v>79061</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4217,10 +4208,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>505312</v>
+        <v>505487</v>
       </c>
       <c r="R30" t="n">
-        <v>6666032</v>
+        <v>6666090</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4252,7 +4243,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4262,7 +4253,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4274,6 +4265,26 @@
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4290,10 +4301,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127296321</v>
+        <v>127297555</v>
       </c>
       <c r="B31" t="n">
-        <v>79055</v>
+        <v>75145</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4301,21 +4312,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4328,10 +4339,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>505487</v>
+        <v>505501</v>
       </c>
       <c r="R31" t="n">
-        <v>6666090</v>
+        <v>6666172</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4363,7 +4374,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4373,7 +4384,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4388,22 +4399,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4421,37 +4432,46 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127297555</v>
+        <v>127294722</v>
       </c>
       <c r="B32" t="n">
-        <v>75139</v>
+        <v>98467</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4459,10 +4479,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>505501</v>
+        <v>505312</v>
       </c>
       <c r="R32" t="n">
-        <v>6666172</v>
+        <v>6666032</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4494,7 +4514,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4504,7 +4524,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4516,26 +4536,6 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4555,7 +4555,7 @@
         <v>127295731</v>
       </c>
       <c r="B33" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>127294455</v>
       </c>
       <c r="B34" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>127298053</v>
       </c>
       <c r="B35" t="n">
-        <v>78429</v>
+        <v>78435</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4923,46 +4923,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127294976</v>
+        <v>127296758</v>
       </c>
       <c r="B36" t="n">
-        <v>98459</v>
+        <v>78435</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4970,10 +4961,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>505373</v>
+        <v>505486</v>
       </c>
       <c r="R36" t="n">
-        <v>6666042</v>
+        <v>6666108</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5005,7 +4996,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5015,7 +5006,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5027,6 +5018,26 @@
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5043,37 +5054,46 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127296758</v>
+        <v>127294976</v>
       </c>
       <c r="B37" t="n">
-        <v>78429</v>
+        <v>98467</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5081,10 +5101,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>505486</v>
+        <v>505373</v>
       </c>
       <c r="R37" t="n">
-        <v>6666108</v>
+        <v>6666042</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5116,7 +5136,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5126,7 +5146,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5138,26 +5158,6 @@
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5177,7 +5177,7 @@
         <v>127297810</v>
       </c>
       <c r="B38" t="n">
-        <v>96711</v>
+        <v>96719</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>127295841</v>
       </c>
       <c r="B39" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>127294730</v>
       </c>
       <c r="B40" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         <v>127295873</v>
       </c>
       <c r="B41" t="n">
-        <v>96711</v>
+        <v>96719</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5815,44 +5815,36 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127295399</v>
+        <v>127301907</v>
       </c>
       <c r="B43" t="n">
-        <v>98459</v>
+        <v>96814</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1841</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
@@ -5862,10 +5854,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>505404</v>
+        <v>505491</v>
       </c>
       <c r="R43" t="n">
-        <v>6666039</v>
+        <v>6666106</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5895,19 +5887,9 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>15:03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5919,6 +5901,26 @@
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5935,36 +5937,44 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127301907</v>
+        <v>127295399</v>
       </c>
       <c r="B44" t="n">
-        <v>96806</v>
+        <v>98467</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1841</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
@@ -5974,10 +5984,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>505491</v>
+        <v>505404</v>
       </c>
       <c r="R44" t="n">
-        <v>6666106</v>
+        <v>6666039</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6007,9 +6017,19 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6021,26 +6041,6 @@
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6060,7 +6060,7 @@
         <v>127298146</v>
       </c>
       <c r="B45" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>127295179</v>
       </c>
       <c r="B46" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         <v>127295238</v>
       </c>
       <c r="B47" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6423,37 +6423,46 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127296862</v>
+        <v>127296142</v>
       </c>
       <c r="B48" t="n">
-        <v>79055</v>
+        <v>98467</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6461,10 +6470,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>505478</v>
+        <v>505465</v>
       </c>
       <c r="R48" t="n">
-        <v>6666105</v>
+        <v>6666072</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6496,7 +6505,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6506,7 +6515,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6518,26 +6527,6 @@
       <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6557,7 +6546,7 @@
         <v>127297221</v>
       </c>
       <c r="B49" t="n">
-        <v>75130</v>
+        <v>75136</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6685,46 +6674,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127296142</v>
+        <v>127296862</v>
       </c>
       <c r="B50" t="n">
-        <v>98459</v>
+        <v>79061</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6732,10 +6712,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>505465</v>
+        <v>505478</v>
       </c>
       <c r="R50" t="n">
-        <v>6666072</v>
+        <v>6666105</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6767,7 +6747,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6777,7 +6757,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6789,6 +6769,26 @@
       <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 32085-2025 artfynd.xlsx
+++ b/artfynd/A 32085-2025 artfynd.xlsx
@@ -812,37 +812,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127297595</v>
+        <v>127295076</v>
       </c>
       <c r="B3" t="n">
-        <v>75145</v>
+        <v>98468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -850,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505508</v>
+        <v>505375</v>
       </c>
       <c r="R3" t="n">
-        <v>6666170</v>
+        <v>6666039</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,26 +916,6 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -943,46 +932,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127295076</v>
+        <v>127297595</v>
       </c>
       <c r="B4" t="n">
-        <v>98467</v>
+        <v>75145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -990,10 +970,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505375</v>
+        <v>505508</v>
       </c>
       <c r="R4" t="n">
-        <v>6666039</v>
+        <v>6666170</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1025,7 +1005,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1035,7 +1015,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,6 +1027,26 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1205,7 +1205,7 @@
         <v>127294425</v>
       </c>
       <c r="B6" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>127296163</v>
       </c>
       <c r="B7" t="n">
-        <v>96719</v>
+        <v>96720</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>127295189</v>
       </c>
       <c r="B8" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>127294826</v>
       </c>
       <c r="B9" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>127295345</v>
       </c>
       <c r="B10" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>127297697</v>
       </c>
       <c r="B11" t="n">
-        <v>96719</v>
+        <v>96720</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>127294550</v>
       </c>
       <c r="B12" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>127295061</v>
       </c>
       <c r="B13" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>127294748</v>
       </c>
       <c r="B14" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>127295213</v>
       </c>
       <c r="B15" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2418,37 +2418,46 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127297615</v>
+        <v>127295297</v>
       </c>
       <c r="B16" t="n">
-        <v>75145</v>
+        <v>98468</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2456,10 +2465,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505511</v>
+        <v>505400</v>
       </c>
       <c r="R16" t="n">
-        <v>6666168</v>
+        <v>6666034</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2491,7 +2500,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2501,7 +2510,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2513,26 +2522,6 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2549,36 +2538,44 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127297651</v>
+        <v>127296113</v>
       </c>
       <c r="B17" t="n">
-        <v>96719</v>
+        <v>98468</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2588,10 +2585,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505512</v>
+        <v>505461</v>
       </c>
       <c r="R17" t="n">
-        <v>6666168</v>
+        <v>6666073</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2623,7 +2620,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2633,7 +2630,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2645,26 +2642,6 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2681,44 +2658,36 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127295297</v>
+        <v>127297651</v>
       </c>
       <c r="B18" t="n">
-        <v>98467</v>
+        <v>96720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2728,10 +2697,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505400</v>
+        <v>505512</v>
       </c>
       <c r="R18" t="n">
-        <v>6666034</v>
+        <v>6666168</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2763,7 +2732,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2773,7 +2742,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2785,6 +2754,26 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2801,46 +2790,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127296113</v>
+        <v>127297615</v>
       </c>
       <c r="B19" t="n">
-        <v>98467</v>
+        <v>75145</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2848,10 +2828,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>505461</v>
+        <v>505511</v>
       </c>
       <c r="R19" t="n">
-        <v>6666073</v>
+        <v>6666168</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2883,7 +2863,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2893,7 +2873,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2905,6 +2885,26 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3055,7 +3055,7 @@
         <v>127297420</v>
       </c>
       <c r="B21" t="n">
-        <v>96719</v>
+        <v>96720</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>127296043</v>
       </c>
       <c r="B23" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>127295317</v>
       </c>
       <c r="B24" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3555,45 +3555,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127294423</v>
+        <v>127298417</v>
       </c>
       <c r="B25" t="n">
-        <v>98467</v>
+        <v>98385</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3602,10 +3606,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>505296</v>
+        <v>505547</v>
       </c>
       <c r="R25" t="n">
-        <v>6666023</v>
+        <v>6666020</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3637,7 +3641,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3647,7 +3651,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3675,10 +3679,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127295681</v>
+        <v>127294423</v>
       </c>
       <c r="B26" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3705,7 +3709,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3722,10 +3726,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>505425</v>
+        <v>505296</v>
       </c>
       <c r="R26" t="n">
-        <v>6666033</v>
+        <v>6666023</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3757,7 +3761,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3767,7 +3771,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3795,10 +3799,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295207</v>
+        <v>127295681</v>
       </c>
       <c r="B27" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3825,7 +3829,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3842,10 +3846,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>505383</v>
+        <v>505425</v>
       </c>
       <c r="R27" t="n">
-        <v>6666039</v>
+        <v>6666033</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3877,7 +3881,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3887,7 +3891,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3915,49 +3919,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127298417</v>
+        <v>127295207</v>
       </c>
       <c r="B28" t="n">
-        <v>98384</v>
+        <v>98468</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>505547</v>
+        <v>505383</v>
       </c>
       <c r="R28" t="n">
-        <v>6666020</v>
+        <v>6666039</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4435,7 +4435,7 @@
         <v>127294722</v>
       </c>
       <c r="B32" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>127295731</v>
       </c>
       <c r="B33" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>127294455</v>
       </c>
       <c r="B34" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         <v>127294976</v>
       </c>
       <c r="B37" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5174,36 +5174,44 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127297810</v>
+        <v>127295841</v>
       </c>
       <c r="B38" t="n">
-        <v>96719</v>
+        <v>98468</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -5213,10 +5221,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>505515</v>
+        <v>505457</v>
       </c>
       <c r="R38" t="n">
-        <v>6666146</v>
+        <v>6666062</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5248,7 +5256,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5258,7 +5266,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5270,26 +5278,6 @@
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5306,10 +5294,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127295841</v>
+        <v>127294730</v>
       </c>
       <c r="B39" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5336,7 +5324,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5353,10 +5341,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>505457</v>
+        <v>505313</v>
       </c>
       <c r="R39" t="n">
-        <v>6666062</v>
+        <v>6666027</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5388,7 +5376,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5398,7 +5386,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5426,44 +5414,36 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127294730</v>
+        <v>127297810</v>
       </c>
       <c r="B40" t="n">
-        <v>98467</v>
+        <v>96720</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
@@ -5473,10 +5453,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>505313</v>
+        <v>505515</v>
       </c>
       <c r="R40" t="n">
-        <v>6666027</v>
+        <v>6666146</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5508,7 +5488,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5518,7 +5498,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5530,6 +5510,26 @@
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5549,7 +5549,7 @@
         <v>127295873</v>
       </c>
       <c r="B41" t="n">
-        <v>96719</v>
+        <v>96720</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5815,36 +5815,44 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127301907</v>
+        <v>127295399</v>
       </c>
       <c r="B43" t="n">
-        <v>96814</v>
+        <v>98468</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1841</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
@@ -5854,10 +5862,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>505491</v>
+        <v>505404</v>
       </c>
       <c r="R43" t="n">
-        <v>6666106</v>
+        <v>6666039</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5887,9 +5895,19 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5901,26 +5919,6 @@
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5937,44 +5935,36 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127295399</v>
+        <v>127301907</v>
       </c>
       <c r="B44" t="n">
-        <v>98467</v>
+        <v>96815</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1841</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
@@ -5984,10 +5974,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>505404</v>
+        <v>505491</v>
       </c>
       <c r="R44" t="n">
-        <v>6666039</v>
+        <v>6666106</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6017,19 +6007,9 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>15:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6041,6 +6021,26 @@
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6060,7 +6060,7 @@
         <v>127298146</v>
       </c>
       <c r="B45" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>127295179</v>
       </c>
       <c r="B46" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         <v>127295238</v>
       </c>
       <c r="B47" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6423,46 +6423,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127296142</v>
+        <v>127297221</v>
       </c>
       <c r="B48" t="n">
-        <v>98467</v>
+        <v>75136</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6439</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6470,10 +6461,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>505465</v>
+        <v>505478</v>
       </c>
       <c r="R48" t="n">
-        <v>6666072</v>
+        <v>6666109</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6505,7 +6496,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6515,7 +6506,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6527,6 +6518,26 @@
       <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6543,32 +6554,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127297221</v>
+        <v>127296862</v>
       </c>
       <c r="B49" t="n">
-        <v>75136</v>
+        <v>79061</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6439</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6584,7 +6595,7 @@
         <v>505478</v>
       </c>
       <c r="R49" t="n">
-        <v>6666109</v>
+        <v>6666105</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6616,7 +6627,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6626,7 +6637,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6641,22 +6652,22 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6674,37 +6685,46 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127296862</v>
+        <v>127296142</v>
       </c>
       <c r="B50" t="n">
-        <v>79061</v>
+        <v>98468</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6712,10 +6732,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>505478</v>
+        <v>505465</v>
       </c>
       <c r="R50" t="n">
-        <v>6666105</v>
+        <v>6666072</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6747,7 +6767,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6757,7 +6777,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6769,26 +6789,6 @@
       <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 32085-2025 artfynd.xlsx
+++ b/artfynd/A 32085-2025 artfynd.xlsx
@@ -812,46 +812,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127295076</v>
+        <v>127297595</v>
       </c>
       <c r="B3" t="n">
-        <v>98468</v>
+        <v>75145</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -859,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505375</v>
+        <v>505508</v>
       </c>
       <c r="R3" t="n">
-        <v>6666039</v>
+        <v>6666170</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +895,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,6 +907,26 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -932,37 +943,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127297595</v>
+        <v>127295076</v>
       </c>
       <c r="B4" t="n">
-        <v>75145</v>
+        <v>98468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -970,10 +990,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505508</v>
+        <v>505375</v>
       </c>
       <c r="R4" t="n">
-        <v>6666170</v>
+        <v>6666039</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,7 +1025,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1015,7 +1035,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,26 +1047,6 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1314,36 +1314,44 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127296163</v>
+        <v>127295189</v>
       </c>
       <c r="B7" t="n">
-        <v>96720</v>
+        <v>98468</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1353,10 +1361,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505465</v>
+        <v>505380</v>
       </c>
       <c r="R7" t="n">
-        <v>6666072</v>
+        <v>6666036</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1388,7 +1396,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1398,7 +1406,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1410,26 +1418,6 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1446,7 +1434,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127295189</v>
+        <v>127294826</v>
       </c>
       <c r="B8" t="n">
         <v>98468</v>
@@ -1476,7 +1464,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1493,10 +1481,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505380</v>
+        <v>505332</v>
       </c>
       <c r="R8" t="n">
-        <v>6666036</v>
+        <v>6666037</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1528,7 +1516,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1538,7 +1526,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1566,7 +1554,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127294826</v>
+        <v>127295345</v>
       </c>
       <c r="B9" t="n">
         <v>98468</v>
@@ -1596,7 +1584,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1613,10 +1601,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505332</v>
+        <v>505402</v>
       </c>
       <c r="R9" t="n">
-        <v>6666037</v>
+        <v>6666038</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1648,7 +1636,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1658,7 +1646,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1686,44 +1674,36 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127295345</v>
+        <v>127296163</v>
       </c>
       <c r="B10" t="n">
-        <v>98468</v>
+        <v>96720</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1733,10 +1713,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505402</v>
+        <v>505465</v>
       </c>
       <c r="R10" t="n">
-        <v>6666038</v>
+        <v>6666072</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1768,7 +1748,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1778,7 +1758,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1790,6 +1770,26 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -3052,36 +3052,44 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127297420</v>
+        <v>127296043</v>
       </c>
       <c r="B21" t="n">
-        <v>96720</v>
+        <v>98468</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -3091,10 +3099,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>505483</v>
+        <v>505457</v>
       </c>
       <c r="R21" t="n">
-        <v>6666164</v>
+        <v>6666067</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3126,7 +3134,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3136,7 +3144,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3148,26 +3156,6 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3184,37 +3172,46 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127297958</v>
+        <v>127295317</v>
       </c>
       <c r="B22" t="n">
-        <v>75145</v>
+        <v>98468</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3222,10 +3219,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>505525</v>
+        <v>505401</v>
       </c>
       <c r="R22" t="n">
-        <v>6666131</v>
+        <v>6666036</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3257,7 +3254,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3267,7 +3264,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3279,26 +3276,6 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3315,44 +3292,36 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127296043</v>
+        <v>127297420</v>
       </c>
       <c r="B23" t="n">
-        <v>98468</v>
+        <v>96720</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -3362,10 +3331,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>505457</v>
+        <v>505483</v>
       </c>
       <c r="R23" t="n">
-        <v>6666067</v>
+        <v>6666164</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3397,7 +3366,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3407,7 +3376,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3419,6 +3388,26 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3435,46 +3424,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295317</v>
+        <v>127297958</v>
       </c>
       <c r="B24" t="n">
-        <v>98468</v>
+        <v>75145</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3482,10 +3462,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505401</v>
+        <v>505525</v>
       </c>
       <c r="R24" t="n">
-        <v>6666036</v>
+        <v>6666131</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3517,7 +3497,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3527,7 +3507,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3539,6 +3519,26 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -4923,37 +4923,46 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127296758</v>
+        <v>127294976</v>
       </c>
       <c r="B36" t="n">
-        <v>78435</v>
+        <v>98468</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4961,10 +4970,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>505486</v>
+        <v>505373</v>
       </c>
       <c r="R36" t="n">
-        <v>6666108</v>
+        <v>6666042</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4996,7 +5005,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5006,7 +5015,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5018,26 +5027,6 @@
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5054,46 +5043,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127294976</v>
+        <v>127296758</v>
       </c>
       <c r="B37" t="n">
-        <v>98468</v>
+        <v>78435</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5101,10 +5081,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>505373</v>
+        <v>505486</v>
       </c>
       <c r="R37" t="n">
-        <v>6666042</v>
+        <v>6666108</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5136,7 +5116,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5146,7 +5126,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5158,6 +5138,26 @@
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5174,44 +5174,36 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127295841</v>
+        <v>127297810</v>
       </c>
       <c r="B38" t="n">
-        <v>98468</v>
+        <v>96720</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -5221,10 +5213,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>505457</v>
+        <v>505515</v>
       </c>
       <c r="R38" t="n">
-        <v>6666062</v>
+        <v>6666146</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5256,7 +5248,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5266,7 +5258,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5278,6 +5270,26 @@
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5294,7 +5306,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127294730</v>
+        <v>127295841</v>
       </c>
       <c r="B39" t="n">
         <v>98468</v>
@@ -5324,7 +5336,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5341,10 +5353,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>505313</v>
+        <v>505457</v>
       </c>
       <c r="R39" t="n">
-        <v>6666027</v>
+        <v>6666062</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5376,7 +5388,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5386,7 +5398,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5414,36 +5426,44 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127297810</v>
+        <v>127294730</v>
       </c>
       <c r="B40" t="n">
-        <v>96720</v>
+        <v>98468</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
@@ -5453,10 +5473,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>505515</v>
+        <v>505313</v>
       </c>
       <c r="R40" t="n">
-        <v>6666146</v>
+        <v>6666027</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5488,7 +5508,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5498,7 +5518,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5510,26 +5530,6 @@
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -6554,37 +6554,46 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127296862</v>
+        <v>127296142</v>
       </c>
       <c r="B49" t="n">
-        <v>79061</v>
+        <v>98468</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6592,10 +6601,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>505478</v>
+        <v>505465</v>
       </c>
       <c r="R49" t="n">
-        <v>6666105</v>
+        <v>6666072</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6627,7 +6636,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6637,7 +6646,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6649,26 +6658,6 @@
       <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6685,46 +6674,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127296142</v>
+        <v>127296862</v>
       </c>
       <c r="B50" t="n">
-        <v>98468</v>
+        <v>79061</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6732,10 +6712,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>505465</v>
+        <v>505478</v>
       </c>
       <c r="R50" t="n">
-        <v>6666072</v>
+        <v>6666105</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6767,7 +6747,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6777,7 +6757,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6789,6 +6769,26 @@
       <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 32085-2025 artfynd.xlsx
+++ b/artfynd/A 32085-2025 artfynd.xlsx
@@ -812,37 +812,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127297595</v>
+        <v>127295076</v>
       </c>
       <c r="B3" t="n">
-        <v>75145</v>
+        <v>98469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -850,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505508</v>
+        <v>505375</v>
       </c>
       <c r="R3" t="n">
-        <v>6666170</v>
+        <v>6666039</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,26 +916,6 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -943,46 +932,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127295076</v>
+        <v>127297595</v>
       </c>
       <c r="B4" t="n">
-        <v>98468</v>
+        <v>75145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -990,10 +970,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505375</v>
+        <v>505508</v>
       </c>
       <c r="R4" t="n">
-        <v>6666039</v>
+        <v>6666170</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1025,7 +1005,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1035,7 +1015,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,6 +1027,26 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1063,45 +1063,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127296095</v>
+        <v>127294425</v>
       </c>
       <c r="B5" t="n">
-        <v>79061</v>
+        <v>97346</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1109,10 +1102,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505457</v>
+        <v>505296</v>
       </c>
       <c r="R5" t="n">
-        <v>6666067</v>
+        <v>6666023</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1137,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1154,7 +1147,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,26 +1159,6 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Dead branch  # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1202,38 +1175,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127294425</v>
+        <v>127296095</v>
       </c>
       <c r="B6" t="n">
-        <v>97345</v>
+        <v>79061</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1241,10 +1221,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505296</v>
+        <v>505457</v>
       </c>
       <c r="R6" t="n">
-        <v>6666023</v>
+        <v>6666067</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1276,7 +1256,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1286,7 +1266,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1298,6 +1278,26 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Dead branch  # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1314,44 +1314,36 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127295189</v>
+        <v>127296163</v>
       </c>
       <c r="B7" t="n">
-        <v>98468</v>
+        <v>96721</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1361,10 +1353,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505380</v>
+        <v>505465</v>
       </c>
       <c r="R7" t="n">
-        <v>6666036</v>
+        <v>6666072</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1396,7 +1388,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1406,7 +1398,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1418,6 +1410,26 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1434,10 +1446,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127294826</v>
+        <v>127295189</v>
       </c>
       <c r="B8" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1464,7 +1476,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1481,10 +1493,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505332</v>
+        <v>505380</v>
       </c>
       <c r="R8" t="n">
-        <v>6666037</v>
+        <v>6666036</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1516,7 +1528,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1526,7 +1538,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1554,10 +1566,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127295345</v>
+        <v>127294826</v>
       </c>
       <c r="B9" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1596,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1601,10 +1613,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505402</v>
+        <v>505332</v>
       </c>
       <c r="R9" t="n">
-        <v>6666038</v>
+        <v>6666037</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1636,7 +1648,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1646,7 +1658,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1674,36 +1686,44 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127296163</v>
+        <v>127295345</v>
       </c>
       <c r="B10" t="n">
-        <v>96720</v>
+        <v>98469</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1713,10 +1733,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505465</v>
+        <v>505402</v>
       </c>
       <c r="R10" t="n">
-        <v>6666072</v>
+        <v>6666038</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1748,7 +1768,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1758,7 +1778,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1770,26 +1790,6 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1809,7 +1809,7 @@
         <v>127297697</v>
       </c>
       <c r="B11" t="n">
-        <v>96720</v>
+        <v>96721</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1938,10 +1938,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127294550</v>
+        <v>127294748</v>
       </c>
       <c r="B12" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1985,10 +1985,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505307</v>
+        <v>505318</v>
       </c>
       <c r="R12" t="n">
-        <v>6666031</v>
+        <v>6666032</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2058,10 +2058,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127295061</v>
+        <v>127294550</v>
       </c>
       <c r="B13" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505372</v>
+        <v>505307</v>
       </c>
       <c r="R13" t="n">
-        <v>6666038</v>
+        <v>6666031</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2178,10 +2178,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127294748</v>
+        <v>127295061</v>
       </c>
       <c r="B14" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2225,10 +2225,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505318</v>
+        <v>505372</v>
       </c>
       <c r="R14" t="n">
-        <v>6666032</v>
+        <v>6666038</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2301,7 +2301,7 @@
         <v>127295213</v>
       </c>
       <c r="B15" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2418,46 +2418,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127295297</v>
+        <v>127297615</v>
       </c>
       <c r="B16" t="n">
-        <v>98468</v>
+        <v>75145</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2465,10 +2456,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505400</v>
+        <v>505511</v>
       </c>
       <c r="R16" t="n">
-        <v>6666034</v>
+        <v>6666168</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2500,7 +2491,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2510,7 +2501,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2522,6 +2513,26 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2538,44 +2549,36 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127296113</v>
+        <v>127297651</v>
       </c>
       <c r="B17" t="n">
-        <v>98468</v>
+        <v>96721</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2585,10 +2588,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505461</v>
+        <v>505512</v>
       </c>
       <c r="R17" t="n">
-        <v>6666073</v>
+        <v>6666168</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2620,7 +2623,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2630,7 +2633,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2642,6 +2645,26 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2658,36 +2681,44 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127297651</v>
+        <v>127295297</v>
       </c>
       <c r="B18" t="n">
-        <v>96720</v>
+        <v>98469</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2697,10 +2728,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505512</v>
+        <v>505400</v>
       </c>
       <c r="R18" t="n">
-        <v>6666168</v>
+        <v>6666034</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2732,7 +2763,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2742,7 +2773,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2754,26 +2785,6 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2790,37 +2801,46 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127297615</v>
+        <v>127296113</v>
       </c>
       <c r="B19" t="n">
-        <v>75145</v>
+        <v>98469</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2828,10 +2848,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>505511</v>
+        <v>505461</v>
       </c>
       <c r="R19" t="n">
-        <v>6666168</v>
+        <v>6666073</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2863,7 +2883,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2873,7 +2893,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2885,26 +2905,6 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3052,44 +3052,36 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127296043</v>
+        <v>127297420</v>
       </c>
       <c r="B21" t="n">
-        <v>98468</v>
+        <v>96721</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -3099,10 +3091,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>505457</v>
+        <v>505483</v>
       </c>
       <c r="R21" t="n">
-        <v>6666067</v>
+        <v>6666164</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3134,7 +3126,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3144,7 +3136,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3156,6 +3148,26 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3172,46 +3184,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295317</v>
+        <v>127297958</v>
       </c>
       <c r="B22" t="n">
-        <v>98468</v>
+        <v>75145</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3219,10 +3222,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>505401</v>
+        <v>505525</v>
       </c>
       <c r="R22" t="n">
-        <v>6666036</v>
+        <v>6666131</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3254,7 +3257,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3264,7 +3267,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3276,6 +3279,26 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3292,36 +3315,44 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127297420</v>
+        <v>127296043</v>
       </c>
       <c r="B23" t="n">
-        <v>96720</v>
+        <v>98469</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -3331,10 +3362,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>505483</v>
+        <v>505457</v>
       </c>
       <c r="R23" t="n">
-        <v>6666164</v>
+        <v>6666067</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3366,7 +3397,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3376,7 +3407,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3388,26 +3419,6 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3424,37 +3435,46 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127297958</v>
+        <v>127295317</v>
       </c>
       <c r="B24" t="n">
-        <v>75145</v>
+        <v>98469</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3462,10 +3482,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505525</v>
+        <v>505401</v>
       </c>
       <c r="R24" t="n">
-        <v>6666131</v>
+        <v>6666036</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3497,7 +3517,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3507,7 +3527,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3519,26 +3539,6 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3558,7 +3558,7 @@
         <v>127298417</v>
       </c>
       <c r="B25" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>127294423</v>
       </c>
       <c r="B26" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>127295681</v>
       </c>
       <c r="B27" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>127295207</v>
       </c>
       <c r="B28" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4039,10 +4039,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127298321</v>
+        <v>127296321</v>
       </c>
       <c r="B29" t="n">
-        <v>79647</v>
+        <v>79061</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4050,21 +4050,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4077,10 +4077,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>505552</v>
+        <v>505487</v>
       </c>
       <c r="R29" t="n">
-        <v>6666024</v>
+        <v>6666090</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4137,22 +4137,22 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stump # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4170,10 +4170,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127296321</v>
+        <v>127297555</v>
       </c>
       <c r="B30" t="n">
-        <v>79061</v>
+        <v>75145</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4181,21 +4181,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>505487</v>
+        <v>505501</v>
       </c>
       <c r="R30" t="n">
-        <v>6666090</v>
+        <v>6666172</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4268,22 +4268,22 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4301,10 +4301,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127297555</v>
+        <v>127298321</v>
       </c>
       <c r="B31" t="n">
-        <v>75145</v>
+        <v>79647</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4312,21 +4312,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>308</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4339,10 +4339,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>505501</v>
+        <v>505552</v>
       </c>
       <c r="R31" t="n">
-        <v>6666172</v>
+        <v>6666024</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Stump # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4435,7 +4435,7 @@
         <v>127294722</v>
       </c>
       <c r="B32" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4552,10 +4552,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127295731</v>
+        <v>127294455</v>
       </c>
       <c r="B33" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>505443</v>
+        <v>505303</v>
       </c>
       <c r="R33" t="n">
-        <v>6666049</v>
+        <v>6666020</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4672,10 +4672,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127294455</v>
+        <v>127295731</v>
       </c>
       <c r="B34" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>505303</v>
+        <v>505443</v>
       </c>
       <c r="R34" t="n">
-        <v>6666020</v>
+        <v>6666049</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4754,7 +4754,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4926,7 +4926,7 @@
         <v>127294976</v>
       </c>
       <c r="B36" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>127297810</v>
       </c>
       <c r="B38" t="n">
-        <v>96720</v>
+        <v>96721</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>127295841</v>
       </c>
       <c r="B39" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>127294730</v>
       </c>
       <c r="B40" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         <v>127295873</v>
       </c>
       <c r="B41" t="n">
-        <v>96720</v>
+        <v>96721</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5815,44 +5815,36 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127295399</v>
+        <v>127301907</v>
       </c>
       <c r="B43" t="n">
-        <v>98468</v>
+        <v>96816</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1841</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
@@ -5862,10 +5854,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>505404</v>
+        <v>505491</v>
       </c>
       <c r="R43" t="n">
-        <v>6666039</v>
+        <v>6666106</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5895,19 +5887,9 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>15:03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5919,6 +5901,26 @@
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5935,36 +5937,44 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127301907</v>
+        <v>127295399</v>
       </c>
       <c r="B44" t="n">
-        <v>96815</v>
+        <v>98469</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1841</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
@@ -5974,10 +5984,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>505491</v>
+        <v>505404</v>
       </c>
       <c r="R44" t="n">
-        <v>6666106</v>
+        <v>6666039</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6007,9 +6017,19 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6021,26 +6041,6 @@
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6057,37 +6057,46 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127298146</v>
+        <v>127295179</v>
       </c>
       <c r="B45" t="n">
-        <v>91370</v>
+        <v>98469</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6095,10 +6104,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>505544</v>
+        <v>505378</v>
       </c>
       <c r="R45" t="n">
-        <v>6666053</v>
+        <v>6666040</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6130,7 +6139,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6140,7 +6149,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6152,21 +6161,6 @@
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6183,10 +6177,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127295179</v>
+        <v>127295238</v>
       </c>
       <c r="B46" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6213,7 +6207,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6230,10 +6224,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>505378</v>
+        <v>505388</v>
       </c>
       <c r="R46" t="n">
-        <v>6666040</v>
+        <v>6666037</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6265,7 +6259,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6275,7 +6269,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6303,46 +6297,37 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127295238</v>
+        <v>127298146</v>
       </c>
       <c r="B47" t="n">
-        <v>98468</v>
+        <v>91371</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6350,10 +6335,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>505388</v>
+        <v>505544</v>
       </c>
       <c r="R47" t="n">
-        <v>6666037</v>
+        <v>6666053</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6385,7 +6370,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6395,7 +6380,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6407,6 +6392,21 @@
       <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6423,32 +6423,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127297221</v>
+        <v>127296862</v>
       </c>
       <c r="B48" t="n">
-        <v>75136</v>
+        <v>79061</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6439</v>
+        <v>185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6464,7 +6464,7 @@
         <v>505478</v>
       </c>
       <c r="R48" t="n">
-        <v>6666109</v>
+        <v>6666105</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6521,22 +6521,22 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6554,46 +6554,37 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127296142</v>
+        <v>127297221</v>
       </c>
       <c r="B49" t="n">
-        <v>98468</v>
+        <v>75136</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6439</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6601,10 +6592,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>505465</v>
+        <v>505478</v>
       </c>
       <c r="R49" t="n">
-        <v>6666072</v>
+        <v>6666109</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6636,7 +6627,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6646,7 +6637,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6658,6 +6649,26 @@
       <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6674,37 +6685,46 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127296862</v>
+        <v>127296142</v>
       </c>
       <c r="B50" t="n">
-        <v>79061</v>
+        <v>98469</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6712,10 +6732,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>505478</v>
+        <v>505465</v>
       </c>
       <c r="R50" t="n">
-        <v>6666105</v>
+        <v>6666072</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6747,7 +6767,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6757,7 +6777,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6769,26 +6789,6 @@
       <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 32085-2025 artfynd.xlsx
+++ b/artfynd/A 32085-2025 artfynd.xlsx
@@ -6808,7 +6808,7 @@
         <v>130181166</v>
       </c>
       <c r="B51" t="n">
-        <v>97172</v>
+        <v>97174</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>130181123</v>
       </c>
       <c r="B52" t="n">
-        <v>97077</v>
+        <v>97079</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 32085-2025 artfynd.xlsx
+++ b/artfynd/A 32085-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127298150</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>8447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>127295076</v>
       </c>
       <c r="B3" t="n">
-        <v>98469</v>
+        <v>98436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>127297595</v>
       </c>
       <c r="B4" t="n">
-        <v>75145</v>
+        <v>75127</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1063,38 +1063,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127294425</v>
+        <v>127296095</v>
       </c>
       <c r="B5" t="n">
-        <v>97346</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1102,10 +1109,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505296</v>
+        <v>505457</v>
       </c>
       <c r="R5" t="n">
-        <v>6666023</v>
+        <v>6666067</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1137,7 +1144,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1147,7 +1154,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,6 +1166,26 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Dead branch  # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1175,45 +1202,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127296095</v>
+        <v>127294425</v>
       </c>
       <c r="B6" t="n">
-        <v>79061</v>
+        <v>97314</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1221,10 +1241,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505457</v>
+        <v>505296</v>
       </c>
       <c r="R6" t="n">
-        <v>6666067</v>
+        <v>6666023</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,7 +1276,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1266,7 +1286,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,26 +1298,6 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Dead branch  # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1314,36 +1314,44 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127296163</v>
+        <v>127295189</v>
       </c>
       <c r="B7" t="n">
-        <v>96721</v>
+        <v>98436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1353,10 +1361,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505465</v>
+        <v>505380</v>
       </c>
       <c r="R7" t="n">
-        <v>6666072</v>
+        <v>6666036</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1388,7 +1396,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1398,7 +1406,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1410,26 +1418,6 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1446,10 +1434,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127295189</v>
+        <v>127294826</v>
       </c>
       <c r="B8" t="n">
-        <v>98469</v>
+        <v>98436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1464,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1493,10 +1481,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505380</v>
+        <v>505332</v>
       </c>
       <c r="R8" t="n">
-        <v>6666036</v>
+        <v>6666037</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1528,7 +1516,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1538,7 +1526,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1566,44 +1554,36 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127294826</v>
+        <v>127296163</v>
       </c>
       <c r="B9" t="n">
-        <v>98469</v>
+        <v>96689</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1613,10 +1593,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505332</v>
+        <v>505465</v>
       </c>
       <c r="R9" t="n">
-        <v>6666037</v>
+        <v>6666072</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1648,7 +1628,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1658,7 +1638,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1670,6 +1650,26 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1689,7 +1689,7 @@
         <v>127295345</v>
       </c>
       <c r="B10" t="n">
-        <v>98469</v>
+        <v>98436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>127297697</v>
       </c>
       <c r="B11" t="n">
-        <v>96721</v>
+        <v>96689</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1938,10 +1938,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127294748</v>
+        <v>127294550</v>
       </c>
       <c r="B12" t="n">
-        <v>98469</v>
+        <v>98436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1985,10 +1985,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505318</v>
+        <v>505307</v>
       </c>
       <c r="R12" t="n">
-        <v>6666032</v>
+        <v>6666031</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2058,10 +2058,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127294550</v>
+        <v>127295061</v>
       </c>
       <c r="B13" t="n">
-        <v>98469</v>
+        <v>98436</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505307</v>
+        <v>505372</v>
       </c>
       <c r="R13" t="n">
-        <v>6666031</v>
+        <v>6666038</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2178,10 +2178,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127295061</v>
+        <v>127294748</v>
       </c>
       <c r="B14" t="n">
-        <v>98469</v>
+        <v>98436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2225,10 +2225,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505372</v>
+        <v>505318</v>
       </c>
       <c r="R14" t="n">
-        <v>6666038</v>
+        <v>6666032</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2301,7 +2301,7 @@
         <v>127295213</v>
       </c>
       <c r="B15" t="n">
-        <v>98469</v>
+        <v>98436</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2418,37 +2418,46 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127297615</v>
+        <v>127295297</v>
       </c>
       <c r="B16" t="n">
-        <v>75145</v>
+        <v>98436</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2456,10 +2465,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505511</v>
+        <v>505400</v>
       </c>
       <c r="R16" t="n">
-        <v>6666168</v>
+        <v>6666034</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2491,7 +2500,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2501,7 +2510,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2513,26 +2522,6 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2549,36 +2538,44 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127297651</v>
+        <v>127296113</v>
       </c>
       <c r="B17" t="n">
-        <v>96721</v>
+        <v>98436</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2588,10 +2585,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505512</v>
+        <v>505461</v>
       </c>
       <c r="R17" t="n">
-        <v>6666168</v>
+        <v>6666073</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2623,7 +2620,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2633,7 +2630,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2645,26 +2642,6 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2681,46 +2658,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127295297</v>
+        <v>127297615</v>
       </c>
       <c r="B18" t="n">
-        <v>98469</v>
+        <v>75127</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2728,10 +2696,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505400</v>
+        <v>505511</v>
       </c>
       <c r="R18" t="n">
-        <v>6666034</v>
+        <v>6666168</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2763,7 +2731,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2773,7 +2741,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2785,6 +2753,26 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2801,44 +2789,36 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127296113</v>
+        <v>127297651</v>
       </c>
       <c r="B19" t="n">
-        <v>98469</v>
+        <v>96689</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2848,10 +2828,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>505461</v>
+        <v>505512</v>
       </c>
       <c r="R19" t="n">
-        <v>6666073</v>
+        <v>6666168</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2883,7 +2863,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2893,7 +2873,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2905,6 +2885,26 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2924,7 +2924,7 @@
         <v>127295662</v>
       </c>
       <c r="B20" t="n">
-        <v>75145</v>
+        <v>75127</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3052,36 +3052,44 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127297420</v>
+        <v>127296043</v>
       </c>
       <c r="B21" t="n">
-        <v>96721</v>
+        <v>98436</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -3091,10 +3099,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>505483</v>
+        <v>505457</v>
       </c>
       <c r="R21" t="n">
-        <v>6666164</v>
+        <v>6666067</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3126,7 +3134,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3136,7 +3144,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3148,26 +3156,6 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3184,10 +3172,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127297958</v>
+        <v>127297420</v>
       </c>
       <c r="B22" t="n">
-        <v>75145</v>
+        <v>96689</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3195,26 +3183,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>308</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3222,10 +3211,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>505525</v>
+        <v>505483</v>
       </c>
       <c r="R22" t="n">
-        <v>6666131</v>
+        <v>6666164</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3257,7 +3246,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3267,7 +3256,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3292,12 +3281,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3315,10 +3304,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127296043</v>
+        <v>127295317</v>
       </c>
       <c r="B23" t="n">
-        <v>98469</v>
+        <v>98436</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3345,7 +3334,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>68</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3362,10 +3351,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>505457</v>
+        <v>505401</v>
       </c>
       <c r="R23" t="n">
-        <v>6666067</v>
+        <v>6666036</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3397,7 +3386,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3407,7 +3396,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3435,46 +3424,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295317</v>
+        <v>127297958</v>
       </c>
       <c r="B24" t="n">
-        <v>98469</v>
+        <v>75127</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3482,10 +3462,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505401</v>
+        <v>505525</v>
       </c>
       <c r="R24" t="n">
-        <v>6666036</v>
+        <v>6666131</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3517,7 +3497,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3527,7 +3507,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3539,6 +3519,26 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3555,49 +3555,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127298417</v>
+        <v>127294423</v>
       </c>
       <c r="B25" t="n">
-        <v>98386</v>
+        <v>98436</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3606,10 +3602,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>505547</v>
+        <v>505296</v>
       </c>
       <c r="R25" t="n">
-        <v>6666020</v>
+        <v>6666023</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3641,7 +3637,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3651,7 +3647,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3679,10 +3675,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127294423</v>
+        <v>127295681</v>
       </c>
       <c r="B26" t="n">
-        <v>98469</v>
+        <v>98436</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3709,7 +3705,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3726,10 +3722,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>505296</v>
+        <v>505425</v>
       </c>
       <c r="R26" t="n">
-        <v>6666023</v>
+        <v>6666033</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3761,7 +3757,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3771,7 +3767,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3799,10 +3795,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295681</v>
+        <v>127295207</v>
       </c>
       <c r="B27" t="n">
-        <v>98469</v>
+        <v>98436</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3829,7 +3825,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3846,10 +3842,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>505425</v>
+        <v>505383</v>
       </c>
       <c r="R27" t="n">
-        <v>6666033</v>
+        <v>6666039</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3881,7 +3877,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3891,7 +3887,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3919,45 +3915,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127295207</v>
+        <v>127298417</v>
       </c>
       <c r="B28" t="n">
-        <v>98469</v>
+        <v>98353</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>505383</v>
+        <v>505547</v>
       </c>
       <c r="R28" t="n">
-        <v>6666039</v>
+        <v>6666020</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4042,7 +4042,7 @@
         <v>127296321</v>
       </c>
       <c r="B29" t="n">
-        <v>79061</v>
+        <v>79043</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4170,37 +4170,46 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127297555</v>
+        <v>127294722</v>
       </c>
       <c r="B30" t="n">
-        <v>75145</v>
+        <v>98436</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4208,10 +4217,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>505501</v>
+        <v>505312</v>
       </c>
       <c r="R30" t="n">
-        <v>6666172</v>
+        <v>6666032</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4243,7 +4252,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4253,7 +4262,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4265,26 +4274,6 @@
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4304,7 +4293,7 @@
         <v>127298321</v>
       </c>
       <c r="B31" t="n">
-        <v>79647</v>
+        <v>79629</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4432,46 +4421,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127294722</v>
+        <v>127297555</v>
       </c>
       <c r="B32" t="n">
-        <v>98469</v>
+        <v>75127</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4479,10 +4459,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>505312</v>
+        <v>505501</v>
       </c>
       <c r="R32" t="n">
-        <v>6666032</v>
+        <v>6666172</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4514,7 +4494,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4524,7 +4504,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4536,6 +4516,26 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4552,10 +4552,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127294455</v>
+        <v>127295731</v>
       </c>
       <c r="B33" t="n">
-        <v>98469</v>
+        <v>98436</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>505303</v>
+        <v>505443</v>
       </c>
       <c r="R33" t="n">
-        <v>6666020</v>
+        <v>6666049</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4672,10 +4672,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127295731</v>
+        <v>127294455</v>
       </c>
       <c r="B34" t="n">
-        <v>98469</v>
+        <v>98436</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>505443</v>
+        <v>505303</v>
       </c>
       <c r="R34" t="n">
-        <v>6666049</v>
+        <v>6666020</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4754,7 +4754,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4795,7 +4795,7 @@
         <v>127298053</v>
       </c>
       <c r="B35" t="n">
-        <v>78435</v>
+        <v>78417</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4923,46 +4923,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127294976</v>
+        <v>127296758</v>
       </c>
       <c r="B36" t="n">
-        <v>98469</v>
+        <v>78417</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4970,10 +4961,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>505373</v>
+        <v>505486</v>
       </c>
       <c r="R36" t="n">
-        <v>6666042</v>
+        <v>6666108</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5005,7 +4996,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5015,7 +5006,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5027,6 +5018,26 @@
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5043,37 +5054,46 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127296758</v>
+        <v>127294976</v>
       </c>
       <c r="B37" t="n">
-        <v>78435</v>
+        <v>98436</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5081,10 +5101,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>505486</v>
+        <v>505373</v>
       </c>
       <c r="R37" t="n">
-        <v>6666108</v>
+        <v>6666042</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5116,7 +5136,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5126,7 +5146,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5138,26 +5158,6 @@
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5174,36 +5174,44 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127297810</v>
+        <v>127295841</v>
       </c>
       <c r="B38" t="n">
-        <v>96721</v>
+        <v>98436</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -5213,10 +5221,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>505515</v>
+        <v>505457</v>
       </c>
       <c r="R38" t="n">
-        <v>6666146</v>
+        <v>6666062</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5248,7 +5256,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5258,7 +5266,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5270,26 +5278,6 @@
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5306,44 +5294,36 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127295841</v>
+        <v>127297810</v>
       </c>
       <c r="B39" t="n">
-        <v>98469</v>
+        <v>96689</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -5353,10 +5333,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>505457</v>
+        <v>505515</v>
       </c>
       <c r="R39" t="n">
-        <v>6666062</v>
+        <v>6666146</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5388,7 +5368,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5398,7 +5378,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5410,6 +5390,26 @@
       <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5429,7 +5429,7 @@
         <v>127294730</v>
       </c>
       <c r="B40" t="n">
-        <v>98469</v>
+        <v>98436</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         <v>127295873</v>
       </c>
       <c r="B41" t="n">
-        <v>96721</v>
+        <v>96689</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         <v>127294173</v>
       </c>
       <c r="B42" t="n">
-        <v>4773</v>
+        <v>4772</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5815,36 +5815,44 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127301907</v>
+        <v>127295399</v>
       </c>
       <c r="B43" t="n">
-        <v>96816</v>
+        <v>98436</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1841</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
@@ -5854,10 +5862,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>505491</v>
+        <v>505404</v>
       </c>
       <c r="R43" t="n">
-        <v>6666106</v>
+        <v>6666039</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5887,9 +5895,19 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5901,26 +5919,6 @@
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5937,44 +5935,36 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127295399</v>
+        <v>127301907</v>
       </c>
       <c r="B44" t="n">
-        <v>98469</v>
+        <v>96784</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1841</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
@@ -5984,10 +5974,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>505404</v>
+        <v>505491</v>
       </c>
       <c r="R44" t="n">
-        <v>6666039</v>
+        <v>6666106</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6017,19 +6007,9 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>15:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6041,6 +6021,26 @@
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6060,7 +6060,7 @@
         <v>127295179</v>
       </c>
       <c r="B45" t="n">
-        <v>98469</v>
+        <v>98436</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>127295238</v>
       </c>
       <c r="B46" t="n">
-        <v>98469</v>
+        <v>98436</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>127298146</v>
       </c>
       <c r="B47" t="n">
-        <v>91371</v>
+        <v>91339</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6423,32 +6423,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127296862</v>
+        <v>127297221</v>
       </c>
       <c r="B48" t="n">
-        <v>79061</v>
+        <v>75118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>6439</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6464,7 +6464,7 @@
         <v>505478</v>
       </c>
       <c r="R48" t="n">
-        <v>6666105</v>
+        <v>6666109</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6521,22 +6521,22 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6554,32 +6554,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127297221</v>
+        <v>127296862</v>
       </c>
       <c r="B49" t="n">
-        <v>75136</v>
+        <v>79043</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6439</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6595,7 +6595,7 @@
         <v>505478</v>
       </c>
       <c r="R49" t="n">
-        <v>6666109</v>
+        <v>6666105</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6652,22 +6652,22 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6688,7 +6688,7 @@
         <v>127296142</v>
       </c>
       <c r="B50" t="n">
-        <v>98469</v>
+        <v>98436</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>130181166</v>
       </c>
       <c r="B51" t="n">
-        <v>97174</v>
+        <v>97261</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>130181123</v>
       </c>
       <c r="B52" t="n">
-        <v>97079</v>
+        <v>97166</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 32085-2025 artfynd.xlsx
+++ b/artfynd/A 32085-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127298150</v>
       </c>
       <c r="B2" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>127295076</v>
       </c>
       <c r="B3" t="n">
-        <v>98436</v>
+        <v>98469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>127297595</v>
       </c>
       <c r="B4" t="n">
-        <v>75127</v>
+        <v>75145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1063,45 +1063,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127296095</v>
+        <v>127294425</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>97346</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1109,10 +1102,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505457</v>
+        <v>505296</v>
       </c>
       <c r="R5" t="n">
-        <v>6666067</v>
+        <v>6666023</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1137,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1154,7 +1147,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,26 +1159,6 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Dead branch  # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1202,38 +1175,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127294425</v>
+        <v>127296095</v>
       </c>
       <c r="B6" t="n">
-        <v>97314</v>
+        <v>79061</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1241,10 +1221,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505296</v>
+        <v>505457</v>
       </c>
       <c r="R6" t="n">
-        <v>6666023</v>
+        <v>6666067</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1276,7 +1256,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1286,7 +1266,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1298,6 +1278,26 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Dead branch  # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1314,44 +1314,36 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127295189</v>
+        <v>127296163</v>
       </c>
       <c r="B7" t="n">
-        <v>98436</v>
+        <v>96721</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1361,10 +1353,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505380</v>
+        <v>505465</v>
       </c>
       <c r="R7" t="n">
-        <v>6666036</v>
+        <v>6666072</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1396,7 +1388,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1406,7 +1398,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1418,6 +1410,26 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1434,10 +1446,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127294826</v>
+        <v>127295189</v>
       </c>
       <c r="B8" t="n">
-        <v>98436</v>
+        <v>98469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1464,7 +1476,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1481,10 +1493,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505332</v>
+        <v>505380</v>
       </c>
       <c r="R8" t="n">
-        <v>6666037</v>
+        <v>6666036</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1516,7 +1528,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1526,7 +1538,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1554,36 +1566,44 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127296163</v>
+        <v>127294826</v>
       </c>
       <c r="B9" t="n">
-        <v>96689</v>
+        <v>98469</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1593,10 +1613,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505465</v>
+        <v>505332</v>
       </c>
       <c r="R9" t="n">
-        <v>6666072</v>
+        <v>6666037</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1628,7 +1648,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1638,7 +1658,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1650,26 +1670,6 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1689,7 +1689,7 @@
         <v>127295345</v>
       </c>
       <c r="B10" t="n">
-        <v>98436</v>
+        <v>98469</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>127297697</v>
       </c>
       <c r="B11" t="n">
-        <v>96689</v>
+        <v>96721</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1938,10 +1938,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127294550</v>
+        <v>127294748</v>
       </c>
       <c r="B12" t="n">
-        <v>98436</v>
+        <v>98469</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1985,10 +1985,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505307</v>
+        <v>505318</v>
       </c>
       <c r="R12" t="n">
-        <v>6666031</v>
+        <v>6666032</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2058,10 +2058,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127295061</v>
+        <v>127294550</v>
       </c>
       <c r="B13" t="n">
-        <v>98436</v>
+        <v>98469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505372</v>
+        <v>505307</v>
       </c>
       <c r="R13" t="n">
-        <v>6666038</v>
+        <v>6666031</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2178,10 +2178,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127294748</v>
+        <v>127295061</v>
       </c>
       <c r="B14" t="n">
-        <v>98436</v>
+        <v>98469</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2225,10 +2225,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505318</v>
+        <v>505372</v>
       </c>
       <c r="R14" t="n">
-        <v>6666032</v>
+        <v>6666038</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2301,7 +2301,7 @@
         <v>127295213</v>
       </c>
       <c r="B15" t="n">
-        <v>98436</v>
+        <v>98469</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2418,46 +2418,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127295297</v>
+        <v>127297615</v>
       </c>
       <c r="B16" t="n">
-        <v>98436</v>
+        <v>75145</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2465,10 +2456,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505400</v>
+        <v>505511</v>
       </c>
       <c r="R16" t="n">
-        <v>6666034</v>
+        <v>6666168</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2500,7 +2491,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2510,7 +2501,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2522,6 +2513,26 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2538,44 +2549,36 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127296113</v>
+        <v>127297651</v>
       </c>
       <c r="B17" t="n">
-        <v>98436</v>
+        <v>96721</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2585,10 +2588,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505461</v>
+        <v>505512</v>
       </c>
       <c r="R17" t="n">
-        <v>6666073</v>
+        <v>6666168</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2620,7 +2623,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2630,7 +2633,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2642,6 +2645,26 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2658,37 +2681,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127297615</v>
+        <v>127295297</v>
       </c>
       <c r="B18" t="n">
-        <v>75127</v>
+        <v>98469</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2696,10 +2728,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505511</v>
+        <v>505400</v>
       </c>
       <c r="R18" t="n">
-        <v>6666168</v>
+        <v>6666034</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2731,7 +2763,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2741,7 +2773,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2753,26 +2785,6 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2789,36 +2801,44 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127297651</v>
+        <v>127296113</v>
       </c>
       <c r="B19" t="n">
-        <v>96689</v>
+        <v>98469</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2828,10 +2848,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>505512</v>
+        <v>505461</v>
       </c>
       <c r="R19" t="n">
-        <v>6666168</v>
+        <v>6666073</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2863,7 +2883,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2873,7 +2893,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2885,26 +2905,6 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2924,7 +2924,7 @@
         <v>127295662</v>
       </c>
       <c r="B20" t="n">
-        <v>75127</v>
+        <v>75145</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3052,44 +3052,36 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127296043</v>
+        <v>127297420</v>
       </c>
       <c r="B21" t="n">
-        <v>98436</v>
+        <v>96721</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -3099,10 +3091,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>505457</v>
+        <v>505483</v>
       </c>
       <c r="R21" t="n">
-        <v>6666067</v>
+        <v>6666164</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3134,7 +3126,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3144,7 +3136,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3156,6 +3148,26 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3172,10 +3184,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127297420</v>
+        <v>127297958</v>
       </c>
       <c r="B22" t="n">
-        <v>96689</v>
+        <v>75145</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3183,27 +3195,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3211,10 +3222,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>505483</v>
+        <v>505525</v>
       </c>
       <c r="R22" t="n">
-        <v>6666164</v>
+        <v>6666131</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3246,7 +3257,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3256,7 +3267,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3281,12 +3292,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3304,10 +3315,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127295317</v>
+        <v>127296043</v>
       </c>
       <c r="B23" t="n">
-        <v>98436</v>
+        <v>98469</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3334,7 +3345,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3351,10 +3362,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>505401</v>
+        <v>505457</v>
       </c>
       <c r="R23" t="n">
-        <v>6666036</v>
+        <v>6666067</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3386,7 +3397,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3396,7 +3407,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3424,37 +3435,46 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127297958</v>
+        <v>127295317</v>
       </c>
       <c r="B24" t="n">
-        <v>75127</v>
+        <v>98469</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3462,10 +3482,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505525</v>
+        <v>505401</v>
       </c>
       <c r="R24" t="n">
-        <v>6666131</v>
+        <v>6666036</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3497,7 +3517,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3507,7 +3527,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3519,26 +3539,6 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3555,45 +3555,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127294423</v>
+        <v>127298417</v>
       </c>
       <c r="B25" t="n">
-        <v>98436</v>
+        <v>98386</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3602,10 +3606,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>505296</v>
+        <v>505547</v>
       </c>
       <c r="R25" t="n">
-        <v>6666023</v>
+        <v>6666020</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3637,7 +3641,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3647,7 +3651,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3675,10 +3679,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127295681</v>
+        <v>127294423</v>
       </c>
       <c r="B26" t="n">
-        <v>98436</v>
+        <v>98469</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3705,7 +3709,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3722,10 +3726,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>505425</v>
+        <v>505296</v>
       </c>
       <c r="R26" t="n">
-        <v>6666033</v>
+        <v>6666023</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3757,7 +3761,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3767,7 +3771,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3795,10 +3799,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295207</v>
+        <v>127295681</v>
       </c>
       <c r="B27" t="n">
-        <v>98436</v>
+        <v>98469</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3825,7 +3829,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3842,10 +3846,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>505383</v>
+        <v>505425</v>
       </c>
       <c r="R27" t="n">
-        <v>6666039</v>
+        <v>6666033</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3877,7 +3881,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3887,7 +3891,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3915,49 +3919,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127298417</v>
+        <v>127295207</v>
       </c>
       <c r="B28" t="n">
-        <v>98353</v>
+        <v>98469</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>505547</v>
+        <v>505383</v>
       </c>
       <c r="R28" t="n">
-        <v>6666020</v>
+        <v>6666039</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4042,7 +4042,7 @@
         <v>127296321</v>
       </c>
       <c r="B29" t="n">
-        <v>79043</v>
+        <v>79061</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4170,46 +4170,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127294722</v>
+        <v>127297555</v>
       </c>
       <c r="B30" t="n">
-        <v>98436</v>
+        <v>75145</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4217,10 +4208,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>505312</v>
+        <v>505501</v>
       </c>
       <c r="R30" t="n">
-        <v>6666032</v>
+        <v>6666172</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4252,7 +4243,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4262,7 +4253,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4274,6 +4265,26 @@
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4293,7 +4304,7 @@
         <v>127298321</v>
       </c>
       <c r="B31" t="n">
-        <v>79629</v>
+        <v>79647</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4421,37 +4432,46 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127297555</v>
+        <v>127294722</v>
       </c>
       <c r="B32" t="n">
-        <v>75127</v>
+        <v>98469</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4459,10 +4479,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>505501</v>
+        <v>505312</v>
       </c>
       <c r="R32" t="n">
-        <v>6666172</v>
+        <v>6666032</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4494,7 +4514,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4504,7 +4524,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4516,26 +4536,6 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4552,10 +4552,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127295731</v>
+        <v>127294455</v>
       </c>
       <c r="B33" t="n">
-        <v>98436</v>
+        <v>98469</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>505443</v>
+        <v>505303</v>
       </c>
       <c r="R33" t="n">
-        <v>6666049</v>
+        <v>6666020</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4672,10 +4672,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127294455</v>
+        <v>127295731</v>
       </c>
       <c r="B34" t="n">
-        <v>98436</v>
+        <v>98469</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>505303</v>
+        <v>505443</v>
       </c>
       <c r="R34" t="n">
-        <v>6666020</v>
+        <v>6666049</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4754,7 +4754,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4795,7 +4795,7 @@
         <v>127298053</v>
       </c>
       <c r="B35" t="n">
-        <v>78417</v>
+        <v>78435</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4923,37 +4923,46 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127296758</v>
+        <v>127294976</v>
       </c>
       <c r="B36" t="n">
-        <v>78417</v>
+        <v>98469</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4961,10 +4970,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>505486</v>
+        <v>505373</v>
       </c>
       <c r="R36" t="n">
-        <v>6666108</v>
+        <v>6666042</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4996,7 +5005,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5006,7 +5015,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5018,26 +5027,6 @@
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5054,46 +5043,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127294976</v>
+        <v>127296758</v>
       </c>
       <c r="B37" t="n">
-        <v>98436</v>
+        <v>78435</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5101,10 +5081,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>505373</v>
+        <v>505486</v>
       </c>
       <c r="R37" t="n">
-        <v>6666042</v>
+        <v>6666108</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5136,7 +5116,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5146,7 +5126,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5158,6 +5138,26 @@
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5174,44 +5174,36 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127295841</v>
+        <v>127297810</v>
       </c>
       <c r="B38" t="n">
-        <v>98436</v>
+        <v>96721</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -5221,10 +5213,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>505457</v>
+        <v>505515</v>
       </c>
       <c r="R38" t="n">
-        <v>6666062</v>
+        <v>6666146</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5256,7 +5248,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5266,7 +5258,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5278,6 +5270,26 @@
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5294,36 +5306,44 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127297810</v>
+        <v>127295841</v>
       </c>
       <c r="B39" t="n">
-        <v>96689</v>
+        <v>98469</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -5333,10 +5353,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>505515</v>
+        <v>505457</v>
       </c>
       <c r="R39" t="n">
-        <v>6666146</v>
+        <v>6666062</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5368,7 +5388,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5378,7 +5398,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5390,26 +5410,6 @@
       <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5429,7 +5429,7 @@
         <v>127294730</v>
       </c>
       <c r="B40" t="n">
-        <v>98436</v>
+        <v>98469</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         <v>127295873</v>
       </c>
       <c r="B41" t="n">
-        <v>96689</v>
+        <v>96721</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         <v>127294173</v>
       </c>
       <c r="B42" t="n">
-        <v>4772</v>
+        <v>4773</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5815,44 +5815,36 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127295399</v>
+        <v>127301907</v>
       </c>
       <c r="B43" t="n">
-        <v>98436</v>
+        <v>96816</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1841</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
@@ -5862,10 +5854,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>505404</v>
+        <v>505491</v>
       </c>
       <c r="R43" t="n">
-        <v>6666039</v>
+        <v>6666106</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5895,19 +5887,9 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>15:03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5919,6 +5901,26 @@
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5935,36 +5937,44 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127301907</v>
+        <v>127295399</v>
       </c>
       <c r="B44" t="n">
-        <v>96784</v>
+        <v>98469</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1841</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
@@ -5974,10 +5984,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>505491</v>
+        <v>505404</v>
       </c>
       <c r="R44" t="n">
-        <v>6666106</v>
+        <v>6666039</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6007,9 +6017,19 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6021,26 +6041,6 @@
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6060,7 +6060,7 @@
         <v>127295179</v>
       </c>
       <c r="B45" t="n">
-        <v>98436</v>
+        <v>98469</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>127295238</v>
       </c>
       <c r="B46" t="n">
-        <v>98436</v>
+        <v>98469</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>127298146</v>
       </c>
       <c r="B47" t="n">
-        <v>91339</v>
+        <v>91371</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6423,32 +6423,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127297221</v>
+        <v>127296862</v>
       </c>
       <c r="B48" t="n">
-        <v>75118</v>
+        <v>79061</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6439</v>
+        <v>185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6464,7 +6464,7 @@
         <v>505478</v>
       </c>
       <c r="R48" t="n">
-        <v>6666109</v>
+        <v>6666105</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6521,22 +6521,22 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6554,32 +6554,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127296862</v>
+        <v>127297221</v>
       </c>
       <c r="B49" t="n">
-        <v>79043</v>
+        <v>75136</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>6439</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6595,7 +6595,7 @@
         <v>505478</v>
       </c>
       <c r="R49" t="n">
-        <v>6666105</v>
+        <v>6666109</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6652,22 +6652,22 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6688,7 +6688,7 @@
         <v>127296142</v>
       </c>
       <c r="B50" t="n">
-        <v>98436</v>
+        <v>98469</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 32085-2025 artfynd.xlsx
+++ b/artfynd/A 32085-2025 artfynd.xlsx
@@ -6808,7 +6808,7 @@
         <v>130181166</v>
       </c>
       <c r="B51" t="n">
-        <v>97261</v>
+        <v>97264</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>130181123</v>
       </c>
       <c r="B52" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 32085-2025 artfynd.xlsx
+++ b/artfynd/A 32085-2025 artfynd.xlsx
@@ -6808,7 +6808,7 @@
         <v>130181166</v>
       </c>
       <c r="B51" t="n">
-        <v>97264</v>
+        <v>97290</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>130181123</v>
       </c>
       <c r="B52" t="n">
-        <v>97169</v>
+        <v>97195</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 32085-2025 artfynd.xlsx
+++ b/artfynd/A 32085-2025 artfynd.xlsx
@@ -6808,7 +6808,7 @@
         <v>130181166</v>
       </c>
       <c r="B51" t="n">
-        <v>97290</v>
+        <v>97291</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>130181123</v>
       </c>
       <c r="B52" t="n">
-        <v>97195</v>
+        <v>97196</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 32085-2025 artfynd.xlsx
+++ b/artfynd/A 32085-2025 artfynd.xlsx
@@ -6808,7 +6808,7 @@
         <v>130181166</v>
       </c>
       <c r="B51" t="n">
-        <v>97291</v>
+        <v>97292</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>130181123</v>
       </c>
       <c r="B52" t="n">
-        <v>97196</v>
+        <v>97197</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 32085-2025 artfynd.xlsx
+++ b/artfynd/A 32085-2025 artfynd.xlsx
@@ -6808,7 +6808,7 @@
         <v>130181166</v>
       </c>
       <c r="B51" t="n">
-        <v>97292</v>
+        <v>97294</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>130181123</v>
       </c>
       <c r="B52" t="n">
-        <v>97197</v>
+        <v>97199</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 32085-2025 artfynd.xlsx
+++ b/artfynd/A 32085-2025 artfynd.xlsx
@@ -6808,7 +6808,7 @@
         <v>130181166</v>
       </c>
       <c r="B51" t="n">
-        <v>97294</v>
+        <v>97298</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>130181123</v>
       </c>
       <c r="B52" t="n">
-        <v>97199</v>
+        <v>97203</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 32085-2025 artfynd.xlsx
+++ b/artfynd/A 32085-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AY60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,43 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127298150</v>
+        <v>127295873</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505544</v>
+        <v>505457</v>
       </c>
       <c r="R2" t="n">
-        <v>6666053</v>
+        <v>6666062</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,12 +784,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -812,44 +807,36 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127295076</v>
+        <v>127296163</v>
       </c>
       <c r="B3" t="n">
-        <v>98469</v>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -859,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505375</v>
+        <v>505465</v>
       </c>
       <c r="R3" t="n">
-        <v>6666039</v>
+        <v>6666072</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,6 +903,26 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -932,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127297595</v>
+        <v>127297420</v>
       </c>
       <c r="B4" t="n">
-        <v>75145</v>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,26 +950,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -970,10 +978,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505508</v>
+        <v>505483</v>
       </c>
       <c r="R4" t="n">
-        <v>6666170</v>
+        <v>6666164</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,7 +1013,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1015,7 +1023,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,12 +1048,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1063,32 +1071,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127294425</v>
+        <v>127297475</v>
       </c>
       <c r="B5" t="n">
-        <v>97346</v>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1102,10 +1110,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505296</v>
+        <v>505479</v>
       </c>
       <c r="R5" t="n">
-        <v>6666023</v>
+        <v>6666186</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1137,7 +1145,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1147,7 +1155,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,6 +1167,26 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1175,10 +1203,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127296095</v>
+        <v>127297651</v>
       </c>
       <c r="B6" t="n">
-        <v>79061</v>
+        <v>97358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,34 +1214,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1221,10 +1242,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505457</v>
+        <v>505512</v>
       </c>
       <c r="R6" t="n">
-        <v>6666067</v>
+        <v>6666168</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,7 +1277,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1266,7 +1287,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1281,22 +1302,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Dead branch  # Betula pubescens</t>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1314,10 +1335,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127296163</v>
+        <v>127297697</v>
       </c>
       <c r="B7" t="n">
-        <v>96721</v>
+        <v>97358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,10 +1374,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505465</v>
+        <v>505514</v>
       </c>
       <c r="R7" t="n">
-        <v>6666072</v>
+        <v>6666167</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1388,7 +1409,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1398,7 +1419,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1413,12 +1434,12 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -1428,7 +1449,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1446,44 +1467,36 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127295189</v>
+        <v>127297810</v>
       </c>
       <c r="B8" t="n">
-        <v>98469</v>
+        <v>97358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1493,10 +1506,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505380</v>
+        <v>505515</v>
       </c>
       <c r="R8" t="n">
-        <v>6666036</v>
+        <v>6666146</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1528,7 +1541,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1538,7 +1551,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1550,6 +1563,26 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1566,57 +1599,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127294826</v>
+        <v>130181123</v>
       </c>
       <c r="B9" t="n">
-        <v>98469</v>
+        <v>97358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ö om Främundstjärnen, Dlr</t>
+          <t>Främundsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505332</v>
+        <v>505469</v>
       </c>
       <c r="R9" t="n">
-        <v>6666037</v>
+        <v>6666108</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1643,22 +1664,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:38</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:38</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1667,76 +1678,63 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127295345</v>
+        <v>130183686</v>
       </c>
       <c r="B10" t="n">
-        <v>98469</v>
+        <v>97358</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ö om Främundstjärnen, Dlr</t>
+          <t>Främundsberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505402</v>
+        <v>505445</v>
       </c>
       <c r="R10" t="n">
-        <v>6666038</v>
+        <v>6666135</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1763,22 +1761,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1787,29 +1775,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127297697</v>
+        <v>127296095</v>
       </c>
       <c r="B11" t="n">
-        <v>96721</v>
+        <v>79359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,27 +1804,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1845,10 +1839,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505514</v>
+        <v>505457</v>
       </c>
       <c r="R11" t="n">
-        <v>6666167</v>
+        <v>6666067</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1880,7 +1874,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1890,7 +1884,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1905,22 +1899,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Dead branch  # Betula pubescens</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1938,46 +1932,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127294748</v>
+        <v>127296321</v>
       </c>
       <c r="B12" t="n">
-        <v>98469</v>
+        <v>79359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1985,10 +1970,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505318</v>
+        <v>505487</v>
       </c>
       <c r="R12" t="n">
-        <v>6666032</v>
+        <v>6666090</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2020,7 +2005,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2030,7 +2015,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2042,6 +2027,26 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2058,46 +2063,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127294550</v>
+        <v>127296862</v>
       </c>
       <c r="B13" t="n">
-        <v>98469</v>
+        <v>79359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2105,10 +2101,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505307</v>
+        <v>505478</v>
       </c>
       <c r="R13" t="n">
-        <v>6666031</v>
+        <v>6666105</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2140,7 +2136,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2150,7 +2146,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2162,6 +2158,26 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2178,46 +2194,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127295061</v>
+        <v>127295662</v>
       </c>
       <c r="B14" t="n">
-        <v>98469</v>
+        <v>83299</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2225,10 +2232,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505372</v>
+        <v>505425</v>
       </c>
       <c r="R14" t="n">
-        <v>6666038</v>
+        <v>6666039</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2260,7 +2267,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2270,7 +2277,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2282,6 +2289,26 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2298,46 +2325,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127295213</v>
+        <v>127297555</v>
       </c>
       <c r="B15" t="n">
-        <v>98469</v>
+        <v>83299</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2345,10 +2363,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>505383</v>
+        <v>505501</v>
       </c>
       <c r="R15" t="n">
-        <v>6666036</v>
+        <v>6666172</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2380,7 +2398,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2390,7 +2408,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2402,6 +2420,26 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2418,10 +2456,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127297615</v>
+        <v>127297595</v>
       </c>
       <c r="B16" t="n">
-        <v>75145</v>
+        <v>83299</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2456,10 +2494,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505511</v>
+        <v>505508</v>
       </c>
       <c r="R16" t="n">
-        <v>6666168</v>
+        <v>6666170</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2491,7 +2529,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2501,7 +2539,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2549,10 +2587,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127297651</v>
+        <v>127297615</v>
       </c>
       <c r="B17" t="n">
-        <v>96721</v>
+        <v>83299</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2560,27 +2598,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2588,7 +2625,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505512</v>
+        <v>505511</v>
       </c>
       <c r="R17" t="n">
         <v>6666168</v>
@@ -2623,7 +2660,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2633,7 +2670,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2658,12 +2695,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2681,46 +2718,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127295297</v>
+        <v>127297958</v>
       </c>
       <c r="B18" t="n">
-        <v>98469</v>
+        <v>83299</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2728,10 +2756,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505400</v>
+        <v>505525</v>
       </c>
       <c r="R18" t="n">
-        <v>6666034</v>
+        <v>6666131</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2763,7 +2791,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2773,7 +2801,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2785,6 +2813,26 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2801,57 +2849,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127296113</v>
+        <v>130183651</v>
       </c>
       <c r="B19" t="n">
-        <v>98469</v>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ö om Främundstjärnen, Dlr</t>
+          <t>Främundsberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>505461</v>
+        <v>505458</v>
       </c>
       <c r="R19" t="n">
-        <v>6666073</v>
+        <v>6666162</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2878,22 +2914,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>15:29</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>15:29</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2902,29 +2928,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127295662</v>
+        <v>127301907</v>
       </c>
       <c r="B20" t="n">
-        <v>75145</v>
+        <v>97453</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2932,26 +2957,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>308</v>
+        <v>1841</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2959,10 +2985,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>505425</v>
+        <v>505491</v>
       </c>
       <c r="R20" t="n">
-        <v>6666039</v>
+        <v>6666106</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2992,19 +3018,9 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>15:08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3019,22 +3035,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3052,10 +3068,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127297420</v>
+        <v>130181166</v>
       </c>
       <c r="B21" t="n">
-        <v>96721</v>
+        <v>97453</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3063,38 +3079,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>1841</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ö om Främundstjärnen, Dlr</t>
+          <t>Främundsberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>505483</v>
+        <v>505485</v>
       </c>
       <c r="R21" t="n">
-        <v>6666164</v>
+        <v>6666118</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3121,22 +3133,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>16:19</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>16:19</t>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Återfynd.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3145,87 +3152,63 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127297958</v>
+        <v>130181360</v>
       </c>
       <c r="B22" t="n">
-        <v>75145</v>
+        <v>97231</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>308</v>
+        <v>2869</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ö om Främundstjärnen, Dlr</t>
+          <t>Främundsberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>505525</v>
+        <v>505468</v>
       </c>
       <c r="R22" t="n">
-        <v>6666131</v>
+        <v>6666200</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3252,22 +3235,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>16:44</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>16:44</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3276,85 +3249,55 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127296043</v>
+        <v>127298146</v>
       </c>
       <c r="B23" t="n">
-        <v>98469</v>
+        <v>91930</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3362,10 +3305,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>505457</v>
+        <v>505544</v>
       </c>
       <c r="R23" t="n">
-        <v>6666067</v>
+        <v>6666053</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3397,7 +3340,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3407,7 +3350,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3419,6 +3362,21 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3435,57 +3393,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295317</v>
+        <v>130183613</v>
       </c>
       <c r="B24" t="n">
-        <v>98469</v>
+        <v>91872</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ö om Främundstjärnen, Dlr</t>
+          <t>Främundsberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505401</v>
+        <v>505495</v>
       </c>
       <c r="R24" t="n">
-        <v>6666036</v>
+        <v>6666206</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3512,22 +3461,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:59</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:59</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3540,65 +3479,67 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127298417</v>
+        <v>127296758</v>
       </c>
       <c r="B25" t="n">
-        <v>98386</v>
+        <v>78730</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219790</v>
+        <v>6437</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3606,10 +3547,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>505547</v>
+        <v>505486</v>
       </c>
       <c r="R25" t="n">
-        <v>6666020</v>
+        <v>6666108</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3641,7 +3582,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3651,7 +3592,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3663,6 +3604,26 @@
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3679,46 +3640,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127294423</v>
+        <v>127298053</v>
       </c>
       <c r="B26" t="n">
-        <v>98469</v>
+        <v>78730</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3726,10 +3678,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>505296</v>
+        <v>505553</v>
       </c>
       <c r="R26" t="n">
-        <v>6666023</v>
+        <v>6666065</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3761,7 +3713,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3771,7 +3723,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3783,6 +3735,26 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3799,46 +3771,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295681</v>
+        <v>127297221</v>
       </c>
       <c r="B27" t="n">
-        <v>98469</v>
+        <v>83290</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6439</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3846,10 +3809,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>505425</v>
+        <v>505478</v>
       </c>
       <c r="R27" t="n">
-        <v>6666033</v>
+        <v>6666109</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3881,7 +3844,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3891,7 +3854,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3903,6 +3866,26 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3919,46 +3902,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127295207</v>
+        <v>127298321</v>
       </c>
       <c r="B28" t="n">
-        <v>98469</v>
+        <v>79946</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3966,10 +3940,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>505383</v>
+        <v>505552</v>
       </c>
       <c r="R28" t="n">
-        <v>6666039</v>
+        <v>6666024</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4001,7 +3975,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4011,7 +3985,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4023,6 +3997,26 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Stump # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -4039,37 +4033,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127296321</v>
+        <v>127295763</v>
       </c>
       <c r="B29" t="n">
-        <v>79061</v>
+        <v>57141</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4077,10 +4084,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>505487</v>
+        <v>505467</v>
       </c>
       <c r="R29" t="n">
-        <v>6666090</v>
+        <v>6666042</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4112,7 +4119,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4122,7 +4129,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4131,29 +4138,8 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4170,37 +4156,43 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127297555</v>
+        <v>127294173</v>
       </c>
       <c r="B30" t="n">
-        <v>75145</v>
+        <v>4775</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>308</v>
+        <v>100299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4208,10 +4200,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>505501</v>
+        <v>505254</v>
       </c>
       <c r="R30" t="n">
-        <v>6666172</v>
+        <v>6666041</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4243,7 +4235,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4253,7 +4245,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4268,12 +4260,12 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -4283,7 +4275,7 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4301,37 +4293,43 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127298321</v>
+        <v>127298150</v>
       </c>
       <c r="B31" t="n">
-        <v>79647</v>
+        <v>8455</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4339,10 +4337,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>505552</v>
+        <v>505544</v>
       </c>
       <c r="R31" t="n">
-        <v>6666024</v>
+        <v>6666053</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4374,7 +4372,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4384,7 +4382,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4409,12 +4407,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stump # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4432,45 +4430,49 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127294722</v>
+        <v>127298417</v>
       </c>
       <c r="B32" t="n">
-        <v>98469</v>
+        <v>99035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
@@ -4479,10 +4481,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>505312</v>
+        <v>505547</v>
       </c>
       <c r="R32" t="n">
-        <v>6666032</v>
+        <v>6666020</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4514,7 +4516,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4524,7 +4526,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4552,10 +4554,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127294455</v>
+        <v>127294344</v>
       </c>
       <c r="B33" t="n">
-        <v>98469</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4582,7 +4584,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4599,10 +4601,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>505303</v>
+        <v>505264</v>
       </c>
       <c r="R33" t="n">
-        <v>6666020</v>
+        <v>6666055</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4634,7 +4636,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4644,7 +4646,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4672,10 +4674,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127295731</v>
+        <v>127294423</v>
       </c>
       <c r="B34" t="n">
-        <v>98469</v>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4702,7 +4704,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4719,10 +4721,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>505443</v>
+        <v>505296</v>
       </c>
       <c r="R34" t="n">
-        <v>6666049</v>
+        <v>6666023</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4754,7 +4756,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4764,7 +4766,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4792,37 +4794,46 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127298053</v>
+        <v>127294455</v>
       </c>
       <c r="B35" t="n">
-        <v>78435</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4830,10 +4841,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>505553</v>
+        <v>505303</v>
       </c>
       <c r="R35" t="n">
-        <v>6666065</v>
+        <v>6666020</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4865,7 +4876,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4875,7 +4886,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4887,26 +4898,6 @@
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4923,10 +4914,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127294976</v>
+        <v>127294550</v>
       </c>
       <c r="B36" t="n">
-        <v>98469</v>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4953,7 +4944,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4970,10 +4961,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>505373</v>
+        <v>505307</v>
       </c>
       <c r="R36" t="n">
-        <v>6666042</v>
+        <v>6666031</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5005,7 +4996,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5015,7 +5006,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5043,37 +5034,46 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127296758</v>
+        <v>127294722</v>
       </c>
       <c r="B37" t="n">
-        <v>78435</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5081,10 +5081,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>505486</v>
+        <v>505312</v>
       </c>
       <c r="R37" t="n">
-        <v>6666108</v>
+        <v>6666032</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5116,7 +5116,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5138,26 +5138,6 @@
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5174,36 +5154,44 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127297810</v>
+        <v>127294730</v>
       </c>
       <c r="B38" t="n">
-        <v>96721</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -5213,10 +5201,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>505515</v>
+        <v>505313</v>
       </c>
       <c r="R38" t="n">
-        <v>6666146</v>
+        <v>6666027</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5248,7 +5236,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5258,7 +5246,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5270,26 +5258,6 @@
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5306,10 +5274,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127295841</v>
+        <v>127294748</v>
       </c>
       <c r="B39" t="n">
-        <v>98469</v>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5336,7 +5304,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5353,10 +5321,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>505457</v>
+        <v>505318</v>
       </c>
       <c r="R39" t="n">
-        <v>6666062</v>
+        <v>6666032</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5388,7 +5356,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5398,7 +5366,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5426,10 +5394,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127294730</v>
+        <v>127294826</v>
       </c>
       <c r="B40" t="n">
-        <v>98469</v>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5456,7 +5424,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5473,10 +5441,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>505313</v>
+        <v>505332</v>
       </c>
       <c r="R40" t="n">
-        <v>6666027</v>
+        <v>6666037</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5508,7 +5476,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5518,7 +5486,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5546,36 +5514,44 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127295873</v>
+        <v>127294976</v>
       </c>
       <c r="B41" t="n">
-        <v>96721</v>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
@@ -5585,10 +5561,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>505457</v>
+        <v>505373</v>
       </c>
       <c r="R41" t="n">
-        <v>6666062</v>
+        <v>6666042</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5620,7 +5596,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5630,7 +5606,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5642,26 +5618,6 @@
       <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5678,43 +5634,46 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127294173</v>
+        <v>127295061</v>
       </c>
       <c r="B42" t="n">
-        <v>4773</v>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5722,10 +5681,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>505254</v>
+        <v>505372</v>
       </c>
       <c r="R42" t="n">
-        <v>6666041</v>
+        <v>6666038</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5757,7 +5716,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5767,7 +5726,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5779,26 +5738,6 @@
       <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5815,36 +5754,44 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127301907</v>
+        <v>127295076</v>
       </c>
       <c r="B43" t="n">
-        <v>96816</v>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1841</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
@@ -5854,10 +5801,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>505491</v>
+        <v>505375</v>
       </c>
       <c r="R43" t="n">
-        <v>6666106</v>
+        <v>6666039</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5887,9 +5834,19 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5901,26 +5858,6 @@
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5937,10 +5874,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127295399</v>
+        <v>127295179</v>
       </c>
       <c r="B44" t="n">
-        <v>98469</v>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5967,7 +5904,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>149</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5984,10 +5921,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>505404</v>
+        <v>505378</v>
       </c>
       <c r="R44" t="n">
-        <v>6666039</v>
+        <v>6666040</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6019,7 +5956,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6029,7 +5966,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6057,10 +5994,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127295179</v>
+        <v>127295189</v>
       </c>
       <c r="B45" t="n">
-        <v>98469</v>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6087,7 +6024,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6104,10 +6041,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>505378</v>
+        <v>505380</v>
       </c>
       <c r="R45" t="n">
-        <v>6666040</v>
+        <v>6666036</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6139,7 +6076,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6149,7 +6086,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6177,10 +6114,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127295238</v>
+        <v>127295207</v>
       </c>
       <c r="B46" t="n">
-        <v>98469</v>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6207,7 +6144,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6224,10 +6161,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>505388</v>
+        <v>505383</v>
       </c>
       <c r="R46" t="n">
-        <v>6666037</v>
+        <v>6666039</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6259,7 +6196,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6269,7 +6206,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6297,37 +6234,46 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127298146</v>
+        <v>127295213</v>
       </c>
       <c r="B47" t="n">
-        <v>91371</v>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6335,10 +6281,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>505544</v>
+        <v>505383</v>
       </c>
       <c r="R47" t="n">
-        <v>6666053</v>
+        <v>6666036</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6370,7 +6316,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6380,7 +6326,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6392,21 +6338,6 @@
       <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6423,37 +6354,46 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127296862</v>
+        <v>127295238</v>
       </c>
       <c r="B48" t="n">
-        <v>79061</v>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6461,10 +6401,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>505478</v>
+        <v>505388</v>
       </c>
       <c r="R48" t="n">
-        <v>6666105</v>
+        <v>6666037</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6496,7 +6436,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6506,7 +6446,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6518,26 +6458,6 @@
       <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6554,37 +6474,46 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127297221</v>
+        <v>127295297</v>
       </c>
       <c r="B49" t="n">
-        <v>75136</v>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6439</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6592,10 +6521,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>505478</v>
+        <v>505400</v>
       </c>
       <c r="R49" t="n">
-        <v>6666109</v>
+        <v>6666034</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6627,7 +6556,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6637,7 +6566,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6649,26 +6578,6 @@
       <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6685,10 +6594,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127296142</v>
+        <v>127295317</v>
       </c>
       <c r="B50" t="n">
-        <v>98469</v>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6715,7 +6624,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>68</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6732,10 +6641,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>505465</v>
+        <v>505401</v>
       </c>
       <c r="R50" t="n">
-        <v>6666072</v>
+        <v>6666036</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6767,7 +6676,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6777,7 +6686,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6805,45 +6714,57 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130181166</v>
+        <v>127295345</v>
       </c>
       <c r="B51" t="n">
-        <v>97298</v>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1841</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Främundsberget, Dlr</t>
+          <t>Ö om Främundstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>505485</v>
+        <v>505402</v>
       </c>
       <c r="R51" t="n">
-        <v>6666118</v>
+        <v>6666038</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6870,17 +6791,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Återfynd.</t>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6889,63 +6815,76 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130181123</v>
+        <v>127295399</v>
       </c>
       <c r="B52" t="n">
-        <v>97203</v>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Främundsberget, Dlr</t>
+          <t>Ö om Främundstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>505469</v>
+        <v>505404</v>
       </c>
       <c r="R52" t="n">
-        <v>6666108</v>
+        <v>6666039</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6972,12 +6911,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6986,21 +6935,974 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>127295681</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Ö om Främundstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>505425</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6666033</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>127295731</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Ö om Främundstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>505443</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6666049</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>127295841</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Ö om Främundstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>505457</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6666062</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>127296043</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Ö om Främundstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>505457</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6666067</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>127296105</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Ö om Främundstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>505454</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6666071</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>127296113</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Ö om Främundstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>505461</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6666073</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>127296142</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Ö om Främundstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>505465</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6666072</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>127294425</v>
+      </c>
+      <c r="B60" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Ö om Främundstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>505296</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6666023</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
